--- a/Results/Hydrogen/hydrogen land use results.xlsx
+++ b/Results/Hydrogen/hydrogen land use results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28.51959972144338</v>
+        <v>28.51959972144363</v>
       </c>
       <c r="C2" t="n">
-        <v>55.07466720368041</v>
+        <v>55.07466720368068</v>
       </c>
       <c r="D2" t="n">
-        <v>118.2833657098831</v>
+        <v>118.283365709883</v>
       </c>
       <c r="E2" t="n">
-        <v>55.07466720368041</v>
+        <v>55.07466720368068</v>
       </c>
       <c r="F2" t="n">
-        <v>55.07466720368041</v>
+        <v>55.07466720368068</v>
       </c>
       <c r="G2" t="n">
-        <v>90.55606635355856</v>
+        <v>90.55606635355741</v>
       </c>
       <c r="H2" t="n">
-        <v>181.45591233467</v>
+        <v>181.4559123346697</v>
       </c>
       <c r="I2" t="n">
-        <v>55.07466720368041</v>
+        <v>55.07466720368068</v>
       </c>
       <c r="J2" t="n">
-        <v>49.53480942920174</v>
+        <v>49.53480942920022</v>
       </c>
       <c r="K2" t="n">
-        <v>34.78862090000901</v>
+        <v>34.78862090000982</v>
       </c>
       <c r="L2" t="n">
-        <v>159.4345329922352</v>
+        <v>13.02146820476462</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.984255050875179</v>
+        <v>1.984255050875503</v>
       </c>
       <c r="C3" t="n">
-        <v>1.173858341730927</v>
+        <v>1.173858341730922</v>
       </c>
       <c r="D3" t="n">
-        <v>1.984255050875179</v>
+        <v>1.984255050875503</v>
       </c>
       <c r="E3" t="n">
-        <v>1.376556343150849</v>
+        <v>1.376556343150911</v>
       </c>
       <c r="F3" t="n">
-        <v>1.376556343150848</v>
+        <v>1.376556343150879</v>
       </c>
       <c r="G3" t="n">
-        <v>1.979733000758823</v>
+        <v>1.979733000758681</v>
       </c>
       <c r="H3" t="n">
-        <v>1.984255050875179</v>
+        <v>1.984255050875503</v>
       </c>
       <c r="I3" t="n">
-        <v>1.957013301450427</v>
+        <v>1.95701330145055</v>
       </c>
       <c r="J3" t="n">
-        <v>1.984255050875178</v>
+        <v>1.984255050875503</v>
       </c>
       <c r="K3" t="n">
-        <v>1.984255050875178</v>
+        <v>1.984255050875503</v>
       </c>
       <c r="L3" t="n">
-        <v>1.984255050875178</v>
+        <v>1.984255050875503</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15.54894977686838</v>
+        <v>4.090424665668298</v>
       </c>
       <c r="C4" t="n">
-        <v>3.932677319261771</v>
+        <v>3.932677319261733</v>
       </c>
       <c r="D4" t="n">
-        <v>4.175318037160463</v>
+        <v>4.175298528824691</v>
       </c>
       <c r="E4" t="n">
-        <v>3.898883751007093</v>
+        <v>3.898883751007163</v>
       </c>
       <c r="F4" t="n">
-        <v>4.082313411900388</v>
+        <v>4.082313411900459</v>
       </c>
       <c r="G4" t="n">
-        <v>15.54442772675207</v>
+        <v>15.54442772675217</v>
       </c>
       <c r="H4" t="n">
-        <v>18.78162889571</v>
+        <v>18.78162889570952</v>
       </c>
       <c r="I4" t="n">
-        <v>15.52170802744365</v>
+        <v>4.063182916243152</v>
       </c>
       <c r="J4" t="n">
-        <v>4.239737876661651</v>
+        <v>4.239737876662783</v>
       </c>
       <c r="K4" t="n">
-        <v>3.93051640018341</v>
+        <v>3.930516400183484</v>
       </c>
       <c r="L4" t="n">
-        <v>4.144701134886802</v>
+        <v>4.144701134886949</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.726786654179111</v>
+        <v>5.726786654178929</v>
       </c>
       <c r="C5" t="n">
-        <v>5.699544904754418</v>
+        <v>5.699544904754394</v>
       </c>
       <c r="D5" t="n">
-        <v>5.726783824482136</v>
+        <v>5.726783824482181</v>
       </c>
       <c r="E5" t="n">
-        <v>5.652502716499931</v>
+        <v>5.652502716499955</v>
       </c>
       <c r="F5" t="n">
-        <v>5.652502716499931</v>
+        <v>5.652502716499955</v>
       </c>
       <c r="G5" t="n">
-        <v>5.72226460406285</v>
+        <v>5.722264604062719</v>
       </c>
       <c r="H5" t="n">
-        <v>5.726786654179111</v>
+        <v>5.726786654178929</v>
       </c>
       <c r="I5" t="n">
-        <v>5.699544904754418</v>
+        <v>5.699544904754394</v>
       </c>
       <c r="J5" t="n">
-        <v>5.726786654179111</v>
+        <v>5.726786654178929</v>
       </c>
       <c r="K5" t="n">
-        <v>5.726786654179111</v>
+        <v>5.726786654178929</v>
       </c>
       <c r="L5" t="n">
-        <v>5.726786654179111</v>
+        <v>5.726786654178929</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.7277843192236</v>
+        <v>15.72778431922366</v>
       </c>
       <c r="C6" t="n">
-        <v>24.72119354787286</v>
+        <v>24.72119354787248</v>
       </c>
       <c r="D6" t="n">
-        <v>26.67107458682882</v>
+        <v>26.67107458682915</v>
       </c>
       <c r="E6" t="n">
-        <v>22.24689275694159</v>
+        <v>22.24689275694148</v>
       </c>
       <c r="F6" t="n">
-        <v>15.95979114860431</v>
+        <v>15.95979114860445</v>
       </c>
       <c r="G6" t="n">
-        <v>24.78710558083917</v>
+        <v>24.78710558083943</v>
       </c>
       <c r="H6" t="n">
-        <v>24.79162763094584</v>
+        <v>24.79162763094629</v>
       </c>
       <c r="I6" t="n">
-        <v>24.7643858815307</v>
+        <v>24.76438588153021</v>
       </c>
       <c r="J6" t="n">
-        <v>24.79340893218406</v>
+        <v>24.79340893218418</v>
       </c>
       <c r="K6" t="n">
-        <v>15.55941877647514</v>
+        <v>15.55941877647538</v>
       </c>
       <c r="L6" t="n">
-        <v>34.25956987311933</v>
+        <v>34.2595698731196</v>
       </c>
     </row>
     <row r="7">
@@ -721,31 +721,31 @@
         <v>657.0221274340049</v>
       </c>
       <c r="D7" t="n">
-        <v>657.0493709638374</v>
+        <v>657.0493709638371</v>
       </c>
       <c r="E7" t="n">
         <v>820.918743828835</v>
       </c>
       <c r="F7" t="n">
-        <v>657.0221256220825</v>
+        <v>657.0221256220832</v>
       </c>
       <c r="G7" t="n">
-        <v>657.0448471333142</v>
+        <v>657.0448471333139</v>
       </c>
       <c r="H7" t="n">
-        <v>657.0493691834301</v>
+        <v>657.0493691834307</v>
       </c>
       <c r="I7" t="n">
         <v>657.0221274340049</v>
       </c>
       <c r="J7" t="n">
-        <v>657.0493691834301</v>
+        <v>657.0493691834307</v>
       </c>
       <c r="K7" t="n">
-        <v>478.2115105901403</v>
+        <v>574.7581321101153</v>
       </c>
       <c r="L7" t="n">
-        <v>657.0493691834301</v>
+        <v>657.0493691834307</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.918644083430193</v>
+        <v>4.918644083430334</v>
       </c>
       <c r="C8" t="n">
-        <v>2.507350833693804</v>
+        <v>2.507350833693946</v>
       </c>
       <c r="D8" t="n">
-        <v>3.003574057350165</v>
+        <v>3.003574057350299</v>
       </c>
       <c r="E8" t="n">
-        <v>2.507350833693804</v>
+        <v>2.507350833693946</v>
       </c>
       <c r="F8" t="n">
-        <v>2.507350833693804</v>
+        <v>2.507350833693946</v>
       </c>
       <c r="G8" t="n">
-        <v>3.606453486315502</v>
+        <v>3.606453486315528</v>
       </c>
       <c r="H8" t="n">
-        <v>2.085407559954449</v>
+        <v>2.085407559954473</v>
       </c>
       <c r="I8" t="n">
-        <v>2.507350833693804</v>
+        <v>2.507350833693946</v>
       </c>
       <c r="J8" t="n">
-        <v>4.529990183161317</v>
+        <v>4.529990183161274</v>
       </c>
       <c r="K8" t="n">
-        <v>4.794643469280338</v>
+        <v>4.794643469280122</v>
       </c>
       <c r="L8" t="n">
-        <v>5.280721700383704</v>
+        <v>5.280721700383756</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.167930158145349</v>
+        <v>5.167930158145228</v>
       </c>
       <c r="C9" t="n">
-        <v>3.126742231314267</v>
+        <v>3.126742231314435</v>
       </c>
       <c r="D9" t="n">
-        <v>4.387999082813701</v>
+        <v>4.387999082813585</v>
       </c>
       <c r="E9" t="n">
-        <v>3.126742231314267</v>
+        <v>3.126742231314435</v>
       </c>
       <c r="F9" t="n">
-        <v>3.126742231314267</v>
+        <v>3.126742231314435</v>
       </c>
       <c r="G9" t="n">
-        <v>4.612063302576462</v>
+        <v>4.612063302576538</v>
       </c>
       <c r="H9" t="n">
-        <v>4.017097723503517</v>
+        <v>4.017097723503296</v>
       </c>
       <c r="I9" t="n">
-        <v>3.126742231314267</v>
+        <v>3.126742231314435</v>
       </c>
       <c r="J9" t="n">
-        <v>5.009982567007448</v>
+        <v>5.00998256700735</v>
       </c>
       <c r="K9" t="n">
-        <v>5.117459862876144</v>
+        <v>5.117459862876309</v>
       </c>
       <c r="L9" t="n">
-        <v>5.315523881191032</v>
+        <v>5.315523881190961</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>112.7371896451805</v>
+        <v>112.73718964518</v>
       </c>
       <c r="C2" t="n">
-        <v>78.93818134162299</v>
+        <v>78.9381813416222</v>
       </c>
       <c r="D2" t="n">
-        <v>60.22520562207505</v>
+        <v>60.22520562207448</v>
       </c>
       <c r="E2" t="n">
-        <v>78.93818134162299</v>
+        <v>78.9381813416222</v>
       </c>
       <c r="F2" t="n">
-        <v>78.93818134162299</v>
+        <v>78.9381813416222</v>
       </c>
       <c r="G2" t="n">
-        <v>215.6787120018072</v>
+        <v>215.6787120017912</v>
       </c>
       <c r="H2" t="n">
-        <v>64.73136664546271</v>
+        <v>64.73136664546323</v>
       </c>
       <c r="I2" t="n">
-        <v>78.93818134162299</v>
+        <v>78.9381813416222</v>
       </c>
       <c r="J2" t="n">
         <v>107.2175734006595</v>
       </c>
       <c r="K2" t="n">
-        <v>77.57719299711974</v>
+        <v>77.57719299712028</v>
       </c>
       <c r="L2" t="n">
-        <v>110.1150955129074</v>
+        <v>97.55330965010386</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.220641620573216</v>
+        <v>6.220641620573334</v>
       </c>
       <c r="C3" t="n">
-        <v>5.023076849433604</v>
+        <v>5.023076849432901</v>
       </c>
       <c r="D3" t="n">
-        <v>6.220641620573216</v>
+        <v>6.220641620573334</v>
       </c>
       <c r="E3" t="n">
-        <v>5.432278018025515</v>
+        <v>5.432278018024864</v>
       </c>
       <c r="F3" t="n">
-        <v>5.432278018025515</v>
+        <v>5.432278018024845</v>
       </c>
       <c r="G3" t="n">
-        <v>6.210499934977983</v>
+        <v>6.210499934978031</v>
       </c>
       <c r="H3" t="n">
-        <v>6.220641620573216</v>
+        <v>6.220641620573334</v>
       </c>
       <c r="I3" t="n">
-        <v>6.158917943760176</v>
+        <v>6.15891794375969</v>
       </c>
       <c r="J3" t="n">
-        <v>6.220641620573216</v>
+        <v>6.220641620573335</v>
       </c>
       <c r="K3" t="n">
-        <v>6.220641620573217</v>
+        <v>6.220641620573333</v>
       </c>
       <c r="L3" t="n">
-        <v>6.220641620573216</v>
+        <v>6.220641620573334</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.96743795462719</v>
+        <v>23.96743795462764</v>
       </c>
       <c r="C4" t="n">
-        <v>9.887530255969217</v>
+        <v>9.887530255968597</v>
       </c>
       <c r="D4" t="n">
-        <v>10.32386806003145</v>
+        <v>24.69084358460322</v>
       </c>
       <c r="E4" t="n">
-        <v>9.531839281397618</v>
+        <v>9.531839281396891</v>
       </c>
       <c r="F4" t="n">
-        <v>10.23430237526731</v>
+        <v>10.23430237526662</v>
       </c>
       <c r="G4" t="n">
-        <v>23.95729626903213</v>
+        <v>10.33202344943743</v>
       </c>
       <c r="H4" t="n">
-        <v>26.98566856769995</v>
+        <v>26.98566856769997</v>
       </c>
       <c r="I4" t="n">
-        <v>10.28044145821941</v>
+        <v>10.28044145821876</v>
       </c>
       <c r="J4" t="n">
-        <v>24.59899953113112</v>
+        <v>24.59899953113167</v>
       </c>
       <c r="K4" t="n">
-        <v>10.15152073547478</v>
+        <v>10.15152073547532</v>
       </c>
       <c r="L4" t="n">
-        <v>10.23436996695453</v>
+        <v>10.23436996695496</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.25463370661467</v>
+        <v>11.2546337066143</v>
       </c>
       <c r="C5" t="n">
-        <v>11.19291002980163</v>
+        <v>11.19291002980101</v>
       </c>
       <c r="D5" t="n">
-        <v>11.25462971123135</v>
+        <v>11.25462971123111</v>
       </c>
       <c r="E5" t="n">
-        <v>11.11594025484209</v>
+        <v>11.1159402548415</v>
       </c>
       <c r="F5" t="n">
-        <v>11.11594025484209</v>
+        <v>11.1159402548415</v>
       </c>
       <c r="G5" t="n">
-        <v>11.2444920210194</v>
+        <v>11.24449202101932</v>
       </c>
       <c r="H5" t="n">
-        <v>11.25463370661467</v>
+        <v>11.2546337066143</v>
       </c>
       <c r="I5" t="n">
-        <v>11.19291002980163</v>
+        <v>11.19291002980101</v>
       </c>
       <c r="J5" t="n">
-        <v>11.25463370661467</v>
+        <v>11.2546337066143</v>
       </c>
       <c r="K5" t="n">
-        <v>11.25463370661467</v>
+        <v>11.2546337066143</v>
       </c>
       <c r="L5" t="n">
-        <v>11.25463370661467</v>
+        <v>11.2546337066143</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22.50631544381556</v>
+        <v>22.50631544381421</v>
       </c>
       <c r="C6" t="n">
-        <v>34.69018411563731</v>
+        <v>34.69018411563643</v>
       </c>
       <c r="D6" t="n">
-        <v>37.37701432638313</v>
+        <v>37.37701432638398</v>
       </c>
       <c r="E6" t="n">
-        <v>31.32919411480855</v>
+        <v>31.32919411480767</v>
       </c>
       <c r="F6" t="n">
-        <v>22.78909967681501</v>
+        <v>22.78909967681419</v>
       </c>
       <c r="G6" t="n">
-        <v>34.81291592021969</v>
+        <v>34.81291592021946</v>
       </c>
       <c r="H6" t="n">
-        <v>34.82305760571407</v>
+        <v>34.82305760571433</v>
       </c>
       <c r="I6" t="n">
-        <v>34.76133392900182</v>
+        <v>34.76133392900087</v>
       </c>
       <c r="J6" t="n">
-        <v>34.8254781569369</v>
+        <v>34.82547815693803</v>
       </c>
       <c r="K6" t="n">
-        <v>22.27752563874876</v>
+        <v>22.27752563874892</v>
       </c>
       <c r="L6" t="n">
-        <v>47.68892466346091</v>
+        <v>47.68892466346006</v>
       </c>
     </row>
     <row r="7">
@@ -1111,34 +1111,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>456.0686257631175</v>
+        <v>456.0686257631173</v>
       </c>
       <c r="C7" t="n">
-        <v>581.2716566610351</v>
+        <v>581.2716566610344</v>
       </c>
       <c r="D7" t="n">
-        <v>581.3333895925688</v>
+        <v>581.3333895925686</v>
       </c>
       <c r="E7" t="n">
-        <v>725.8245356992323</v>
+        <v>725.8245356992308</v>
       </c>
       <c r="F7" t="n">
-        <v>581.2716566088453</v>
+        <v>581.2716566088444</v>
       </c>
       <c r="G7" t="n">
-        <v>581.3232386522526</v>
+        <v>581.3232386522519</v>
       </c>
       <c r="H7" t="n">
         <v>581.3333803378476</v>
       </c>
       <c r="I7" t="n">
-        <v>581.2716566610351</v>
+        <v>581.2716566610344</v>
       </c>
       <c r="J7" t="n">
         <v>581.3333803378476</v>
       </c>
       <c r="K7" t="n">
-        <v>508.7544934770821</v>
+        <v>508.754493477081</v>
       </c>
       <c r="L7" t="n">
         <v>581.3333803378476</v>
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.500847379187196</v>
+        <v>7.500847379187135</v>
       </c>
       <c r="C8" t="n">
-        <v>6.750460844098352</v>
+        <v>6.750460844098193</v>
       </c>
       <c r="D8" t="n">
-        <v>8.83582986496674</v>
+        <v>8.83582986496662</v>
       </c>
       <c r="E8" t="n">
-        <v>6.750460844098352</v>
+        <v>6.750460844098193</v>
       </c>
       <c r="F8" t="n">
-        <v>6.750460844098352</v>
+        <v>6.750460844098193</v>
       </c>
       <c r="G8" t="n">
-        <v>4.849654729222712</v>
+        <v>4.849654729222802</v>
       </c>
       <c r="H8" t="n">
-        <v>8.917696681755176</v>
+        <v>8.917696681754988</v>
       </c>
       <c r="I8" t="n">
-        <v>6.750460844098352</v>
+        <v>6.750460844098193</v>
       </c>
       <c r="J8" t="n">
-        <v>7.878953115763946</v>
+        <v>7.878953115763976</v>
       </c>
       <c r="K8" t="n">
-        <v>8.309083299371478</v>
+        <v>8.309083299371585</v>
       </c>
       <c r="L8" t="n">
-        <v>7.815190113481811</v>
+        <v>8.281235224518346</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.002647382001227</v>
+        <v>9.002647382001632</v>
       </c>
       <c r="C9" t="n">
-        <v>7.772270221318011</v>
+        <v>7.772270221317972</v>
       </c>
       <c r="D9" t="n">
-        <v>9.546414588838537</v>
+        <v>9.546414588838266</v>
       </c>
       <c r="E9" t="n">
-        <v>7.772270221318011</v>
+        <v>7.772270221317972</v>
       </c>
       <c r="F9" t="n">
-        <v>7.772270221318011</v>
+        <v>7.772270221317972</v>
       </c>
       <c r="G9" t="n">
-        <v>7.887908418865466</v>
+        <v>7.88790841886544</v>
       </c>
       <c r="H9" t="n">
-        <v>9.580953469303502</v>
+        <v>9.580953469303575</v>
       </c>
       <c r="I9" t="n">
-        <v>7.772270221318011</v>
+        <v>7.772270221317972</v>
       </c>
       <c r="J9" t="n">
-        <v>9.15754877259446</v>
+        <v>9.157548772594284</v>
       </c>
       <c r="K9" t="n">
-        <v>9.331938990493597</v>
+        <v>9.331938990494001</v>
       </c>
       <c r="L9" t="n">
-        <v>9.132488150428543</v>
+        <v>9.132488150428662</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-15.83302403596104</v>
+        <v>-15.83302403596091</v>
       </c>
       <c r="C2" t="n">
-        <v>7.241481360481615</v>
+        <v>7.241481360480872</v>
       </c>
       <c r="D2" t="n">
-        <v>119.5922547783642</v>
+        <v>119.5922547783652</v>
       </c>
       <c r="E2" t="n">
-        <v>52.14063836887257</v>
+        <v>52.14063836887477</v>
       </c>
       <c r="F2" t="n">
-        <v>52.14063836887257</v>
+        <v>52.14063836887477</v>
       </c>
       <c r="G2" t="n">
-        <v>69.1447887990583</v>
+        <v>69.14478879905819</v>
       </c>
       <c r="H2" t="n">
-        <v>80.8666118850972</v>
+        <v>80.86661188509694</v>
       </c>
       <c r="I2" t="n">
-        <v>52.14063836887257</v>
+        <v>52.14063836887477</v>
       </c>
       <c r="J2" t="n">
-        <v>35.45031363811637</v>
+        <v>35.45031363811658</v>
       </c>
       <c r="K2" t="n">
-        <v>62.47352553697429</v>
+        <v>62.47352553697431</v>
       </c>
       <c r="L2" t="n">
-        <v>65.34621304485682</v>
+        <v>65.3462130448554</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.736620471301346</v>
+        <v>1.736620471301221</v>
       </c>
       <c r="C3" t="n">
-        <v>1.083515158923771</v>
+        <v>1.083515158923763</v>
       </c>
       <c r="D3" t="n">
-        <v>1.736620471301345</v>
+        <v>1.736620471301236</v>
       </c>
       <c r="E3" t="n">
-        <v>1.380517034724315</v>
+        <v>1.380517034720345</v>
       </c>
       <c r="F3" t="n">
-        <v>1.380517034724356</v>
+        <v>1.380517034720774</v>
       </c>
       <c r="G3" t="n">
-        <v>1.730573246506471</v>
+        <v>1.730573246506099</v>
       </c>
       <c r="H3" t="n">
-        <v>1.736620471301345</v>
+        <v>1.736620471301236</v>
       </c>
       <c r="I3" t="n">
-        <v>1.698926289838478</v>
+        <v>1.698926289838011</v>
       </c>
       <c r="J3" t="n">
-        <v>1.736620471301245</v>
+        <v>1.736620471301237</v>
       </c>
       <c r="K3" t="n">
-        <v>1.736620471301346</v>
+        <v>1.736620471301237</v>
       </c>
       <c r="L3" t="n">
-        <v>1.736620471301346</v>
+        <v>1.736620471301237</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.73757472110983</v>
+        <v>3.455724172536242</v>
       </c>
       <c r="C4" t="n">
-        <v>3.26740614935193</v>
+        <v>3.267406149351941</v>
       </c>
       <c r="D4" t="n">
-        <v>3.559706198468684</v>
+        <v>3.559682451165855</v>
       </c>
       <c r="E4" t="n">
-        <v>3.326147270161368</v>
+        <v>3.326147270161365</v>
       </c>
       <c r="F4" t="n">
-        <v>3.443103411088598</v>
+        <v>3.443103411088597</v>
       </c>
       <c r="G4" t="n">
-        <v>13.73152749631482</v>
+        <v>13.73152749631468</v>
       </c>
       <c r="H4" t="n">
-        <v>16.70185024134043</v>
+        <v>16.70185024134044</v>
       </c>
       <c r="I4" t="n">
-        <v>13.69988053964664</v>
+        <v>13.69988053964659</v>
       </c>
       <c r="J4" t="n">
-        <v>14.00358363853804</v>
+        <v>14.0035836385381</v>
       </c>
       <c r="K4" t="n">
-        <v>3.38496236463604</v>
+        <v>3.384962364635957</v>
       </c>
       <c r="L4" t="n">
-        <v>3.478781709208337</v>
+        <v>3.478781709208412</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.043310481855036</v>
+        <v>5.043310481855281</v>
       </c>
       <c r="C5" t="n">
-        <v>5.035230218795796</v>
+        <v>5.03523021879581</v>
       </c>
       <c r="D5" t="n">
-        <v>5.043304414150442</v>
+        <v>5.043304414150588</v>
       </c>
       <c r="E5" t="n">
-        <v>5.025158425301361</v>
+        <v>5.025158425301387</v>
       </c>
       <c r="F5" t="n">
-        <v>5.025158425301361</v>
+        <v>5.025158425301387</v>
       </c>
       <c r="G5" t="n">
-        <v>5.037263257060101</v>
+        <v>5.037263257060113</v>
       </c>
       <c r="H5" t="n">
-        <v>5.043310481855036</v>
+        <v>5.043310481855281</v>
       </c>
       <c r="I5" t="n">
-        <v>5.005616300392062</v>
+        <v>5.005616300392031</v>
       </c>
       <c r="J5" t="n">
-        <v>5.043310481855036</v>
+        <v>5.043310481855281</v>
       </c>
       <c r="K5" t="n">
-        <v>5.043310481855036</v>
+        <v>5.043310481855281</v>
       </c>
       <c r="L5" t="n">
-        <v>5.043310481855036</v>
+        <v>5.043310481855281</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.29807182082236</v>
+        <v>14.29807182082252</v>
       </c>
       <c r="C6" t="n">
-        <v>22.52779551902457</v>
+        <v>22.52779551919751</v>
       </c>
       <c r="D6" t="n">
-        <v>24.21952087724468</v>
+        <v>24.21952087724377</v>
       </c>
       <c r="E6" t="n">
-        <v>20.24861842862837</v>
+        <v>20.24861842862763</v>
       </c>
       <c r="F6" t="n">
-        <v>14.53252106539338</v>
+        <v>14.53252106539301</v>
       </c>
       <c r="G6" t="n">
-        <v>22.50952202791341</v>
+        <v>22.50952202791323</v>
       </c>
       <c r="H6" t="n">
-        <v>22.51556925271465</v>
+        <v>22.51556925271376</v>
       </c>
       <c r="I6" t="n">
-        <v>22.47787507124519</v>
+        <v>22.4778750712451</v>
       </c>
       <c r="J6" t="n">
-        <v>22.51718422519696</v>
+        <v>22.51718422519613</v>
       </c>
       <c r="K6" t="n">
-        <v>14.14542758697523</v>
+        <v>14.14542758697481</v>
       </c>
       <c r="L6" t="n">
-        <v>31.0994324556236</v>
+        <v>31.09943245562244</v>
       </c>
     </row>
     <row r="7">
@@ -1507,34 +1507,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>472.708803914014</v>
+        <v>472.7088039140141</v>
       </c>
       <c r="C7" t="n">
-        <v>603.0532314493587</v>
+        <v>603.0532314493583</v>
       </c>
       <c r="D7" t="n">
-        <v>603.0613140870593</v>
+        <v>603.0613140870591</v>
       </c>
       <c r="E7" t="n">
-        <v>753.4476492800369</v>
+        <v>753.4476492800371</v>
       </c>
       <c r="F7" t="n">
         <v>603.0236171491749</v>
       </c>
       <c r="G7" t="n">
-        <v>603.055264487623</v>
+        <v>603.0552644876227</v>
       </c>
       <c r="H7" t="n">
         <v>603.0613117124192</v>
       </c>
       <c r="I7" t="n">
-        <v>603.0236175309547</v>
+        <v>603.0236175309543</v>
       </c>
       <c r="J7" t="n">
         <v>603.0613117124192</v>
       </c>
       <c r="K7" t="n">
-        <v>438.9242359384338</v>
+        <v>527.5345577589724</v>
       </c>
       <c r="L7" t="n">
         <v>603.0613117124192</v>
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.349283506835699</v>
+        <v>6.349283506835739</v>
       </c>
       <c r="C8" t="n">
-        <v>2.092553655153025</v>
+        <v>2.092553655152999</v>
       </c>
       <c r="D8" t="n">
-        <v>0.432659494695745</v>
+        <v>0.4326594946956694</v>
       </c>
       <c r="E8" t="n">
-        <v>2.213119991982287</v>
+        <v>2.213119991982347</v>
       </c>
       <c r="F8" t="n">
-        <v>2.213119991982287</v>
+        <v>2.213119991982347</v>
       </c>
       <c r="G8" t="n">
         <v>3.41717964446588</v>
       </c>
       <c r="H8" t="n">
-        <v>1.541052704473396</v>
+        <v>1.541052704473401</v>
       </c>
       <c r="I8" t="n">
-        <v>2.213119991982287</v>
+        <v>2.213119991982347</v>
       </c>
       <c r="J8" t="n">
-        <v>4.630067517652254</v>
+        <v>4.630067517652128</v>
       </c>
       <c r="K8" t="n">
-        <v>3.722123302943476</v>
+        <v>3.722123302943449</v>
       </c>
       <c r="L8" t="n">
-        <v>1.361311434758469</v>
+        <v>1.361311434758441</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.002651261568168</v>
+        <v>6.002651261568204</v>
       </c>
       <c r="C9" t="n">
-        <v>2.125685016538609</v>
+        <v>2.125685016538492</v>
       </c>
       <c r="D9" t="n">
-        <v>1.989880872792167</v>
+        <v>1.989880872792201</v>
       </c>
       <c r="E9" t="n">
-        <v>2.83527872630667</v>
+        <v>2.835278726306624</v>
       </c>
       <c r="F9" t="n">
-        <v>2.83527872630667</v>
+        <v>2.835278726306624</v>
       </c>
       <c r="G9" t="n">
-        <v>4.228470255155893</v>
+        <v>4.228470255155881</v>
       </c>
       <c r="H9" t="n">
-        <v>2.442713516930695</v>
+        <v>2.442713516930704</v>
       </c>
       <c r="I9" t="n">
-        <v>2.83527872630667</v>
+        <v>2.835278726306624</v>
       </c>
       <c r="J9" t="n">
-        <v>4.97755184133555</v>
+        <v>4.977551841335552</v>
       </c>
       <c r="K9" t="n">
-        <v>4.462774424459021</v>
+        <v>4.462774424459043</v>
       </c>
       <c r="L9" t="n">
-        <v>2.068052917493921</v>
+        <v>2.068052917493928</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.306010916300833</v>
+        <v>8.306010916300769</v>
       </c>
       <c r="C2" t="n">
-        <v>9.865129949859588</v>
+        <v>9.865129949857273</v>
       </c>
       <c r="D2" t="n">
         <v>141.3151066139582</v>
       </c>
       <c r="E2" t="n">
-        <v>75.91998006382487</v>
+        <v>75.91998006382458</v>
       </c>
       <c r="F2" t="n">
-        <v>75.91998006382487</v>
+        <v>75.91998006382458</v>
       </c>
       <c r="G2" t="n">
-        <v>86.00953882059783</v>
+        <v>86.00953882059683</v>
       </c>
       <c r="H2" t="n">
-        <v>50.55239755859188</v>
+        <v>50.55239755859181</v>
       </c>
       <c r="I2" t="n">
-        <v>75.91998006382487</v>
+        <v>75.91998006382458</v>
       </c>
       <c r="J2" t="n">
-        <v>25.93391480385743</v>
+        <v>25.9339148038574</v>
       </c>
       <c r="K2" t="n">
-        <v>93.93741360972402</v>
+        <v>93.93741360972393</v>
       </c>
       <c r="L2" t="n">
-        <v>96.65095074226643</v>
+        <v>96.65095074226629</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.194249767491241</v>
+        <v>2.194249767491242</v>
       </c>
       <c r="C3" t="n">
-        <v>1.605265190270609</v>
+        <v>1.60526519027067</v>
       </c>
       <c r="D3" t="n">
-        <v>2.194249767491241</v>
+        <v>2.194249767491242</v>
       </c>
       <c r="E3" t="n">
-        <v>2.245083690772399</v>
+        <v>2.245083690772412</v>
       </c>
       <c r="F3" t="n">
-        <v>2.245083690772396</v>
+        <v>2.245083690772419</v>
       </c>
       <c r="G3" t="n">
-        <v>2.188971796760145</v>
+        <v>2.188971796760164</v>
       </c>
       <c r="H3" t="n">
-        <v>2.194249767491241</v>
+        <v>2.194249767491242</v>
       </c>
       <c r="I3" t="n">
-        <v>2.161389537408272</v>
+        <v>2.161389537408299</v>
       </c>
       <c r="J3" t="n">
-        <v>2.19424976749124</v>
+        <v>2.194249767491212</v>
       </c>
       <c r="K3" t="n">
-        <v>2.19424976749124</v>
+        <v>2.194249767491242</v>
       </c>
       <c r="L3" t="n">
-        <v>2.194249767491241</v>
+        <v>2.194249767491242</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.0828007908609</v>
+        <v>14.08280079086069</v>
       </c>
       <c r="C4" t="n">
-        <v>3.786495827188531</v>
+        <v>3.786495827188501</v>
       </c>
       <c r="D4" t="n">
-        <v>4.090889915009796</v>
+        <v>14.40387575258529</v>
       </c>
       <c r="E4" t="n">
-        <v>3.916584499018195</v>
+        <v>3.916584499018277</v>
       </c>
       <c r="F4" t="n">
-        <v>4.012358324598011</v>
+        <v>4.01235832459809</v>
       </c>
       <c r="G4" t="n">
-        <v>3.990642832903188</v>
+        <v>3.990642832903172</v>
       </c>
       <c r="H4" t="n">
         <v>16.86411539263434</v>
       </c>
       <c r="I4" t="n">
-        <v>3.963060573551282</v>
+        <v>3.963060573551349</v>
       </c>
       <c r="J4" t="n">
-        <v>4.106717722740706</v>
+        <v>4.106717722740677</v>
       </c>
       <c r="K4" t="n">
-        <v>3.938565325925097</v>
+        <v>3.938565325925179</v>
       </c>
       <c r="L4" t="n">
-        <v>4.013128607378984</v>
+        <v>4.013128607378903</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.599064246116603</v>
+        <v>5.599064246116738</v>
       </c>
       <c r="C5" t="n">
-        <v>5.590772038658061</v>
+        <v>5.59077203865816</v>
       </c>
       <c r="D5" t="n">
-        <v>5.599043073515827</v>
+        <v>5.59904307351588</v>
       </c>
       <c r="E5" t="n">
-        <v>5.693356608512449</v>
+        <v>5.693356608512485</v>
       </c>
       <c r="F5" t="n">
-        <v>5.693356608512449</v>
+        <v>5.693356608512485</v>
       </c>
       <c r="G5" t="n">
-        <v>5.593786275385575</v>
+        <v>5.593786275385582</v>
       </c>
       <c r="H5" t="n">
-        <v>5.599064246116603</v>
+        <v>5.599064246116738</v>
       </c>
       <c r="I5" t="n">
-        <v>5.566204016033729</v>
+        <v>5.566204016033775</v>
       </c>
       <c r="J5" t="n">
-        <v>5.599064246116603</v>
+        <v>5.599064246116738</v>
       </c>
       <c r="K5" t="n">
-        <v>5.599064246116603</v>
+        <v>5.599064246116738</v>
       </c>
       <c r="L5" t="n">
-        <v>5.599064246116603</v>
+        <v>5.599064246116738</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.58545272490874</v>
+        <v>14.58545272490861</v>
       </c>
       <c r="C6" t="n">
-        <v>22.94471380770657</v>
+        <v>22.94471380790113</v>
       </c>
       <c r="D6" t="n">
-        <v>24.53934012455321</v>
+        <v>24.53934012455322</v>
       </c>
       <c r="E6" t="n">
-        <v>20.65235297906814</v>
+        <v>20.65235297906808</v>
       </c>
       <c r="F6" t="n">
-        <v>14.88979145079223</v>
+        <v>14.88979145079222</v>
       </c>
       <c r="G6" t="n">
-        <v>22.82453943120113</v>
+        <v>22.82453943120114</v>
       </c>
       <c r="H6" t="n">
-        <v>22.82981740191916</v>
+        <v>22.82981740191907</v>
       </c>
       <c r="I6" t="n">
-        <v>22.79695717184925</v>
+        <v>22.79695717184919</v>
       </c>
       <c r="J6" t="n">
         <v>22.83143765157181</v>
       </c>
       <c r="K6" t="n">
-        <v>14.43230941836901</v>
+        <v>14.4323094183688</v>
       </c>
       <c r="L6" t="n">
-        <v>31.4417456861961</v>
+        <v>31.44174568619597</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>448.4840081262021</v>
+        <v>448.4840081262018</v>
       </c>
       <c r="C7" t="n">
-        <v>572.0609499847222</v>
+        <v>572.0609499847219</v>
       </c>
       <c r="D7" t="n">
-        <v>572.0692454573932</v>
+        <v>572.069245457393</v>
       </c>
       <c r="E7" t="n">
-        <v>714.6511248521984</v>
+        <v>714.6511248521982</v>
       </c>
       <c r="F7" t="n">
-        <v>572.0363821673536</v>
+        <v>572.0363821673535</v>
       </c>
       <c r="G7" t="n">
-        <v>572.0639642214497</v>
+        <v>572.0639642214494</v>
       </c>
       <c r="H7" t="n">
-        <v>572.069242192181</v>
+        <v>572.0692421921808</v>
       </c>
       <c r="I7" t="n">
-        <v>572.0363819620975</v>
+        <v>572.0363819620974</v>
       </c>
       <c r="J7" t="n">
-        <v>572.069242192181</v>
+        <v>572.0692421921808</v>
       </c>
       <c r="K7" t="n">
-        <v>500.4634735910098</v>
+        <v>500.4634735910096</v>
       </c>
       <c r="L7" t="n">
-        <v>572.069242192181</v>
+        <v>572.0692421921808</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.083389863809477</v>
+        <v>6.083389863809522</v>
       </c>
       <c r="C8" t="n">
-        <v>2.336845655250968</v>
+        <v>2.336845655251086</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2900905304590793</v>
+        <v>0.2900905304590953</v>
       </c>
       <c r="E8" t="n">
-        <v>2.178233844747118</v>
+        <v>2.178233844747116</v>
       </c>
       <c r="F8" t="n">
-        <v>2.178233844747118</v>
+        <v>2.178233844747116</v>
       </c>
       <c r="G8" t="n">
-        <v>3.408217747622893</v>
+        <v>3.408217747622901</v>
       </c>
       <c r="H8" t="n">
-        <v>2.642010574484381</v>
+        <v>2.642010574484335</v>
       </c>
       <c r="I8" t="n">
-        <v>2.178233844747118</v>
+        <v>2.178233844747116</v>
       </c>
       <c r="J8" t="n">
-        <v>5.514950200011365</v>
+        <v>5.514950200011319</v>
       </c>
       <c r="K8" t="n">
-        <v>3.742477987702228</v>
+        <v>3.742477987702221</v>
       </c>
       <c r="L8" t="n">
-        <v>1.08911887524673</v>
+        <v>1.089118875246706</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.056575566749236</v>
+        <v>6.056575566749192</v>
       </c>
       <c r="C9" t="n">
-        <v>2.404872842512034</v>
+        <v>2.404872842512085</v>
       </c>
       <c r="D9" t="n">
-        <v>2.241811644328067</v>
+        <v>2.241811644328002</v>
       </c>
       <c r="E9" t="n">
-        <v>3.168387249769962</v>
+        <v>3.168387249769963</v>
       </c>
       <c r="F9" t="n">
-        <v>3.168387249769962</v>
+        <v>3.168387249769963</v>
       </c>
       <c r="G9" t="n">
-        <v>4.497781836822448</v>
+        <v>4.49778183682239</v>
       </c>
       <c r="H9" t="n">
-        <v>3.200579337477774</v>
+        <v>3.200579337477703</v>
       </c>
       <c r="I9" t="n">
-        <v>3.168387249769962</v>
+        <v>3.168387249769963</v>
       </c>
       <c r="J9" t="n">
-        <v>5.744042044250601</v>
+        <v>5.744042044250588</v>
       </c>
       <c r="K9" t="n">
-        <v>4.967739177177542</v>
+        <v>4.967739177177522</v>
       </c>
       <c r="L9" t="n">
-        <v>2.221844401631436</v>
+        <v>2.221844401631392</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.34958948700161</v>
+        <v>18.34958948700154</v>
       </c>
       <c r="C2" t="n">
-        <v>10.90093750837548</v>
+        <v>10.90093750837567</v>
       </c>
       <c r="D2" t="n">
-        <v>152.4673227234419</v>
+        <v>152.4673227234418</v>
       </c>
       <c r="E2" t="n">
-        <v>75.61445053604537</v>
+        <v>75.6144505360452</v>
       </c>
       <c r="F2" t="n">
-        <v>75.61445053604537</v>
+        <v>75.6144505360452</v>
       </c>
       <c r="G2" t="n">
-        <v>97.09330168744732</v>
+        <v>97.09330168744704</v>
       </c>
       <c r="H2" t="n">
-        <v>35.62290380693626</v>
+        <v>35.62290380693623</v>
       </c>
       <c r="I2" t="n">
-        <v>75.61445053604537</v>
+        <v>75.6144505360452</v>
       </c>
       <c r="J2" t="n">
-        <v>17.12660932580591</v>
+        <v>17.12660932580554</v>
       </c>
       <c r="K2" t="n">
-        <v>111.7255536908269</v>
+        <v>111.7255536908271</v>
       </c>
       <c r="L2" t="n">
-        <v>133.1780066797591</v>
+        <v>133.1780066797589</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.270375902147869</v>
+        <v>2.270375902147857</v>
       </c>
       <c r="C3" t="n">
-        <v>1.696317566637733</v>
+        <v>1.696317566637756</v>
       </c>
       <c r="D3" t="n">
-        <v>2.270375902147869</v>
+        <v>2.270375902147854</v>
       </c>
       <c r="E3" t="n">
-        <v>2.479694096777173</v>
+        <v>2.479694096777119</v>
       </c>
       <c r="F3" t="n">
-        <v>2.479694096777174</v>
+        <v>2.479694096777122</v>
       </c>
       <c r="G3" t="n">
-        <v>2.26488404138579</v>
+        <v>2.26488404138553</v>
       </c>
       <c r="H3" t="n">
-        <v>2.270375902147869</v>
+        <v>2.270375902147854</v>
       </c>
       <c r="I3" t="n">
-        <v>2.236247775759864</v>
+        <v>2.236247775759947</v>
       </c>
       <c r="J3" t="n">
-        <v>2.270375902147869</v>
+        <v>2.270375902147857</v>
       </c>
       <c r="K3" t="n">
-        <v>2.270375902147869</v>
+        <v>2.270375902147854</v>
       </c>
       <c r="L3" t="n">
-        <v>2.270375902147869</v>
+        <v>2.270375902147854</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.41503446608181</v>
+        <v>4.169280006749673</v>
       </c>
       <c r="C4" t="n">
-        <v>3.942933045282665</v>
+        <v>3.942933045283077</v>
       </c>
       <c r="D4" t="n">
-        <v>4.26618829122414</v>
+        <v>4.266188291223673</v>
       </c>
       <c r="E4" t="n">
-        <v>4.083272931303801</v>
+        <v>4.083272931303895</v>
       </c>
       <c r="F4" t="n">
-        <v>4.190656819115693</v>
+        <v>4.190656819115761</v>
       </c>
       <c r="G4" t="n">
-        <v>4.163788145987444</v>
+        <v>14.40954260531967</v>
       </c>
       <c r="H4" t="n">
-        <v>17.17710621832144</v>
+        <v>17.17710621832191</v>
       </c>
       <c r="I4" t="n">
-        <v>4.135151880361731</v>
+        <v>14.38090633969407</v>
       </c>
       <c r="J4" t="n">
-        <v>4.279688937385322</v>
+        <v>14.73204896680002</v>
       </c>
       <c r="K4" t="n">
-        <v>4.121850848152468</v>
+        <v>4.121850848152287</v>
       </c>
       <c r="L4" t="n">
-        <v>4.190395350761967</v>
+        <v>4.190395350762273</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.774295148122154</v>
+        <v>5.774295148122349</v>
       </c>
       <c r="C5" t="n">
-        <v>5.765428088146909</v>
+        <v>5.76542808814706</v>
       </c>
       <c r="D5" t="n">
-        <v>5.774285163453066</v>
+        <v>5.774285163453242</v>
       </c>
       <c r="E5" t="n">
-        <v>5.920286436400891</v>
+        <v>5.920286436400622</v>
       </c>
       <c r="F5" t="n">
-        <v>5.920286436400891</v>
+        <v>5.920286436400622</v>
       </c>
       <c r="G5" t="n">
-        <v>5.768803287359797</v>
+        <v>5.768803287360038</v>
       </c>
       <c r="H5" t="n">
-        <v>5.774295148122154</v>
+        <v>5.774295148122349</v>
       </c>
       <c r="I5" t="n">
-        <v>5.740167021734502</v>
+        <v>5.740167021734447</v>
       </c>
       <c r="J5" t="n">
-        <v>5.774295148122154</v>
+        <v>5.774295148122349</v>
       </c>
       <c r="K5" t="n">
-        <v>5.774295148122154</v>
+        <v>5.774295148122349</v>
       </c>
       <c r="L5" t="n">
-        <v>5.774295148122154</v>
+        <v>5.774295148122349</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.79547844164447</v>
+        <v>14.79547844164336</v>
       </c>
       <c r="C6" t="n">
-        <v>23.34196203725275</v>
+        <v>23.34196203707461</v>
       </c>
       <c r="D6" t="n">
-        <v>24.91493570523919</v>
+        <v>24.91493570523975</v>
       </c>
       <c r="E6" t="n">
-        <v>21.00602931576072</v>
+        <v>21.00602931576174</v>
       </c>
       <c r="F6" t="n">
-        <v>15.13448682069432</v>
+        <v>15.13448682069416</v>
       </c>
       <c r="G6" t="n">
-        <v>23.17148545322256</v>
+        <v>23.17148545322356</v>
       </c>
       <c r="H6" t="n">
-        <v>23.17697731398008</v>
+        <v>23.17697731397998</v>
       </c>
       <c r="I6" t="n">
-        <v>23.14284918759803</v>
+        <v>23.14284918759795</v>
       </c>
       <c r="J6" t="n">
-        <v>23.17862451295533</v>
+        <v>23.17862451295482</v>
       </c>
       <c r="K6" t="n">
-        <v>14.63978779726856</v>
+        <v>14.6397877972696</v>
       </c>
       <c r="L6" t="n">
-        <v>31.93215373073813</v>
+        <v>31.93215373073942</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>448.286942519464</v>
+        <v>448.2869425194642</v>
       </c>
       <c r="C7" t="n">
-        <v>571.810413966801</v>
+        <v>571.8104139668011</v>
       </c>
       <c r="D7" t="n">
-        <v>571.8192848245695</v>
+        <v>571.8192848245699</v>
       </c>
       <c r="E7" t="n">
-        <v>714.3388560996734</v>
+        <v>714.338856099673</v>
       </c>
       <c r="F7" t="n">
-        <v>571.7851532503455</v>
+        <v>571.7851532503456</v>
       </c>
       <c r="G7" t="n">
-        <v>571.813789166014</v>
+        <v>571.8137891660135</v>
       </c>
       <c r="H7" t="n">
-        <v>571.819281026775</v>
+        <v>571.8192810267756</v>
       </c>
       <c r="I7" t="n">
         <v>571.7851529003883</v>
       </c>
       <c r="J7" t="n">
-        <v>571.819281026775</v>
+        <v>571.8192810267756</v>
       </c>
       <c r="K7" t="n">
-        <v>497.3402673390599</v>
+        <v>416.2700154173389</v>
       </c>
       <c r="L7" t="n">
-        <v>571.819281026775</v>
+        <v>571.8192810267756</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.951766528904255</v>
+        <v>5.951766528904216</v>
       </c>
       <c r="C8" t="n">
-        <v>2.427421555856792</v>
+        <v>2.427421555856768</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1760701375264309</v>
+        <v>0.1760701375268753</v>
       </c>
       <c r="E8" t="n">
-        <v>2.385393151391023</v>
+        <v>2.385393151391134</v>
       </c>
       <c r="F8" t="n">
-        <v>2.385393151391023</v>
+        <v>2.385393151391134</v>
       </c>
       <c r="G8" t="n">
-        <v>3.328522727639639</v>
+        <v>3.328522727639901</v>
       </c>
       <c r="H8" t="n">
-        <v>3.121324341961471</v>
+        <v>3.121324341961424</v>
       </c>
       <c r="I8" t="n">
-        <v>2.385393151391023</v>
+        <v>2.385393151391134</v>
       </c>
       <c r="J8" t="n">
-        <v>5.990502030930437</v>
+        <v>5.990502030930661</v>
       </c>
       <c r="K8" t="n">
-        <v>3.66780171825369</v>
+        <v>3.667801718253476</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5022197377528418</v>
+        <v>0.5022197377530911</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.065231850880184</v>
+        <v>6.065231850879925</v>
       </c>
       <c r="C9" t="n">
-        <v>2.509112545248851</v>
+        <v>2.509112545249142</v>
       </c>
       <c r="D9" t="n">
-        <v>2.287497042670274</v>
+        <v>2.287497042670147</v>
       </c>
       <c r="E9" t="n">
-        <v>3.368886032807683</v>
+        <v>3.368886032807794</v>
       </c>
       <c r="F9" t="n">
-        <v>3.368886032807682</v>
+        <v>3.368886032807794</v>
       </c>
       <c r="G9" t="n">
-        <v>4.571744814306145</v>
+        <v>4.571744814306292</v>
       </c>
       <c r="H9" t="n">
-        <v>3.487619986282078</v>
+        <v>3.487619986282034</v>
       </c>
       <c r="I9" t="n">
-        <v>3.368886032807683</v>
+        <v>3.368886032807794</v>
       </c>
       <c r="J9" t="n">
-        <v>6.09524342889348</v>
+        <v>6.095243428893565</v>
       </c>
       <c r="K9" t="n">
-        <v>5.144548443536326</v>
+        <v>5.144548443536674</v>
       </c>
       <c r="L9" t="n">
-        <v>2.090226985968923</v>
+        <v>2.090226985969252</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.121467222916081</v>
+        <v>5.12146722291607</v>
       </c>
       <c r="C2" t="n">
-        <v>7.909716311962286</v>
+        <v>7.909716311962353</v>
       </c>
       <c r="D2" t="n">
-        <v>140.4953359641915</v>
+        <v>140.4953359641918</v>
       </c>
       <c r="E2" t="n">
-        <v>81.00952377099526</v>
+        <v>81.00952377099537</v>
       </c>
       <c r="F2" t="n">
-        <v>81.00952377099526</v>
+        <v>81.00952377099537</v>
       </c>
       <c r="G2" t="n">
-        <v>95.22428108320199</v>
+        <v>95.22428108320145</v>
       </c>
       <c r="H2" t="n">
-        <v>70.73650725978719</v>
+        <v>70.73650725978732</v>
       </c>
       <c r="I2" t="n">
-        <v>81.00952377099526</v>
+        <v>81.00952377099537</v>
       </c>
       <c r="J2" t="n">
-        <v>37.56733158554662</v>
+        <v>37.56733158554658</v>
       </c>
       <c r="K2" t="n">
-        <v>84.56380215555367</v>
+        <v>84.56380215555365</v>
       </c>
       <c r="L2" t="n">
-        <v>99.07573936996383</v>
+        <v>99.07573936996394</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.971289196284228</v>
+        <v>1.97128919628425</v>
       </c>
       <c r="C3" t="n">
-        <v>1.241104350436607</v>
+        <v>1.241104350436613</v>
       </c>
       <c r="D3" t="n">
-        <v>1.971289196284227</v>
+        <v>1.97128919628425</v>
       </c>
       <c r="E3" t="n">
-        <v>2.133240117984752</v>
+        <v>2.133240117984761</v>
       </c>
       <c r="F3" t="n">
-        <v>2.133240117984756</v>
+        <v>2.133240117984762</v>
       </c>
       <c r="G3" t="n">
-        <v>1.966032384468558</v>
+        <v>1.966032384468557</v>
       </c>
       <c r="H3" t="n">
-        <v>1.971289196284227</v>
+        <v>1.97128919628425</v>
       </c>
       <c r="I3" t="n">
-        <v>1.938385997014463</v>
+        <v>1.938385997014466</v>
       </c>
       <c r="J3" t="n">
-        <v>1.971289196284227</v>
+        <v>1.97128919628425</v>
       </c>
       <c r="K3" t="n">
-        <v>1.971289196284228</v>
+        <v>1.97128919628425</v>
       </c>
       <c r="L3" t="n">
-        <v>1.971289196284228</v>
+        <v>1.97128919628425</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.37066479975398</v>
+        <v>3.841158240942411</v>
       </c>
       <c r="C4" t="n">
-        <v>3.58992983816189</v>
+        <v>3.589929838161907</v>
       </c>
       <c r="D4" t="n">
-        <v>3.924916119806068</v>
+        <v>3.92491611980608</v>
       </c>
       <c r="E4" t="n">
-        <v>3.782768716192658</v>
+        <v>3.782768716192677</v>
       </c>
       <c r="F4" t="n">
-        <v>3.867244782312858</v>
+        <v>3.867244782312856</v>
       </c>
       <c r="G4" t="n">
         <v>3.835901429126725</v>
       </c>
       <c r="H4" t="n">
-        <v>17.34882000551148</v>
+        <v>17.3488200055115</v>
       </c>
       <c r="I4" t="n">
-        <v>14.33776160048425</v>
+        <v>3.808255041672636</v>
       </c>
       <c r="J4" t="n">
-        <v>14.67965992838723</v>
+        <v>14.67965992838724</v>
       </c>
       <c r="K4" t="n">
         <v>3.764629650955081</v>
       </c>
       <c r="L4" t="n">
-        <v>3.864860523997437</v>
+        <v>3.864860523997442</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.581912971063371</v>
+        <v>5.581912971063368</v>
       </c>
       <c r="C5" t="n">
-        <v>5.573720621387724</v>
+        <v>5.573720621387731</v>
       </c>
       <c r="D5" t="n">
-        <v>5.581920721857655</v>
+        <v>5.581920721857663</v>
       </c>
       <c r="E5" t="n">
-        <v>5.710682381505186</v>
+        <v>5.710682381505182</v>
       </c>
       <c r="F5" t="n">
-        <v>5.710682381505186</v>
+        <v>5.710682381505182</v>
       </c>
       <c r="G5" t="n">
-        <v>5.576656159247688</v>
+        <v>5.576656159247686</v>
       </c>
       <c r="H5" t="n">
-        <v>5.581912971063371</v>
+        <v>5.581912971063368</v>
       </c>
       <c r="I5" t="n">
         <v>5.549009771793595</v>
       </c>
       <c r="J5" t="n">
-        <v>5.581912971063371</v>
+        <v>5.581912971063368</v>
       </c>
       <c r="K5" t="n">
-        <v>5.581912971063371</v>
+        <v>5.581912971063368</v>
       </c>
       <c r="L5" t="n">
-        <v>5.581912971063371</v>
+        <v>5.581912971063368</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.97842929806532</v>
+        <v>14.97842929806531</v>
       </c>
       <c r="C6" t="n">
         <v>23.70347863067724</v>
       </c>
       <c r="D6" t="n">
-        <v>25.33400992373759</v>
+        <v>25.33400992373736</v>
       </c>
       <c r="E6" t="n">
-        <v>21.31654022975877</v>
+        <v>21.31654022975863</v>
       </c>
       <c r="F6" t="n">
-        <v>15.3138468916155</v>
+        <v>15.31384689161554</v>
       </c>
       <c r="G6" t="n">
-        <v>23.55024189556514</v>
+        <v>23.55024189556531</v>
       </c>
       <c r="H6" t="n">
-        <v>23.55549870737593</v>
+        <v>23.55549870737582</v>
       </c>
       <c r="I6" t="n">
-        <v>23.52259550811111</v>
+        <v>23.52259550811107</v>
       </c>
       <c r="J6" t="n">
-        <v>23.55718434501632</v>
+        <v>23.55718434501656</v>
       </c>
       <c r="K6" t="n">
-        <v>14.81910583025514</v>
+        <v>14.81910583025524</v>
       </c>
       <c r="L6" t="n">
-        <v>32.51496490661698</v>
+        <v>32.51496490661743</v>
       </c>
     </row>
     <row r="7">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>473.9404836961293</v>
+        <v>473.9404836961292</v>
       </c>
       <c r="C7" t="n">
         <v>604.5937741457612</v>
@@ -2707,7 +2707,7 @@
         <v>755.3496470798474</v>
       </c>
       <c r="F7" t="n">
-        <v>604.5690633654585</v>
+        <v>604.5690633654586</v>
       </c>
       <c r="G7" t="n">
         <v>604.5967096836212</v>
@@ -2722,7 +2722,7 @@
         <v>604.601966495437</v>
       </c>
       <c r="K7" t="n">
-        <v>440.0758357937356</v>
+        <v>440.0758357937354</v>
       </c>
       <c r="L7" t="n">
         <v>604.601966495437</v>
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.136485929409005</v>
+        <v>6.136485929409009</v>
       </c>
       <c r="C8" t="n">
         <v>2.292375825571434</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3410098216763549</v>
+        <v>0.3410098216763529</v>
       </c>
       <c r="E8" t="n">
-        <v>1.998230285905627</v>
+        <v>1.99823028590564</v>
       </c>
       <c r="F8" t="n">
-        <v>1.998230285905627</v>
+        <v>1.99823028590564</v>
       </c>
       <c r="G8" t="n">
-        <v>3.19803192778059</v>
+        <v>3.198031927780582</v>
       </c>
       <c r="H8" t="n">
-        <v>2.138551910655165</v>
+        <v>2.138551910655163</v>
       </c>
       <c r="I8" t="n">
-        <v>1.998230285905627</v>
+        <v>1.99823028590564</v>
       </c>
       <c r="J8" t="n">
-        <v>5.068824263992408</v>
+        <v>5.068824263992415</v>
       </c>
       <c r="K8" t="n">
-        <v>3.879185246874776</v>
+        <v>3.879185246874755</v>
       </c>
       <c r="L8" t="n">
-        <v>1.048414529840878</v>
+        <v>1.048414529840881</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.064827158708312</v>
+        <v>6.064827158708313</v>
       </c>
       <c r="C9" t="n">
-        <v>2.33148230181169</v>
+        <v>2.331482301811696</v>
       </c>
       <c r="D9" t="n">
-        <v>2.178835910991546</v>
+        <v>2.178835910991557</v>
       </c>
       <c r="E9" t="n">
-        <v>3.005361854898454</v>
+        <v>3.005361854898464</v>
       </c>
       <c r="F9" t="n">
-        <v>3.005361854898454</v>
+        <v>3.005361854898464</v>
       </c>
       <c r="G9" t="n">
-        <v>4.350943662329985</v>
+        <v>4.350943662329988</v>
       </c>
       <c r="H9" t="n">
-        <v>2.912147527689291</v>
+        <v>2.912147527689296</v>
       </c>
       <c r="I9" t="n">
-        <v>3.005361854898454</v>
+        <v>3.005361854898464</v>
       </c>
       <c r="J9" t="n">
-        <v>5.436753835687763</v>
+        <v>5.43675383568777</v>
       </c>
       <c r="K9" t="n">
-        <v>4.911165100490998</v>
+        <v>4.911165100490981</v>
       </c>
       <c r="L9" t="n">
-        <v>2.150081598785328</v>
+        <v>2.150081598785331</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35.07041894534266</v>
+        <v>35.07041894534263</v>
       </c>
       <c r="C2" t="n">
-        <v>10.80358955754098</v>
+        <v>10.80358955754099</v>
       </c>
       <c r="D2" t="n">
-        <v>161.6318455833375</v>
+        <v>161.6318455833374</v>
       </c>
       <c r="E2" t="n">
-        <v>84.33259935649437</v>
+        <v>84.33259935649467</v>
       </c>
       <c r="F2" t="n">
-        <v>84.33259935649437</v>
+        <v>84.33259935649467</v>
       </c>
       <c r="G2" t="n">
-        <v>109.1565610745266</v>
+        <v>109.1565610745267</v>
       </c>
       <c r="H2" t="n">
-        <v>26.21492589959614</v>
+        <v>26.21492589959615</v>
       </c>
       <c r="I2" t="n">
-        <v>84.33259935649437</v>
+        <v>84.33259935649467</v>
       </c>
       <c r="J2" t="n">
-        <v>27.29215901810984</v>
+        <v>27.29215901810985</v>
       </c>
       <c r="K2" t="n">
-        <v>117.4641926360177</v>
+        <v>117.4641926360176</v>
       </c>
       <c r="L2" t="n">
-        <v>144.127090207391</v>
+        <v>144.1270902073911</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.257156831997252</v>
+        <v>2.257156831997257</v>
       </c>
       <c r="C3" t="n">
-        <v>1.552288011248237</v>
+        <v>1.552288011248236</v>
       </c>
       <c r="D3" t="n">
-        <v>2.257156831997252</v>
+        <v>2.257156831997257</v>
       </c>
       <c r="E3" t="n">
-        <v>2.541000639396868</v>
+        <v>2.541000639396962</v>
       </c>
       <c r="F3" t="n">
-        <v>2.541000639397126</v>
+        <v>2.541000639396963</v>
       </c>
       <c r="G3" t="n">
-        <v>2.251471462257072</v>
+        <v>2.251471462257092</v>
       </c>
       <c r="H3" t="n">
-        <v>2.257156831997252</v>
+        <v>2.257156831997258</v>
       </c>
       <c r="I3" t="n">
-        <v>2.221591973212508</v>
+        <v>2.221591973212597</v>
       </c>
       <c r="J3" t="n">
-        <v>2.257156831997253</v>
+        <v>2.257156831997258</v>
       </c>
       <c r="K3" t="n">
-        <v>2.257156831997253</v>
+        <v>2.257156831997258</v>
       </c>
       <c r="L3" t="n">
-        <v>2.257156831997253</v>
+        <v>2.257156831997258</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.197483891809956</v>
+        <v>4.19748389180995</v>
       </c>
       <c r="C4" t="n">
-        <v>3.923706913839177</v>
+        <v>3.92370691383918</v>
       </c>
       <c r="D4" t="n">
-        <v>14.79257946826736</v>
+        <v>4.281623678640794</v>
       </c>
       <c r="E4" t="n">
-        <v>4.110096392995407</v>
+        <v>4.110096392995433</v>
       </c>
       <c r="F4" t="n">
-        <v>4.218055504094932</v>
+        <v>4.218055504094957</v>
       </c>
       <c r="G4" t="n">
-        <v>4.191798522069771</v>
+        <v>14.44158108578818</v>
       </c>
       <c r="H4" t="n">
-        <v>17.24210069663381</v>
+        <v>17.24210069663389</v>
       </c>
       <c r="I4" t="n">
-        <v>4.161919033025272</v>
+        <v>14.41170159674368</v>
       </c>
       <c r="J4" t="n">
-        <v>4.308475289591505</v>
+        <v>4.308475289591504</v>
       </c>
       <c r="K4" t="n">
-        <v>4.160856175078588</v>
+        <v>4.160856175078586</v>
       </c>
       <c r="L4" t="n">
-        <v>4.218801493164593</v>
+        <v>4.218801493164579</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.812681038562386</v>
+        <v>5.812681038562382</v>
       </c>
       <c r="C5" t="n">
-        <v>5.803600313988247</v>
+        <v>5.803600313988238</v>
       </c>
       <c r="D5" t="n">
-        <v>5.81268779393109</v>
+        <v>5.812687793931087</v>
       </c>
       <c r="E5" t="n">
-        <v>5.974111575622424</v>
+        <v>5.974111575622417</v>
       </c>
       <c r="F5" t="n">
-        <v>5.974111575622424</v>
+        <v>5.974111575622417</v>
       </c>
       <c r="G5" t="n">
-        <v>5.806995668822148</v>
+        <v>5.806995668822219</v>
       </c>
       <c r="H5" t="n">
-        <v>5.812681038562386</v>
+        <v>5.812681038562382</v>
       </c>
       <c r="I5" t="n">
-        <v>5.777116179777744</v>
+        <v>5.777116179777721</v>
       </c>
       <c r="J5" t="n">
-        <v>5.812681038562386</v>
+        <v>5.812681038562382</v>
       </c>
       <c r="K5" t="n">
-        <v>5.812681038562386</v>
+        <v>5.812681038562382</v>
       </c>
       <c r="L5" t="n">
-        <v>5.812681038562386</v>
+        <v>5.812681038562382</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.89269471022349</v>
+        <v>14.89269471022348</v>
       </c>
       <c r="C6" t="n">
         <v>23.51077701903496</v>
       </c>
       <c r="D6" t="n">
-        <v>25.07944392097435</v>
+        <v>25.07944392097434</v>
       </c>
       <c r="E6" t="n">
-        <v>21.15672145753503</v>
+        <v>21.15672145753511</v>
       </c>
       <c r="F6" t="n">
-        <v>15.24209042352371</v>
+        <v>15.24209042352386</v>
       </c>
       <c r="G6" t="n">
-        <v>23.32424315630954</v>
+        <v>23.32424315630956</v>
       </c>
       <c r="H6" t="n">
-        <v>23.32992852603119</v>
+        <v>23.32992852603115</v>
       </c>
       <c r="I6" t="n">
-        <v>23.29436366726499</v>
+        <v>23.29436366726506</v>
       </c>
       <c r="J6" t="n">
-        <v>23.33158667951245</v>
+        <v>23.33158667951243</v>
       </c>
       <c r="K6" t="n">
-        <v>14.73596876048083</v>
+        <v>14.73596876048082</v>
       </c>
       <c r="L6" t="n">
-        <v>32.14332475278843</v>
+        <v>32.14332475278839</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>449.149181811822</v>
+        <v>449.1491818118219</v>
       </c>
       <c r="C7" t="n">
-        <v>572.9082688832431</v>
+        <v>572.9082688832428</v>
       </c>
       <c r="D7" t="n">
-        <v>572.917353950542</v>
+        <v>572.9173539505416</v>
       </c>
       <c r="E7" t="n">
-        <v>715.7076307853392</v>
+        <v>715.7076307853393</v>
       </c>
       <c r="F7" t="n">
-        <v>572.8817853755201</v>
+        <v>572.8817853755199</v>
       </c>
       <c r="G7" t="n">
-        <v>572.9116642380767</v>
+        <v>572.9116642380765</v>
       </c>
       <c r="H7" t="n">
-        <v>572.9173496078172</v>
+        <v>572.9173496078168</v>
       </c>
       <c r="I7" t="n">
-        <v>572.8817847490329</v>
+        <v>572.8817847490326</v>
       </c>
       <c r="J7" t="n">
-        <v>572.9173496078172</v>
+        <v>572.9173496078168</v>
       </c>
       <c r="K7" t="n">
-        <v>501.2055889382352</v>
+        <v>417.071132687313</v>
       </c>
       <c r="L7" t="n">
-        <v>572.9173496078172</v>
+        <v>572.9173496078168</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.722303442687106</v>
+        <v>5.722303442687111</v>
       </c>
       <c r="C8" t="n">
-        <v>2.425590248705636</v>
+        <v>2.425590248705635</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.01356619512661503</v>
+        <v>-0.01356619512661769</v>
       </c>
       <c r="E8" t="n">
-        <v>2.184940902288215</v>
+        <v>2.18494090228818</v>
       </c>
       <c r="F8" t="n">
-        <v>2.184940902288215</v>
+        <v>2.18494090228818</v>
       </c>
       <c r="G8" t="n">
-        <v>3.084093376282065</v>
+        <v>3.084093376282087</v>
       </c>
       <c r="H8" t="n">
-        <v>3.357689154261913</v>
+        <v>3.357689154261917</v>
       </c>
       <c r="I8" t="n">
-        <v>2.184940902288215</v>
+        <v>2.18494090228818</v>
       </c>
       <c r="J8" t="n">
-        <v>5.731400655627999</v>
+        <v>5.731400655627994</v>
       </c>
       <c r="K8" t="n">
-        <v>3.57834463173021</v>
+        <v>3.578344631730239</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2804110649223083</v>
+        <v>0.280411064922307</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.067438542619322</v>
+        <v>6.067438542619323</v>
       </c>
       <c r="C9" t="n">
         <v>2.506039969136884</v>
       </c>
       <c r="D9" t="n">
-        <v>2.229881987283492</v>
+        <v>2.229881987283496</v>
       </c>
       <c r="E9" t="n">
-        <v>3.293098713696779</v>
+        <v>3.29309871369678</v>
       </c>
       <c r="F9" t="n">
-        <v>3.293098713696779</v>
+        <v>3.29309871369678</v>
       </c>
       <c r="G9" t="n">
-        <v>4.496076405571657</v>
+        <v>4.49607640557168</v>
       </c>
       <c r="H9" t="n">
-        <v>3.603318264090914</v>
+        <v>3.603318264090916</v>
       </c>
       <c r="I9" t="n">
-        <v>3.293098713696779</v>
+        <v>3.29309871369678</v>
       </c>
       <c r="J9" t="n">
-        <v>5.976196596085162</v>
+        <v>5.97619659608516</v>
       </c>
       <c r="K9" t="n">
-        <v>5.136972406986877</v>
+        <v>5.136972406986908</v>
       </c>
       <c r="L9" t="n">
-        <v>2.005379298856815</v>
+        <v>2.005379298856813</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.87238187873784</v>
+        <v>49.87238187873779</v>
       </c>
       <c r="C2" t="n">
-        <v>13.22920054393613</v>
+        <v>13.22920054393645</v>
       </c>
       <c r="D2" t="n">
-        <v>167.1066029508697</v>
+        <v>167.1066029508696</v>
       </c>
       <c r="E2" t="n">
-        <v>81.7835085595911</v>
+        <v>81.783508559591</v>
       </c>
       <c r="F2" t="n">
-        <v>81.7835085595911</v>
+        <v>81.783508559591</v>
       </c>
       <c r="G2" t="n">
-        <v>122.3209818880169</v>
+        <v>122.3209818880166</v>
       </c>
       <c r="H2" t="n">
-        <v>29.59368103826181</v>
+        <v>29.59368103826175</v>
       </c>
       <c r="I2" t="n">
-        <v>81.7835085595911</v>
+        <v>81.783508559591</v>
       </c>
       <c r="J2" t="n">
-        <v>27.29539434132904</v>
+        <v>27.29539434132911</v>
       </c>
       <c r="K2" t="n">
-        <v>125.8894019813276</v>
+        <v>125.8894019813275</v>
       </c>
       <c r="L2" t="n">
-        <v>170.5872615666003</v>
+        <v>170.5872615666002</v>
       </c>
     </row>
     <row r="3">
@@ -3327,13 +3327,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.590139560024369</v>
+        <v>2.590139560024215</v>
       </c>
       <c r="C3" t="n">
-        <v>1.724411062321564</v>
+        <v>1.724411062321569</v>
       </c>
       <c r="D3" t="n">
-        <v>2.590139560024369</v>
+        <v>2.590139560024215</v>
       </c>
       <c r="E3" t="n">
         <v>2.732208717930398</v>
@@ -3342,22 +3342,22 @@
         <v>2.732208717930397</v>
       </c>
       <c r="G3" t="n">
-        <v>2.583940855380855</v>
+        <v>2.583940855381061</v>
       </c>
       <c r="H3" t="n">
-        <v>2.590139560024369</v>
+        <v>2.590139560024214</v>
       </c>
       <c r="I3" t="n">
-        <v>2.551810164095726</v>
+        <v>2.551810164095956</v>
       </c>
       <c r="J3" t="n">
-        <v>2.590139560024368</v>
+        <v>2.590139560024214</v>
       </c>
       <c r="K3" t="n">
-        <v>2.590139560024369</v>
+        <v>2.590139560024214</v>
       </c>
       <c r="L3" t="n">
-        <v>2.590139560024369</v>
+        <v>2.590139560024215</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15.50533634701685</v>
+        <v>15.50533634701683</v>
       </c>
       <c r="C4" t="n">
-        <v>4.510788079539921</v>
+        <v>4.510788079539939</v>
       </c>
       <c r="D4" t="n">
-        <v>4.90558601941417</v>
+        <v>4.905586019414178</v>
       </c>
       <c r="E4" t="n">
-        <v>4.649542899987085</v>
+        <v>4.649542899987135</v>
       </c>
       <c r="F4" t="n">
-        <v>4.833887347009999</v>
+        <v>4.833887347010084</v>
       </c>
       <c r="G4" t="n">
-        <v>15.49913764237337</v>
+        <v>15.49913764237349</v>
       </c>
       <c r="H4" t="n">
-        <v>18.30597116497005</v>
+        <v>18.30597116497043</v>
       </c>
       <c r="I4" t="n">
-        <v>4.792683764469919</v>
+        <v>4.792683764470013</v>
       </c>
       <c r="J4" t="n">
-        <v>15.8899598813279</v>
+        <v>15.88995988132809</v>
       </c>
       <c r="K4" t="n">
-        <v>4.806626349483157</v>
+        <v>4.806626349483263</v>
       </c>
       <c r="L4" t="n">
-        <v>4.850698441237037</v>
+        <v>4.850698441237145</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.311743976343167</v>
+        <v>6.311743976343259</v>
       </c>
       <c r="C5" t="n">
-        <v>6.301085188158595</v>
+        <v>6.301085188158646</v>
       </c>
       <c r="D5" t="n">
-        <v>6.311787224761313</v>
+        <v>6.311787224761435</v>
       </c>
       <c r="E5" t="n">
-        <v>6.439879772126416</v>
+        <v>6.43987977212652</v>
       </c>
       <c r="F5" t="n">
-        <v>6.439879772126416</v>
+        <v>6.43987977212652</v>
       </c>
       <c r="G5" t="n">
-        <v>6.305545271699835</v>
+        <v>6.30554527169989</v>
       </c>
       <c r="H5" t="n">
-        <v>6.311743976343167</v>
+        <v>6.311743976343259</v>
       </c>
       <c r="I5" t="n">
-        <v>6.273414580414674</v>
+        <v>6.273414580414667</v>
       </c>
       <c r="J5" t="n">
-        <v>6.311743976343167</v>
+        <v>6.311743976343259</v>
       </c>
       <c r="K5" t="n">
-        <v>6.311743976343167</v>
+        <v>6.311743976343259</v>
       </c>
       <c r="L5" t="n">
-        <v>6.311743976343167</v>
+        <v>6.311743976343259</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.59320405419936</v>
+        <v>15.59320405419932</v>
       </c>
       <c r="C6" t="n">
-        <v>24.59820014749126</v>
+        <v>24.59820014749058</v>
       </c>
       <c r="D6" t="n">
-        <v>26.28416875228992</v>
+        <v>26.28416875228908</v>
       </c>
       <c r="E6" t="n">
-        <v>22.13181631730053</v>
+        <v>22.13181631730031</v>
       </c>
       <c r="F6" t="n">
-        <v>15.93483860432381</v>
+        <v>15.9348386043237</v>
       </c>
       <c r="G6" t="n">
-        <v>24.44185855256629</v>
+        <v>24.44185855256615</v>
       </c>
       <c r="H6" t="n">
-        <v>24.4480572571825</v>
+        <v>24.44805725718176</v>
       </c>
       <c r="I6" t="n">
-        <v>24.40972786128117</v>
+        <v>24.40972786128093</v>
       </c>
       <c r="J6" t="n">
-        <v>24.4497974801882</v>
+        <v>24.44979748018786</v>
       </c>
       <c r="K6" t="n">
-        <v>15.42872061038055</v>
+        <v>15.42872061038021</v>
       </c>
       <c r="L6" t="n">
-        <v>33.6976918502476</v>
+        <v>33.69769185024648</v>
       </c>
     </row>
     <row r="7">
@@ -3490,7 +3490,7 @@
         <v>449.2422140899213</v>
       </c>
       <c r="C7" t="n">
-        <v>573.0134919163079</v>
+        <v>573.0134919163082</v>
       </c>
       <c r="D7" t="n">
         <v>573.024155685458</v>
@@ -3499,25 +3499,25 @@
         <v>715.8275568187091</v>
       </c>
       <c r="F7" t="n">
-        <v>572.9858219128046</v>
+        <v>572.9858219128056</v>
       </c>
       <c r="G7" t="n">
-        <v>573.0179519998496</v>
+        <v>573.0179519998495</v>
       </c>
       <c r="H7" t="n">
-        <v>573.0241507044918</v>
+        <v>573.0241507044921</v>
       </c>
       <c r="I7" t="n">
-        <v>572.9858213085631</v>
+        <v>572.9858213085635</v>
       </c>
       <c r="J7" t="n">
-        <v>573.0241507044918</v>
+        <v>573.0241507044921</v>
       </c>
       <c r="K7" t="n">
-        <v>501.3044125957956</v>
+        <v>498.3946520230532</v>
       </c>
       <c r="L7" t="n">
-        <v>573.0241507044918</v>
+        <v>573.0241507044921</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.729994341146726</v>
+        <v>5.729994341146719</v>
       </c>
       <c r="C8" t="n">
-        <v>2.638148879980264</v>
+        <v>2.638148879980268</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2626302358635222</v>
+        <v>0.2626302358635129</v>
       </c>
       <c r="E8" t="n">
-        <v>2.668130172169649</v>
+        <v>2.668130172169658</v>
       </c>
       <c r="F8" t="n">
-        <v>2.668130172169649</v>
+        <v>2.668130172169658</v>
       </c>
       <c r="G8" t="n">
-        <v>3.152184421372683</v>
+        <v>3.152184421372702</v>
       </c>
       <c r="H8" t="n">
-        <v>3.694548571198603</v>
+        <v>3.694548571198606</v>
       </c>
       <c r="I8" t="n">
-        <v>2.668130172169649</v>
+        <v>2.668130172169658</v>
       </c>
       <c r="J8" t="n">
-        <v>6.365027782896543</v>
+        <v>6.365027782896463</v>
       </c>
       <c r="K8" t="n">
-        <v>3.836023347248049</v>
+        <v>3.836023347247358</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03475966124538779</v>
+        <v>0.03475966124538757</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.277044351908916</v>
+        <v>6.277044351908943</v>
       </c>
       <c r="C9" t="n">
-        <v>2.748437571338547</v>
+        <v>2.748437571338563</v>
       </c>
       <c r="D9" t="n">
-        <v>2.578676992638524</v>
+        <v>2.578676992638496</v>
       </c>
       <c r="E9" t="n">
-        <v>3.73284111733659</v>
+        <v>3.732841117336583</v>
       </c>
       <c r="F9" t="n">
-        <v>3.732841117336601</v>
+        <v>3.732841117336583</v>
       </c>
       <c r="G9" t="n">
-        <v>4.742880301658595</v>
+        <v>4.742880301658634</v>
       </c>
       <c r="H9" t="n">
-        <v>3.976883276782413</v>
+        <v>3.976883276782404</v>
       </c>
       <c r="I9" t="n">
-        <v>3.732841117336601</v>
+        <v>3.732841117336583</v>
       </c>
       <c r="J9" t="n">
-        <v>6.599836626752494</v>
+        <v>6.599836626752589</v>
       </c>
       <c r="K9" t="n">
-        <v>5.508594290935353</v>
+        <v>5.508594290934899</v>
       </c>
       <c r="L9" t="n">
-        <v>2.086040031511199</v>
+        <v>2.086040031511224</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27.92279450361435</v>
+        <v>27.92279450361439</v>
       </c>
       <c r="C2" t="n">
-        <v>9.112028749451948</v>
+        <v>9.112028749451873</v>
       </c>
       <c r="D2" t="n">
         <v>156.5517261016848</v>
       </c>
       <c r="E2" t="n">
-        <v>95.01127686590016</v>
+        <v>95.01127686590084</v>
       </c>
       <c r="F2" t="n">
-        <v>95.01127686590016</v>
+        <v>95.01127686590084</v>
       </c>
       <c r="G2" t="n">
-        <v>115.5877179342988</v>
+        <v>115.5877179342976</v>
       </c>
       <c r="H2" t="n">
-        <v>63.1478881365452</v>
+        <v>63.14788813654506</v>
       </c>
       <c r="I2" t="n">
-        <v>95.01127686590016</v>
+        <v>95.01127686590084</v>
       </c>
       <c r="J2" t="n">
-        <v>26.16015873180606</v>
+        <v>26.16015873180598</v>
       </c>
       <c r="K2" t="n">
-        <v>107.2834037388487</v>
+        <v>107.2834037388485</v>
       </c>
       <c r="L2" t="n">
-        <v>102.6422827143395</v>
+        <v>102.642282714339</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.129910497919184</v>
+        <v>2.129910497919193</v>
       </c>
       <c r="C3" t="n">
-        <v>1.34254901797616</v>
+        <v>1.342549017976163</v>
       </c>
       <c r="D3" t="n">
-        <v>2.129910497919184</v>
+        <v>2.129910497919192</v>
       </c>
       <c r="E3" t="n">
-        <v>2.385669866726599</v>
+        <v>2.385669866726611</v>
       </c>
       <c r="F3" t="n">
-        <v>2.385669866726626</v>
+        <v>2.385669866726611</v>
       </c>
       <c r="G3" t="n">
-        <v>2.124563077956118</v>
+        <v>2.124563077956134</v>
       </c>
       <c r="H3" t="n">
-        <v>2.129910497919184</v>
+        <v>2.129910497919192</v>
       </c>
       <c r="I3" t="n">
-        <v>2.096447617884466</v>
+        <v>2.096447617884717</v>
       </c>
       <c r="J3" t="n">
-        <v>2.129910497919184</v>
+        <v>2.129910497919192</v>
       </c>
       <c r="K3" t="n">
-        <v>2.129910497919184</v>
+        <v>2.129910497919193</v>
       </c>
       <c r="L3" t="n">
-        <v>2.129910497919183</v>
+        <v>2.129910497919192</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.87258730767384</v>
+        <v>4.117425334880606</v>
       </c>
       <c r="C4" t="n">
-        <v>3.81733309964264</v>
+        <v>3.817333099642658</v>
       </c>
       <c r="D4" t="n">
-        <v>4.192270454096878</v>
+        <v>4.192270454096806</v>
       </c>
       <c r="E4" t="n">
-        <v>4.047944115092884</v>
+        <v>4.047944115092953</v>
       </c>
       <c r="F4" t="n">
-        <v>4.145085559051473</v>
+        <v>4.145085559051446</v>
       </c>
       <c r="G4" t="n">
-        <v>14.86723988771068</v>
+        <v>14.8672398877107</v>
       </c>
       <c r="H4" t="n">
-        <v>17.84506560464337</v>
+        <v>17.84506560464338</v>
       </c>
       <c r="I4" t="n">
-        <v>4.083962454846219</v>
+        <v>14.83912442763936</v>
       </c>
       <c r="J4" t="n">
-        <v>15.19914683182523</v>
+        <v>15.19914683182536</v>
       </c>
       <c r="K4" t="n">
-        <v>4.049138809679242</v>
+        <v>4.049138809679144</v>
       </c>
       <c r="L4" t="n">
-        <v>4.132735730161103</v>
+        <v>4.132735730161126</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.916882249918387</v>
+        <v>5.916882249918391</v>
       </c>
       <c r="C5" t="n">
-        <v>5.907953694120707</v>
+        <v>5.90795369412073</v>
       </c>
       <c r="D5" t="n">
-        <v>5.916901162404874</v>
+        <v>5.916901162404836</v>
       </c>
       <c r="E5" t="n">
-        <v>6.072600380614337</v>
+        <v>6.072600380614414</v>
       </c>
       <c r="F5" t="n">
-        <v>6.072600380614337</v>
+        <v>6.072600380614414</v>
       </c>
       <c r="G5" t="n">
-        <v>5.91153482995529</v>
+        <v>5.911534829955237</v>
       </c>
       <c r="H5" t="n">
-        <v>5.916882249918387</v>
+        <v>5.916882249918391</v>
       </c>
       <c r="I5" t="n">
-        <v>5.883419369883864</v>
+        <v>5.883419369883861</v>
       </c>
       <c r="J5" t="n">
-        <v>5.916882249918387</v>
+        <v>5.916882249918391</v>
       </c>
       <c r="K5" t="n">
-        <v>5.916882249918387</v>
+        <v>5.916882249918391</v>
       </c>
       <c r="L5" t="n">
-        <v>5.916882249918387</v>
+        <v>5.916882249918391</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.41784388002847</v>
+        <v>15.41784388002856</v>
       </c>
       <c r="C6" t="n">
-        <v>24.40226176409281</v>
+        <v>24.4022617640934</v>
       </c>
       <c r="D6" t="n">
-        <v>26.0556931327971</v>
+        <v>26.05569313279773</v>
       </c>
       <c r="E6" t="n">
-        <v>21.94879120777632</v>
+        <v>21.94879120777642</v>
       </c>
       <c r="F6" t="n">
-        <v>15.77651603283792</v>
+        <v>15.77651603283805</v>
       </c>
       <c r="G6" t="n">
-        <v>24.22335648862427</v>
+        <v>24.2233564886248</v>
       </c>
       <c r="H6" t="n">
-        <v>24.22870390857397</v>
+        <v>24.22870390857418</v>
       </c>
       <c r="I6" t="n">
-        <v>24.19524102855296</v>
+        <v>24.19524102855337</v>
       </c>
       <c r="J6" t="n">
-        <v>24.23043549197612</v>
+        <v>24.23043549197607</v>
       </c>
       <c r="K6" t="n">
-        <v>15.25417763147379</v>
+        <v>15.25417763147393</v>
       </c>
       <c r="L6" t="n">
-        <v>33.43238395814912</v>
+        <v>33.43238395815016</v>
       </c>
     </row>
     <row r="7">
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>474.7405673041962</v>
+        <v>474.7405673041961</v>
       </c>
       <c r="C7" t="n">
         <v>605.5946237421433</v>
@@ -3892,28 +3892,28 @@
         <v>605.6035564905264</v>
       </c>
       <c r="E7" t="n">
-        <v>756.5832036504629</v>
+        <v>756.583203650463</v>
       </c>
       <c r="F7" t="n">
         <v>605.5700898205516</v>
       </c>
       <c r="G7" t="n">
-        <v>605.5982048779779</v>
+        <v>605.5982048779777</v>
       </c>
       <c r="H7" t="n">
-        <v>605.6035522979415</v>
+        <v>605.6035522979414</v>
       </c>
       <c r="I7" t="n">
         <v>605.5700894179065</v>
       </c>
       <c r="J7" t="n">
-        <v>605.6035522979415</v>
+        <v>605.6035522979414</v>
       </c>
       <c r="K7" t="n">
-        <v>526.7048108021916</v>
+        <v>529.7810266173359</v>
       </c>
       <c r="L7" t="n">
-        <v>605.6035522979415</v>
+        <v>605.6035522979414</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.830382828617828</v>
+        <v>5.830382828617778</v>
       </c>
       <c r="C8" t="n">
-        <v>2.404762038691499</v>
+        <v>2.404762038691502</v>
       </c>
       <c r="D8" t="n">
-        <v>0.187537802039004</v>
+        <v>0.1875378020389893</v>
       </c>
       <c r="E8" t="n">
-        <v>1.882764442347542</v>
+        <v>1.882764442347551</v>
       </c>
       <c r="F8" t="n">
-        <v>1.882764442347542</v>
+        <v>1.882764442347551</v>
       </c>
       <c r="G8" t="n">
-        <v>2.942894290939785</v>
+        <v>2.942894290939779</v>
       </c>
       <c r="H8" t="n">
-        <v>2.510561439532116</v>
+        <v>2.510561439532073</v>
       </c>
       <c r="I8" t="n">
-        <v>1.882764442347542</v>
+        <v>1.882764442347551</v>
       </c>
       <c r="J8" t="n">
-        <v>5.552182594351114</v>
+        <v>5.552182594351152</v>
       </c>
       <c r="K8" t="n">
-        <v>3.686744059292606</v>
+        <v>3.686744059292589</v>
       </c>
       <c r="L8" t="n">
-        <v>1.138609147658113</v>
+        <v>1.138609147658103</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.058045209845745</v>
+        <v>6.058045209845711</v>
       </c>
       <c r="C9" t="n">
         <v>2.457421509414459</v>
       </c>
       <c r="D9" t="n">
-        <v>2.241580912581514</v>
+        <v>2.241580912581529</v>
       </c>
       <c r="E9" t="n">
-        <v>3.07619003586362</v>
+        <v>3.076190035863631</v>
       </c>
       <c r="F9" t="n">
-        <v>3.07619003586362</v>
+        <v>3.076190035863631</v>
       </c>
       <c r="G9" t="n">
-        <v>4.363185707745455</v>
+        <v>4.363185707745478</v>
       </c>
       <c r="H9" t="n">
-        <v>3.188762850748827</v>
+        <v>3.188762850748781</v>
       </c>
       <c r="I9" t="n">
-        <v>3.07619003586362</v>
+        <v>3.076190035863631</v>
       </c>
       <c r="J9" t="n">
-        <v>5.767764340633244</v>
+        <v>5.767764340633242</v>
       </c>
       <c r="K9" t="n">
-        <v>5.023161433124722</v>
+        <v>5.023161433124679</v>
       </c>
       <c r="L9" t="n">
-        <v>2.279879167122183</v>
+        <v>2.279879167122171</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>94.47615425993339</v>
+        <v>94.47615425993233</v>
       </c>
       <c r="C2" t="n">
-        <v>14.62129547760096</v>
+        <v>14.6212954776009</v>
       </c>
       <c r="D2" t="n">
-        <v>165.301847213325</v>
+        <v>165.3018472133257</v>
       </c>
       <c r="E2" t="n">
-        <v>112.8914756155044</v>
+        <v>112.8914756155039</v>
       </c>
       <c r="F2" t="n">
-        <v>112.8914756155044</v>
+        <v>112.8914756155039</v>
       </c>
       <c r="G2" t="n">
-        <v>144.9343864847967</v>
+        <v>144.9343864847964</v>
       </c>
       <c r="H2" t="n">
-        <v>30.87942547582547</v>
+        <v>30.87942547582463</v>
       </c>
       <c r="I2" t="n">
-        <v>112.8914756155044</v>
+        <v>112.8914756155039</v>
       </c>
       <c r="J2" t="n">
-        <v>45.44580244765869</v>
+        <v>45.44580244765925</v>
       </c>
       <c r="K2" t="n">
-        <v>143.1627779140663</v>
+        <v>143.1627779140661</v>
       </c>
       <c r="L2" t="n">
-        <v>149.5921457801059</v>
+        <v>149.592145780105</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.986798861756996</v>
+        <v>2.986798861756264</v>
       </c>
       <c r="C3" t="n">
-        <v>2.078066629428662</v>
+        <v>2.078066629428659</v>
       </c>
       <c r="D3" t="n">
-        <v>2.986798861756996</v>
+        <v>2.986798861756265</v>
       </c>
       <c r="E3" t="n">
-        <v>3.41687750697681</v>
+        <v>3.416877506976793</v>
       </c>
       <c r="F3" t="n">
-        <v>3.416877506976812</v>
+        <v>3.416877506976793</v>
       </c>
       <c r="G3" t="n">
-        <v>2.982540506961664</v>
+        <v>2.982540506961461</v>
       </c>
       <c r="H3" t="n">
-        <v>2.986798861756996</v>
+        <v>2.986798861756265</v>
       </c>
       <c r="I3" t="n">
-        <v>2.961121520051782</v>
+        <v>2.961121520051774</v>
       </c>
       <c r="J3" t="n">
-        <v>2.986798861756996</v>
+        <v>2.986798861756265</v>
       </c>
       <c r="K3" t="n">
-        <v>2.986798861756996</v>
+        <v>2.986798861756265</v>
       </c>
       <c r="L3" t="n">
-        <v>2.986798861756996</v>
+        <v>2.986798861756265</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.40066640990512</v>
+        <v>5.3881723769301</v>
       </c>
       <c r="C4" t="n">
-        <v>5.005065956202798</v>
+        <v>5.005065956202816</v>
       </c>
       <c r="D4" t="n">
-        <v>5.395939673707893</v>
+        <v>5.395918220139671</v>
       </c>
       <c r="E4" t="n">
-        <v>5.246795950921523</v>
+        <v>5.246795950921505</v>
       </c>
       <c r="F4" t="n">
-        <v>5.416488208203379</v>
+        <v>5.416488208203369</v>
       </c>
       <c r="G4" t="n">
-        <v>5.383914022134424</v>
+        <v>5.38391402213512</v>
       </c>
       <c r="H4" t="n">
-        <v>19.21111848370923</v>
+        <v>19.21111848370757</v>
       </c>
       <c r="I4" t="n">
-        <v>5.362495035225038</v>
+        <v>16.37498906820113</v>
       </c>
       <c r="J4" t="n">
-        <v>5.523512557256992</v>
+        <v>16.82731370036025</v>
       </c>
       <c r="K4" t="n">
-        <v>5.354177170623405</v>
+        <v>5.354177170623376</v>
       </c>
       <c r="L4" t="n">
-        <v>5.381122009888484</v>
+        <v>5.381122009888959</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.076609150731023</v>
+        <v>7.076609150731234</v>
       </c>
       <c r="C5" t="n">
-        <v>7.065546963787625</v>
+        <v>7.065546963787649</v>
       </c>
       <c r="D5" t="n">
-        <v>7.076651960892515</v>
+        <v>7.076651960893127</v>
       </c>
       <c r="E5" t="n">
-        <v>7.290833050467525</v>
+        <v>7.290833050467499</v>
       </c>
       <c r="F5" t="n">
-        <v>7.290833050467525</v>
+        <v>7.290833050467499</v>
       </c>
       <c r="G5" t="n">
-        <v>7.072350795936361</v>
+        <v>7.072350795936422</v>
       </c>
       <c r="H5" t="n">
-        <v>7.076609150731023</v>
+        <v>7.076609150731234</v>
       </c>
       <c r="I5" t="n">
-        <v>7.050931809026959</v>
+        <v>7.050931809026953</v>
       </c>
       <c r="J5" t="n">
-        <v>7.076609150731023</v>
+        <v>7.076609150731234</v>
       </c>
       <c r="K5" t="n">
-        <v>7.076609150731023</v>
+        <v>7.076609150731234</v>
       </c>
       <c r="L5" t="n">
-        <v>7.076609150731023</v>
+        <v>7.076609150731234</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.57761350638362</v>
+        <v>16.57761350638173</v>
       </c>
       <c r="C6" t="n">
-        <v>26.11306490412591</v>
+        <v>26.11306490412315</v>
       </c>
       <c r="D6" t="n">
-        <v>27.8246919371419</v>
+        <v>27.82469193713931</v>
       </c>
       <c r="E6" t="n">
-        <v>23.52636379364769</v>
+        <v>23.52636379364601</v>
       </c>
       <c r="F6" t="n">
-        <v>16.99030898860319</v>
+        <v>16.99030898860052</v>
       </c>
       <c r="G6" t="n">
-        <v>25.88881276267035</v>
+        <v>25.88881276266545</v>
       </c>
       <c r="H6" t="n">
-        <v>25.89307111739204</v>
+        <v>25.89307111739033</v>
       </c>
       <c r="I6" t="n">
-        <v>25.86739377576001</v>
+        <v>25.86739377575585</v>
       </c>
       <c r="J6" t="n">
-        <v>25.89490186217434</v>
+        <v>25.89490186217034</v>
       </c>
       <c r="K6" t="n">
-        <v>16.40457409882362</v>
+        <v>16.4045740988218</v>
       </c>
       <c r="L6" t="n">
-        <v>35.62384552998692</v>
+        <v>35.62384552998171</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>451.1537084978193</v>
+        <v>451.1537084978199</v>
       </c>
       <c r="C7" t="n">
-        <v>575.3814517770431</v>
+        <v>575.3814517770429</v>
       </c>
       <c r="D7" t="n">
-        <v>575.3925198517812</v>
+        <v>575.3925198517811</v>
       </c>
       <c r="E7" t="n">
-        <v>718.7357905442974</v>
+        <v>718.7357905442969</v>
       </c>
       <c r="F7" t="n">
-        <v>575.3668377261721</v>
+        <v>575.3668377261716</v>
       </c>
       <c r="G7" t="n">
-        <v>575.3882556091925</v>
+        <v>575.3882556091926</v>
       </c>
       <c r="H7" t="n">
-        <v>575.3925139639873</v>
+        <v>575.3925139639881</v>
       </c>
       <c r="I7" t="n">
-        <v>575.3668366222823</v>
+        <v>575.366836622282</v>
       </c>
       <c r="J7" t="n">
-        <v>575.3925139639873</v>
+        <v>575.3925139639881</v>
       </c>
       <c r="K7" t="n">
-        <v>418.9536798077616</v>
+        <v>503.4080646298203</v>
       </c>
       <c r="L7" t="n">
-        <v>575.3925139639873</v>
+        <v>575.3925139639881</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.474204910401824</v>
+        <v>5.474204910402205</v>
       </c>
       <c r="C8" t="n">
-        <v>2.864352795601274</v>
+        <v>2.864352795601272</v>
       </c>
       <c r="D8" t="n">
-        <v>0.698575545755959</v>
+        <v>0.6985755457562313</v>
       </c>
       <c r="E8" t="n">
-        <v>2.347063841854989</v>
+        <v>2.347063841854987</v>
       </c>
       <c r="F8" t="n">
-        <v>2.347063841854989</v>
+        <v>2.347063841854987</v>
       </c>
       <c r="G8" t="n">
-        <v>3.010467050980683</v>
+        <v>3.010467050980984</v>
       </c>
       <c r="H8" t="n">
-        <v>4.057943857052621</v>
+        <v>4.057943857052825</v>
       </c>
       <c r="I8" t="n">
-        <v>2.347063841854989</v>
+        <v>2.347063841854987</v>
       </c>
       <c r="J8" t="n">
-        <v>6.390337957025917</v>
+        <v>6.390337957026277</v>
       </c>
       <c r="K8" t="n">
-        <v>4.001781940910365</v>
+        <v>4.001781940910777</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7839670631405492</v>
+        <v>0.7839670631406473</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.631416719258048</v>
+        <v>6.631416719258269</v>
       </c>
       <c r="C9" t="n">
-        <v>2.987953854954186</v>
+        <v>2.987953854954183</v>
       </c>
       <c r="D9" t="n">
-        <v>2.980098231977597</v>
+        <v>2.980098231977754</v>
       </c>
       <c r="E9" t="n">
-        <v>3.848068382140065</v>
+        <v>3.848068382140049</v>
       </c>
       <c r="F9" t="n">
-        <v>3.848068382140065</v>
+        <v>3.848068382140048</v>
       </c>
       <c r="G9" t="n">
-        <v>4.910364891463176</v>
+        <v>4.910364891463447</v>
       </c>
       <c r="H9" t="n">
-        <v>4.348775633980384</v>
+        <v>4.34877563398063</v>
       </c>
       <c r="I9" t="n">
-        <v>3.848068382140065</v>
+        <v>3.848068382140048</v>
       </c>
       <c r="J9" t="n">
-        <v>6.865448326094813</v>
+        <v>6.865448326094843</v>
       </c>
       <c r="K9" t="n">
-        <v>5.911690313195585</v>
+        <v>5.911690313195695</v>
       </c>
       <c r="L9" t="n">
-        <v>2.56589812935314</v>
+        <v>2.565898129353228</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>77.95692245052969</v>
+        <v>77.95692245052979</v>
       </c>
       <c r="C2" t="n">
-        <v>15.64054128649302</v>
+        <v>15.6405412864924</v>
       </c>
       <c r="D2" t="n">
-        <v>164.1969725023375</v>
+        <v>164.1969725023378</v>
       </c>
       <c r="E2" t="n">
-        <v>98.32662903127641</v>
+        <v>98.32662903127613</v>
       </c>
       <c r="F2" t="n">
-        <v>98.32662903127641</v>
+        <v>98.32662903127613</v>
       </c>
       <c r="G2" t="n">
-        <v>141.2246770421167</v>
+        <v>141.2246770421169</v>
       </c>
       <c r="H2" t="n">
-        <v>33.06448564581414</v>
+        <v>33.06448564581407</v>
       </c>
       <c r="I2" t="n">
-        <v>98.32662903127641</v>
+        <v>98.32662903127613</v>
       </c>
       <c r="J2" t="n">
-        <v>51.94323437294574</v>
+        <v>51.94323437294607</v>
       </c>
       <c r="K2" t="n">
-        <v>139.9507037893318</v>
+        <v>139.9507037893321</v>
       </c>
       <c r="L2" t="n">
-        <v>169.2013673112981</v>
+        <v>169.2013673112985</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.631142058494801</v>
+        <v>3.631142058495112</v>
       </c>
       <c r="C3" t="n">
-        <v>2.527819714367102</v>
+        <v>2.527819714366497</v>
       </c>
       <c r="D3" t="n">
-        <v>3.631142058494801</v>
+        <v>3.631142058495112</v>
       </c>
       <c r="E3" t="n">
-        <v>3.684077837315701</v>
+        <v>3.684077837315624</v>
       </c>
       <c r="F3" t="n">
-        <v>3.68407783731567</v>
+        <v>3.684077837315628</v>
       </c>
       <c r="G3" t="n">
-        <v>3.626500728631119</v>
+        <v>3.626500728631459</v>
       </c>
       <c r="H3" t="n">
-        <v>3.631142058494801</v>
+        <v>3.631142058495111</v>
       </c>
       <c r="I3" t="n">
-        <v>3.603857949054217</v>
+        <v>3.60385794905424</v>
       </c>
       <c r="J3" t="n">
-        <v>3.631142058494801</v>
+        <v>3.631142058495114</v>
       </c>
       <c r="K3" t="n">
-        <v>3.631142058494801</v>
+        <v>3.631142058495112</v>
       </c>
       <c r="L3" t="n">
-        <v>3.631142058494801</v>
+        <v>3.631142058495112</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.11520537703462</v>
+        <v>6.433214588915487</v>
       </c>
       <c r="C4" t="n">
-        <v>6.035584997752733</v>
+        <v>6.035584997752442</v>
       </c>
       <c r="D4" t="n">
-        <v>6.472160908187066</v>
+        <v>6.472160908187115</v>
       </c>
       <c r="E4" t="n">
-        <v>6.146552778001761</v>
+        <v>6.146552778001792</v>
       </c>
       <c r="F4" t="n">
-        <v>6.437664579807002</v>
+        <v>6.437664579807028</v>
       </c>
       <c r="G4" t="n">
-        <v>18.11056404717103</v>
+        <v>18.11056404717099</v>
       </c>
       <c r="H4" t="n">
-        <v>20.96050456394171</v>
+        <v>20.96050456394189</v>
       </c>
       <c r="I4" t="n">
-        <v>6.405930479474672</v>
+        <v>18.08792126759393</v>
       </c>
       <c r="J4" t="n">
-        <v>18.64012658735329</v>
+        <v>6.626014234243804</v>
       </c>
       <c r="K4" t="n">
-        <v>6.41848652254876</v>
+        <v>6.418486522548708</v>
       </c>
       <c r="L4" t="n">
-        <v>6.432347975022352</v>
+        <v>6.432347975022391</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.892991792739719</v>
+        <v>7.892991792739809</v>
       </c>
       <c r="C5" t="n">
-        <v>7.880261651194965</v>
+        <v>7.88026165119469</v>
       </c>
       <c r="D5" t="n">
-        <v>7.893077498943794</v>
+        <v>7.893077498943934</v>
       </c>
       <c r="E5" t="n">
-        <v>8.009077541860309</v>
+        <v>8.009077541860337</v>
       </c>
       <c r="F5" t="n">
-        <v>8.009077541860309</v>
+        <v>8.009077541860337</v>
       </c>
       <c r="G5" t="n">
-        <v>7.888350462876044</v>
+        <v>7.888350462876069</v>
       </c>
       <c r="H5" t="n">
-        <v>7.892991792739719</v>
+        <v>7.892991792739809</v>
       </c>
       <c r="I5" t="n">
-        <v>7.865707683299033</v>
+        <v>7.865707683298995</v>
       </c>
       <c r="J5" t="n">
-        <v>7.892991792739719</v>
+        <v>7.892991792739809</v>
       </c>
       <c r="K5" t="n">
-        <v>7.892991792739719</v>
+        <v>7.892991792739809</v>
       </c>
       <c r="L5" t="n">
-        <v>7.892991792739719</v>
+        <v>7.892991792739809</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.75850396322786</v>
+        <v>17.75850396322829</v>
       </c>
       <c r="C6" t="n">
-        <v>27.88156464555065</v>
+        <v>27.88156464555097</v>
       </c>
       <c r="D6" t="n">
-        <v>29.82832772411415</v>
+        <v>29.82832772411477</v>
       </c>
       <c r="E6" t="n">
-        <v>25.11829294054794</v>
+        <v>25.11829294054893</v>
       </c>
       <c r="F6" t="n">
-        <v>18.13358214680005</v>
+        <v>18.13358214680014</v>
       </c>
       <c r="G6" t="n">
-        <v>27.75076381216564</v>
+        <v>27.75076381216632</v>
       </c>
       <c r="H6" t="n">
-        <v>27.75540514194772</v>
+        <v>27.75540514194834</v>
       </c>
       <c r="I6" t="n">
-        <v>27.72812103258871</v>
+        <v>27.72812103258901</v>
       </c>
       <c r="J6" t="n">
-        <v>27.75736980116626</v>
+        <v>27.75736980116694</v>
       </c>
       <c r="K6" t="n">
-        <v>17.57280639232761</v>
+        <v>17.57280639232764</v>
       </c>
       <c r="L6" t="n">
-        <v>38.19800433418689</v>
+        <v>38.19800433418741</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>451.1819385357654</v>
+        <v>451.1819385357653</v>
       </c>
       <c r="C7" t="n">
-        <v>575.3858401419784</v>
+        <v>575.3858401419777</v>
       </c>
       <c r="D7" t="n">
         <v>575.3985765351977</v>
       </c>
       <c r="E7" t="n">
-        <v>718.7146523022868</v>
+        <v>718.7146523022865</v>
       </c>
       <c r="F7" t="n">
         <v>575.3712871804785</v>
       </c>
       <c r="G7" t="n">
-        <v>575.3939289536589</v>
+        <v>575.393928953659</v>
       </c>
       <c r="H7" t="n">
-        <v>575.3985702835225</v>
+        <v>575.3985702835223</v>
       </c>
       <c r="I7" t="n">
-        <v>575.3712861740814</v>
+        <v>575.3712861740815</v>
       </c>
       <c r="J7" t="n">
-        <v>575.3985702835225</v>
+        <v>575.3985702835223</v>
       </c>
       <c r="K7" t="n">
-        <v>500.5069895959566</v>
+        <v>500.5069895959564</v>
       </c>
       <c r="L7" t="n">
-        <v>575.3985702835225</v>
+        <v>575.3985702835223</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.503339731785569</v>
+        <v>7.503339731785579</v>
       </c>
       <c r="C8" t="n">
-        <v>3.299633128646372</v>
+        <v>3.299633128646271</v>
       </c>
       <c r="D8" t="n">
-        <v>1.375133153887904</v>
+        <v>1.375133153887902</v>
       </c>
       <c r="E8" t="n">
-        <v>3.38531370218644</v>
+        <v>3.385313702186482</v>
       </c>
       <c r="F8" t="n">
-        <v>3.38531370218644</v>
+        <v>3.385313702186482</v>
       </c>
       <c r="G8" t="n">
-        <v>3.798103086599726</v>
+        <v>3.798103086599729</v>
       </c>
       <c r="H8" t="n">
-        <v>4.660097625465919</v>
+        <v>4.660097625465943</v>
       </c>
       <c r="I8" t="n">
-        <v>3.38531370218644</v>
+        <v>3.385313702186482</v>
       </c>
       <c r="J8" t="n">
-        <v>7.366923565426184</v>
+        <v>7.366923565426212</v>
       </c>
       <c r="K8" t="n">
-        <v>4.714534320020677</v>
+        <v>4.71453432002065</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8421129430806119</v>
+        <v>0.8421129430806072</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.402375140085159</v>
+        <v>8.402375140085176</v>
       </c>
       <c r="C9" t="n">
-        <v>3.429284188201152</v>
+        <v>3.429284188200922</v>
       </c>
       <c r="D9" t="n">
-        <v>3.62921786848508</v>
+        <v>3.629217868485094</v>
       </c>
       <c r="E9" t="n">
-        <v>4.665547044131769</v>
+        <v>4.665547044131785</v>
       </c>
       <c r="F9" t="n">
-        <v>4.665547044131769</v>
+        <v>4.665547044131787</v>
       </c>
       <c r="G9" t="n">
-        <v>5.63365496556107</v>
+        <v>5.633654965561086</v>
       </c>
       <c r="H9" t="n">
-        <v>4.9676316589761</v>
+        <v>4.967631658976138</v>
       </c>
       <c r="I9" t="n">
-        <v>4.665547044131769</v>
+        <v>4.665547044131785</v>
       </c>
       <c r="J9" t="n">
-        <v>7.912470010644465</v>
+        <v>7.912470010644483</v>
       </c>
       <c r="K9" t="n">
-        <v>6.566964720832032</v>
+        <v>6.566964720832006</v>
       </c>
       <c r="L9" t="n">
-        <v>2.861114835265931</v>
+        <v>2.861114835265926</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28.1839177180902</v>
+        <v>28.18391771809001</v>
       </c>
       <c r="C2" t="n">
-        <v>53.05096071271068</v>
+        <v>53.05096071271072</v>
       </c>
       <c r="D2" t="n">
-        <v>139.1744223312423</v>
+        <v>139.1744223312421</v>
       </c>
       <c r="E2" t="n">
-        <v>53.05096071271068</v>
+        <v>53.05096071271072</v>
       </c>
       <c r="F2" t="n">
-        <v>53.05096071271068</v>
+        <v>53.05096071271072</v>
       </c>
       <c r="G2" t="n">
-        <v>94.21565635787863</v>
+        <v>94.2156563578783</v>
       </c>
       <c r="H2" t="n">
-        <v>157.9512030097312</v>
+        <v>157.9512030097309</v>
       </c>
       <c r="I2" t="n">
-        <v>53.05096071271068</v>
+        <v>53.05096071271072</v>
       </c>
       <c r="J2" t="n">
-        <v>57.70993944318111</v>
+        <v>57.70993944318112</v>
       </c>
       <c r="K2" t="n">
-        <v>45.94299681519925</v>
+        <v>45.94299681519903</v>
       </c>
       <c r="L2" t="n">
-        <v>31.84892409387186</v>
+        <v>31.84892409387222</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.935829419730046</v>
+        <v>2.935829419729892</v>
       </c>
       <c r="C3" t="n">
-        <v>1.701278022202025</v>
+        <v>1.701278022201879</v>
       </c>
       <c r="D3" t="n">
-        <v>2.935829419730045</v>
+        <v>2.935829419729892</v>
       </c>
       <c r="E3" t="n">
-        <v>1.991261890227966</v>
+        <v>1.99126189022787</v>
       </c>
       <c r="F3" t="n">
-        <v>1.991261890227966</v>
+        <v>1.99126189022787</v>
       </c>
       <c r="G3" t="n">
-        <v>2.930746495671841</v>
+        <v>2.930746495671317</v>
       </c>
       <c r="H3" t="n">
-        <v>2.935829419730046</v>
+        <v>2.935829419729892</v>
       </c>
       <c r="I3" t="n">
-        <v>2.905765357291517</v>
+        <v>2.905765357291468</v>
       </c>
       <c r="J3" t="n">
-        <v>2.935829419730046</v>
+        <v>2.935829419729892</v>
       </c>
       <c r="K3" t="n">
-        <v>2.935829419730046</v>
+        <v>2.935829419729893</v>
       </c>
       <c r="L3" t="n">
-        <v>2.935829419730046</v>
+        <v>2.935829419729892</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.68419846993694</v>
+        <v>16.68419846993648</v>
       </c>
       <c r="C4" t="n">
-        <v>4.973200191918378</v>
+        <v>4.973200191918218</v>
       </c>
       <c r="D4" t="n">
-        <v>5.674088197312824</v>
+        <v>5.67408819731285</v>
       </c>
       <c r="E4" t="n">
-        <v>4.886051070785448</v>
+        <v>4.886051070785214</v>
       </c>
       <c r="F4" t="n">
-        <v>5.175579782062742</v>
+        <v>5.175579782062487</v>
       </c>
       <c r="G4" t="n">
-        <v>5.213221016568202</v>
+        <v>16.67911554587842</v>
       </c>
       <c r="H4" t="n">
-        <v>5.260382725354567</v>
+        <v>19.9841441260693</v>
       </c>
       <c r="I4" t="n">
-        <v>16.65413440749866</v>
+        <v>16.6541344074981</v>
       </c>
       <c r="J4" t="n">
-        <v>17.35065729431928</v>
+        <v>17.35065729431838</v>
       </c>
       <c r="K4" t="n">
-        <v>5.023112681821027</v>
+        <v>5.02311268182041</v>
       </c>
       <c r="L4" t="n">
-        <v>5.235892558810687</v>
+        <v>5.235892558810042</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.937652833796092</v>
+        <v>6.93765283379615</v>
       </c>
       <c r="C5" t="n">
-        <v>6.90758877135775</v>
+        <v>6.907588771357466</v>
       </c>
       <c r="D5" t="n">
-        <v>6.937732609462404</v>
+        <v>6.937732609462861</v>
       </c>
       <c r="E5" t="n">
-        <v>6.762269384038651</v>
+        <v>6.762269384038404</v>
       </c>
       <c r="F5" t="n">
-        <v>6.762269384038651</v>
+        <v>6.762269384038404</v>
       </c>
       <c r="G5" t="n">
-        <v>6.93256990973793</v>
+        <v>6.932569909737666</v>
       </c>
       <c r="H5" t="n">
-        <v>6.937652833796092</v>
+        <v>6.93765283379615</v>
       </c>
       <c r="I5" t="n">
-        <v>6.90758877135775</v>
+        <v>6.907588771357466</v>
       </c>
       <c r="J5" t="n">
-        <v>6.937652833796092</v>
+        <v>6.93765283379615</v>
       </c>
       <c r="K5" t="n">
-        <v>6.937652833796092</v>
+        <v>6.93765283379615</v>
       </c>
       <c r="L5" t="n">
-        <v>6.937652833796092</v>
+        <v>6.93765283379615</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.98188997292601</v>
+        <v>16.98188997292518</v>
       </c>
       <c r="C6" t="n">
-        <v>26.52575585499339</v>
+        <v>26.52575585499336</v>
       </c>
       <c r="D6" t="n">
-        <v>28.70661632687925</v>
+        <v>28.70661632687908</v>
       </c>
       <c r="E6" t="n">
-        <v>23.88443208359386</v>
+        <v>23.88443208359384</v>
       </c>
       <c r="F6" t="n">
         <v>17.17291425587591</v>
       </c>
       <c r="G6" t="n">
-        <v>26.6878793084979</v>
+        <v>26.68787930849749</v>
       </c>
       <c r="H6" t="n">
-        <v>26.69296223248978</v>
+        <v>26.69296223249039</v>
       </c>
       <c r="I6" t="n">
-        <v>26.66289817011749</v>
+        <v>26.66289817011721</v>
       </c>
       <c r="J6" t="n">
-        <v>26.69487072304109</v>
+        <v>26.69487072304132</v>
       </c>
       <c r="K6" t="n">
-        <v>16.80150182119123</v>
+        <v>16.80150182119148</v>
       </c>
       <c r="L6" t="n">
-        <v>36.83698922169475</v>
+        <v>36.83698922169535</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>483.13530862637</v>
+        <v>483.1353086263699</v>
       </c>
       <c r="C7" t="n">
-        <v>616.2491148388978</v>
+        <v>616.2491148388974</v>
       </c>
       <c r="D7" t="n">
-        <v>616.2791818305136</v>
+        <v>616.2791818305134</v>
       </c>
       <c r="E7" t="n">
-        <v>769.8943190595162</v>
+        <v>769.894319059516</v>
       </c>
       <c r="F7" t="n">
         <v>616.2491135441094</v>
       </c>
       <c r="G7" t="n">
-        <v>616.2740959772775</v>
+        <v>616.2740959772764</v>
       </c>
       <c r="H7" t="n">
-        <v>616.2791789013356</v>
+        <v>616.2791789013361</v>
       </c>
       <c r="I7" t="n">
-        <v>616.2491148388978</v>
+        <v>616.2491148388974</v>
       </c>
       <c r="J7" t="n">
-        <v>616.2791789013356</v>
+        <v>616.2791789013361</v>
       </c>
       <c r="K7" t="n">
-        <v>539.1350987996802</v>
+        <v>539.1350987996814</v>
       </c>
       <c r="L7" t="n">
-        <v>616.2791789013356</v>
+        <v>616.2791789013361</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.964585769012419</v>
+        <v>5.964585769012221</v>
       </c>
       <c r="C8" t="n">
-        <v>3.649071700594446</v>
+        <v>3.649071700594437</v>
       </c>
       <c r="D8" t="n">
-        <v>3.403801137214531</v>
+        <v>3.403801137214187</v>
       </c>
       <c r="E8" t="n">
-        <v>3.649071700594446</v>
+        <v>3.649071700594437</v>
       </c>
       <c r="F8" t="n">
-        <v>3.649071700594446</v>
+        <v>3.649071700594437</v>
       </c>
       <c r="G8" t="n">
-        <v>4.455377263476318</v>
+        <v>4.455377263476314</v>
       </c>
       <c r="H8" t="n">
-        <v>3.391183644866462</v>
+        <v>3.391183644866335</v>
       </c>
       <c r="I8" t="n">
-        <v>3.649071700594446</v>
+        <v>3.649071700594437</v>
       </c>
       <c r="J8" t="n">
-        <v>5.365520981334524</v>
+        <v>5.36552098133449</v>
       </c>
       <c r="K8" t="n">
-        <v>5.564199859378025</v>
+        <v>5.564199859377915</v>
       </c>
       <c r="L8" t="n">
-        <v>3.68127325420922</v>
+        <v>5.957426718172884</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.214519663517399</v>
+        <v>6.21451966351709</v>
       </c>
       <c r="C9" t="n">
-        <v>4.286456950868432</v>
+        <v>4.286456950868443</v>
       </c>
       <c r="D9" t="n">
-        <v>5.171610930524826</v>
+        <v>5.171610930524124</v>
       </c>
       <c r="E9" t="n">
-        <v>4.286456950868432</v>
+        <v>4.286456950868443</v>
       </c>
       <c r="F9" t="n">
-        <v>4.286456950868432</v>
+        <v>4.286456950868443</v>
       </c>
       <c r="G9" t="n">
-        <v>5.575799431497313</v>
+        <v>5.575799431497356</v>
       </c>
       <c r="H9" t="n">
-        <v>5.169297456533228</v>
+        <v>5.169297456533389</v>
       </c>
       <c r="I9" t="n">
-        <v>4.286456950868432</v>
+        <v>4.286456950868443</v>
       </c>
       <c r="J9" t="n">
-        <v>5.970962855148738</v>
+        <v>5.970962855148624</v>
       </c>
       <c r="K9" t="n">
-        <v>6.051495338032549</v>
+        <v>6.051495338031976</v>
       </c>
       <c r="L9" t="n">
-        <v>5.286687231227754</v>
+        <v>6.21201987361649</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36.73350770359078</v>
+        <v>36.73350770359061</v>
       </c>
       <c r="C2" t="n">
-        <v>51.04092156293709</v>
+        <v>51.04092156293711</v>
       </c>
       <c r="D2" t="n">
-        <v>133.5139383209089</v>
+        <v>133.5139383209082</v>
       </c>
       <c r="E2" t="n">
-        <v>51.04092156293709</v>
+        <v>51.04092156293711</v>
       </c>
       <c r="F2" t="n">
-        <v>51.04092156293709</v>
+        <v>51.04092156293711</v>
       </c>
       <c r="G2" t="n">
-        <v>99.23987797256896</v>
+        <v>99.2398779725691</v>
       </c>
       <c r="H2" t="n">
-        <v>144.1929798868387</v>
+        <v>144.1929798868384</v>
       </c>
       <c r="I2" t="n">
-        <v>51.04092156293709</v>
+        <v>51.04092156293711</v>
       </c>
       <c r="J2" t="n">
-        <v>57.8422743061633</v>
+        <v>57.84227430616308</v>
       </c>
       <c r="K2" t="n">
-        <v>60.04860809384259</v>
+        <v>60.04860809384162</v>
       </c>
       <c r="L2" t="n">
-        <v>135.287614332396</v>
+        <v>50.55602366029684</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.433896396182463</v>
+        <v>4.433896396182559</v>
       </c>
       <c r="C3" t="n">
-        <v>3.356916440060689</v>
+        <v>3.356916440060672</v>
       </c>
       <c r="D3" t="n">
-        <v>4.433896396182464</v>
+        <v>4.433896396182684</v>
       </c>
       <c r="E3" t="n">
-        <v>3.682118640309739</v>
+        <v>3.682118640309676</v>
       </c>
       <c r="F3" t="n">
-        <v>3.682118640309738</v>
+        <v>3.68211864030968</v>
       </c>
       <c r="G3" t="n">
-        <v>4.428022331391808</v>
+        <v>4.428022331392216</v>
       </c>
       <c r="H3" t="n">
-        <v>4.433896396182463</v>
+        <v>4.433896396182684</v>
       </c>
       <c r="I3" t="n">
-        <v>4.398887716220781</v>
+        <v>4.398887716220676</v>
       </c>
       <c r="J3" t="n">
-        <v>4.433896396182463</v>
+        <v>4.433896396182684</v>
       </c>
       <c r="K3" t="n">
-        <v>4.433896396182463</v>
+        <v>4.433896396182684</v>
       </c>
       <c r="L3" t="n">
-        <v>4.433896396182463</v>
+        <v>4.433896396182684</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.144798193579452</v>
+        <v>19.01263219649594</v>
       </c>
       <c r="C4" t="n">
-        <v>6.896344340416896</v>
+        <v>6.89634434041689</v>
       </c>
       <c r="D4" t="n">
-        <v>7.53360302291861</v>
+        <v>7.533603022919173</v>
       </c>
       <c r="E4" t="n">
-        <v>6.705503668110467</v>
+        <v>6.705503668110488</v>
       </c>
       <c r="F4" t="n">
-        <v>7.095612111239118</v>
+        <v>7.0956121112391</v>
       </c>
       <c r="G4" t="n">
-        <v>7.13892412878912</v>
+        <v>19.00675813170555</v>
       </c>
       <c r="H4" t="n">
-        <v>21.88693714115872</v>
+        <v>21.88693714115891</v>
       </c>
       <c r="I4" t="n">
-        <v>7.109789513617702</v>
+        <v>18.97762351653407</v>
       </c>
       <c r="J4" t="n">
-        <v>7.323073197074169</v>
+        <v>19.64377239719977</v>
       </c>
       <c r="K4" t="n">
-        <v>6.92377203955805</v>
+        <v>6.923772039558581</v>
       </c>
       <c r="L4" t="n">
-        <v>7.113084974969333</v>
+        <v>7.113084974969732</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.640112128382334</v>
+        <v>8.640112128382192</v>
       </c>
       <c r="C5" t="n">
-        <v>8.605103448420673</v>
+        <v>8.605103448420557</v>
       </c>
       <c r="D5" t="n">
-        <v>8.640120707206959</v>
+        <v>8.640120707207357</v>
       </c>
       <c r="E5" t="n">
-        <v>8.509643527418504</v>
+        <v>8.509643527418445</v>
       </c>
       <c r="F5" t="n">
-        <v>8.509643527418504</v>
+        <v>8.509643527418445</v>
       </c>
       <c r="G5" t="n">
-        <v>8.634238063592033</v>
+        <v>8.634238063591935</v>
       </c>
       <c r="H5" t="n">
-        <v>8.640112128382334</v>
+        <v>8.64011212838229</v>
       </c>
       <c r="I5" t="n">
-        <v>8.605103448420673</v>
+        <v>8.605103448420557</v>
       </c>
       <c r="J5" t="n">
-        <v>8.640112128382334</v>
+        <v>8.64011212838229</v>
       </c>
       <c r="K5" t="n">
-        <v>8.640112128382334</v>
+        <v>8.64011212838229</v>
       </c>
       <c r="L5" t="n">
-        <v>8.640112128382334</v>
+        <v>8.64011212838229</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.66831443053041</v>
+        <v>18.66831443052965</v>
       </c>
       <c r="C6" t="n">
-        <v>28.90013387370971</v>
+        <v>28.90013387401107</v>
       </c>
       <c r="D6" t="n">
-        <v>31.17178364960862</v>
+        <v>31.17178364960814</v>
       </c>
       <c r="E6" t="n">
-        <v>26.0773019297056</v>
+        <v>26.07730192970538</v>
       </c>
       <c r="F6" t="n">
-        <v>18.90462561784826</v>
+        <v>18.90462561784814</v>
       </c>
       <c r="G6" t="n">
-        <v>29.01851089810104</v>
+        <v>29.0185108981006</v>
       </c>
       <c r="H6" t="n">
-        <v>29.02438496276325</v>
+        <v>29.02438496276262</v>
       </c>
       <c r="I6" t="n">
-        <v>28.9893762829296</v>
+        <v>28.98937628292933</v>
       </c>
       <c r="J6" t="n">
-        <v>29.02642020020267</v>
+        <v>29.02642020020237</v>
       </c>
       <c r="K6" t="n">
-        <v>18.47594510615141</v>
+        <v>18.47594510615149</v>
       </c>
       <c r="L6" t="n">
-        <v>39.84216656842646</v>
+        <v>39.84216656842695</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>452.0099395287898</v>
+        <v>452.0099395287885</v>
       </c>
       <c r="C7" t="n">
-        <v>576.3252700494411</v>
+        <v>576.3252700494407</v>
       </c>
       <c r="D7" t="n">
-        <v>576.3602824400515</v>
+        <v>576.3602824400514</v>
       </c>
       <c r="E7" t="n">
-        <v>719.8229266645502</v>
+        <v>719.8229266645496</v>
       </c>
       <c r="F7" t="n">
-        <v>576.3252688305555</v>
+        <v>576.3252688305544</v>
       </c>
       <c r="G7" t="n">
-        <v>576.3544046646123</v>
+        <v>576.3544046646128</v>
       </c>
       <c r="H7" t="n">
-        <v>576.3602787294028</v>
+        <v>576.3602787294021</v>
       </c>
       <c r="I7" t="n">
-        <v>576.3252700494411</v>
+        <v>576.3252700494407</v>
       </c>
       <c r="J7" t="n">
-        <v>576.3602787294028</v>
+        <v>576.3602787294021</v>
       </c>
       <c r="K7" t="n">
         <v>419.7810042570769</v>
       </c>
       <c r="L7" t="n">
-        <v>576.3602787294028</v>
+        <v>576.3602787294021</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.428830560356738</v>
+        <v>7.428830560356765</v>
       </c>
       <c r="C8" t="n">
-        <v>5.401517538703978</v>
+        <v>5.401517538703951</v>
       </c>
       <c r="D8" t="n">
-        <v>4.979176489370721</v>
+        <v>4.979176489370385</v>
       </c>
       <c r="E8" t="n">
-        <v>5.401517538703978</v>
+        <v>5.401517538703951</v>
       </c>
       <c r="F8" t="n">
-        <v>5.401517538703978</v>
+        <v>5.401517538703951</v>
       </c>
       <c r="G8" t="n">
-        <v>5.867779606862051</v>
+        <v>5.86777960686229</v>
       </c>
       <c r="H8" t="n">
-        <v>5.18075386631352</v>
+        <v>5.180753866313862</v>
       </c>
       <c r="I8" t="n">
-        <v>5.401517538703978</v>
+        <v>5.401517538703951</v>
       </c>
       <c r="J8" t="n">
-        <v>6.990858174674992</v>
+        <v>6.990858174674932</v>
       </c>
       <c r="K8" t="n">
-        <v>6.779620209110293</v>
+        <v>6.779620209110488</v>
       </c>
       <c r="L8" t="n">
-        <v>5.491821300092697</v>
+        <v>7.207854929004336</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.795469521076965</v>
+        <v>7.795469521077201</v>
       </c>
       <c r="C9" t="n">
-        <v>6.032705431509412</v>
+        <v>6.032705431509404</v>
       </c>
       <c r="D9" t="n">
-        <v>6.797826803210382</v>
+        <v>6.797826803210539</v>
       </c>
       <c r="E9" t="n">
-        <v>6.032705431509412</v>
+        <v>6.032705431509404</v>
       </c>
       <c r="F9" t="n">
-        <v>6.032705431509412</v>
+        <v>6.032705431509404</v>
       </c>
       <c r="G9" t="n">
-        <v>7.134091654910589</v>
+        <v>7.134091654910676</v>
       </c>
       <c r="H9" t="n">
-        <v>6.882664641139347</v>
+        <v>6.882664641139776</v>
       </c>
       <c r="I9" t="n">
-        <v>6.032705431509412</v>
+        <v>6.032705431509404</v>
       </c>
       <c r="J9" t="n">
-        <v>7.617552182379569</v>
+        <v>7.6175521823799</v>
       </c>
       <c r="K9" t="n">
-        <v>7.531126092286562</v>
+        <v>7.531126092285924</v>
       </c>
       <c r="L9" t="n">
-        <v>7.70621735282054</v>
+        <v>7.706217352820231</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>40.0505043062693</v>
+        <v>40.05050430626786</v>
       </c>
       <c r="C2" t="n">
-        <v>59.40835180412314</v>
+        <v>59.40835180411806</v>
       </c>
       <c r="D2" t="n">
-        <v>124.2999305634651</v>
+        <v>124.2999305634642</v>
       </c>
       <c r="E2" t="n">
-        <v>59.40835180412314</v>
+        <v>59.40835180411806</v>
       </c>
       <c r="F2" t="n">
-        <v>59.40835180412314</v>
+        <v>59.40835180411806</v>
       </c>
       <c r="G2" t="n">
-        <v>109.1792892885974</v>
+        <v>109.1792892885956</v>
       </c>
       <c r="H2" t="n">
-        <v>129.2103559793622</v>
+        <v>129.2103559793736</v>
       </c>
       <c r="I2" t="n">
-        <v>59.40835180412314</v>
+        <v>59.40835180411806</v>
       </c>
       <c r="J2" t="n">
-        <v>63.30301529517843</v>
+        <v>63.30301529517697</v>
       </c>
       <c r="K2" t="n">
-        <v>61.79147861028171</v>
+        <v>61.79147861028014</v>
       </c>
       <c r="L2" t="n">
-        <v>132.8885965185435</v>
+        <v>132.8885965185419</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.575671266195738</v>
+        <v>5.575671266194746</v>
       </c>
       <c r="C3" t="n">
-        <v>4.914516737117517</v>
+        <v>4.914516737117258</v>
       </c>
       <c r="D3" t="n">
-        <v>5.575671266195738</v>
+        <v>5.575671266194858</v>
       </c>
       <c r="E3" t="n">
-        <v>5.247000156558087</v>
+        <v>5.247000156558126</v>
       </c>
       <c r="F3" t="n">
-        <v>5.247000156558085</v>
+        <v>5.247000156557959</v>
       </c>
       <c r="G3" t="n">
-        <v>5.568812070073464</v>
+        <v>5.568812070072946</v>
       </c>
       <c r="H3" t="n">
-        <v>5.575671266195738</v>
+        <v>5.575671266194858</v>
       </c>
       <c r="I3" t="n">
-        <v>5.53407010381203</v>
+        <v>5.534070103811648</v>
       </c>
       <c r="J3" t="n">
-        <v>5.575671266195737</v>
+        <v>5.575671266194858</v>
       </c>
       <c r="K3" t="n">
-        <v>5.575671266195738</v>
+        <v>5.575671266194858</v>
       </c>
       <c r="L3" t="n">
-        <v>5.575671266195738</v>
+        <v>5.575671266194858</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.711465038225487</v>
+        <v>8.711465038226139</v>
       </c>
       <c r="C4" t="n">
-        <v>8.522848722158889</v>
+        <v>8.522848722158576</v>
       </c>
       <c r="D4" t="n">
-        <v>22.05009564551949</v>
+        <v>22.05009564551898</v>
       </c>
       <c r="E4" t="n">
-        <v>8.252646296380673</v>
+        <v>8.252646296380053</v>
       </c>
       <c r="F4" t="n">
-        <v>8.689274638290762</v>
+        <v>8.689274638290412</v>
       </c>
       <c r="G4" t="n">
-        <v>8.70460584210484</v>
+        <v>8.704605842105037</v>
       </c>
       <c r="H4" t="n">
-        <v>24.13917187536745</v>
+        <v>24.13917187536583</v>
       </c>
       <c r="I4" t="n">
-        <v>21.28704040883511</v>
+        <v>21.28704040883502</v>
       </c>
       <c r="J4" t="n">
-        <v>21.91017391022235</v>
+        <v>8.921703111437514</v>
       </c>
       <c r="K4" t="n">
-        <v>8.481203068993976</v>
+        <v>8.481203068994157</v>
       </c>
       <c r="L4" t="n">
-        <v>8.662627289735472</v>
+        <v>8.662627289735722</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.17108677968326</v>
+        <v>10.17108677968318</v>
       </c>
       <c r="C5" t="n">
-        <v>10.12948561730035</v>
+        <v>10.12948561729971</v>
       </c>
       <c r="D5" t="n">
-        <v>10.17100515703512</v>
+        <v>10.17100515703433</v>
       </c>
       <c r="E5" t="n">
-        <v>10.16122170189951</v>
+        <v>10.16122170189978</v>
       </c>
       <c r="F5" t="n">
-        <v>10.16122170189951</v>
+        <v>10.16122170189978</v>
       </c>
       <c r="G5" t="n">
-        <v>10.1642275835616</v>
+        <v>10.1642275835609</v>
       </c>
       <c r="H5" t="n">
-        <v>10.17108677968326</v>
+        <v>10.17108677968295</v>
       </c>
       <c r="I5" t="n">
-        <v>10.12948561730035</v>
+        <v>10.12948561729971</v>
       </c>
       <c r="J5" t="n">
-        <v>10.17108677968326</v>
+        <v>10.17108677968295</v>
       </c>
       <c r="K5" t="n">
-        <v>10.17108677968326</v>
+        <v>10.17108677968295</v>
       </c>
       <c r="L5" t="n">
-        <v>10.17108677968326</v>
+        <v>10.17108677968295</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.62198910861387</v>
+        <v>20.62198910861404</v>
       </c>
       <c r="C6" t="n">
-        <v>31.82061511223581</v>
+        <v>31.82061511223487</v>
       </c>
       <c r="D6" t="n">
-        <v>34.15348966205055</v>
+        <v>34.15348966204913</v>
       </c>
       <c r="E6" t="n">
-        <v>28.75193772627248</v>
+        <v>28.75193772627196</v>
       </c>
       <c r="F6" t="n">
-        <v>20.95463059507833</v>
+        <v>20.95463059507767</v>
       </c>
       <c r="G6" t="n">
-        <v>31.8226733302502</v>
+        <v>31.82267333024942</v>
       </c>
       <c r="H6" t="n">
-        <v>31.82953252623739</v>
+        <v>31.82953252623662</v>
       </c>
       <c r="I6" t="n">
-        <v>31.78793136398902</v>
+        <v>31.78793136398826</v>
       </c>
       <c r="J6" t="n">
-        <v>31.83173509427919</v>
+        <v>31.83173509427837</v>
       </c>
       <c r="K6" t="n">
-        <v>20.41380323908074</v>
+        <v>20.41380323907989</v>
       </c>
       <c r="L6" t="n">
-        <v>43.53674875177715</v>
+        <v>43.536748751776</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>453.1814478803068</v>
+        <v>453.1814478803062</v>
       </c>
       <c r="C7" t="n">
-        <v>577.6444798367047</v>
+        <v>577.6444798367033</v>
       </c>
       <c r="D7" t="n">
-        <v>577.6860853245187</v>
+        <v>577.6860853245182</v>
       </c>
       <c r="E7" t="n">
-        <v>721.3201889255273</v>
+        <v>721.3201889255255</v>
       </c>
       <c r="F7" t="n">
-        <v>577.644478624186</v>
+        <v>577.6444786241846</v>
       </c>
       <c r="G7" t="n">
-        <v>577.6792218029644</v>
+        <v>577.679221802965</v>
       </c>
       <c r="H7" t="n">
-        <v>577.6860809990869</v>
+        <v>577.6860809990862</v>
       </c>
       <c r="I7" t="n">
-        <v>577.6444798367047</v>
+        <v>577.6444798367033</v>
       </c>
       <c r="J7" t="n">
-        <v>577.6860809990869</v>
+        <v>577.6860809990862</v>
       </c>
       <c r="K7" t="n">
         <v>505.5476094218862</v>
       </c>
       <c r="L7" t="n">
-        <v>577.6860809990869</v>
+        <v>577.6860809990862</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.481078379688148</v>
+        <v>8.481078379687981</v>
       </c>
       <c r="C8" t="n">
-        <v>6.380239306116042</v>
+        <v>6.380239306116086</v>
       </c>
       <c r="D8" t="n">
-        <v>6.268811081771335</v>
+        <v>6.268811081770829</v>
       </c>
       <c r="E8" t="n">
-        <v>6.380239306116042</v>
+        <v>6.380239306116086</v>
       </c>
       <c r="F8" t="n">
-        <v>6.380239306116042</v>
+        <v>6.380239306116086</v>
       </c>
       <c r="G8" t="n">
-        <v>6.719494125090637</v>
+        <v>6.719494125090602</v>
       </c>
       <c r="H8" t="n">
-        <v>6.550845054500404</v>
+        <v>6.550845054500713</v>
       </c>
       <c r="I8" t="n">
-        <v>6.380239306116042</v>
+        <v>6.380239306116086</v>
       </c>
       <c r="J8" t="n">
-        <v>8.019873524827107</v>
+        <v>8.019873524827227</v>
       </c>
       <c r="K8" t="n">
-        <v>7.815464057068355</v>
+        <v>7.815464057068409</v>
       </c>
       <c r="L8" t="n">
-        <v>6.656782085212948</v>
+        <v>6.656782085213037</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.884614146685463</v>
+        <v>8.884614146685228</v>
       </c>
       <c r="C9" t="n">
-        <v>7.123490518108373</v>
+        <v>7.123490518108213</v>
       </c>
       <c r="D9" t="n">
-        <v>7.983653521932128</v>
+        <v>7.983653521931991</v>
       </c>
       <c r="E9" t="n">
-        <v>7.123490518108373</v>
+        <v>7.123490518108213</v>
       </c>
       <c r="F9" t="n">
-        <v>7.123490518108373</v>
+        <v>7.123490518108213</v>
       </c>
       <c r="G9" t="n">
-        <v>8.142168557723439</v>
+        <v>8.142168557723346</v>
       </c>
       <c r="H9" t="n">
-        <v>8.101048487420801</v>
+        <v>8.101048487421036</v>
       </c>
       <c r="I9" t="n">
-        <v>7.123490518108373</v>
+        <v>7.123490518108213</v>
       </c>
       <c r="J9" t="n">
-        <v>8.697275834888172</v>
+        <v>8.697275834888778</v>
       </c>
       <c r="K9" t="n">
-        <v>8.613594873900361</v>
+        <v>8.61359487390043</v>
       </c>
       <c r="L9" t="n">
-        <v>8.14362985369085</v>
+        <v>8.143629853691442</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>47.20660058191716</v>
+        <v>47.20660058191531</v>
       </c>
       <c r="C2" t="n">
-        <v>51.0789024768106</v>
+        <v>51.07890247681061</v>
       </c>
       <c r="D2" t="n">
-        <v>66.25774591306735</v>
+        <v>66.25774591306524</v>
       </c>
       <c r="E2" t="n">
-        <v>51.0789024768106</v>
+        <v>51.07890247681061</v>
       </c>
       <c r="F2" t="n">
-        <v>51.0789024768106</v>
+        <v>51.07890247681061</v>
       </c>
       <c r="G2" t="n">
-        <v>148.8017607086462</v>
+        <v>148.8017607086459</v>
       </c>
       <c r="H2" t="n">
-        <v>82.7971690335861</v>
+        <v>82.79716903358613</v>
       </c>
       <c r="I2" t="n">
-        <v>51.0789024768106</v>
+        <v>51.07890247681061</v>
       </c>
       <c r="J2" t="n">
-        <v>63.40644901487681</v>
+        <v>63.40644901487498</v>
       </c>
       <c r="K2" t="n">
-        <v>61.28301926271801</v>
+        <v>61.28301926271483</v>
       </c>
       <c r="L2" t="n">
-        <v>33.50406722941712</v>
+        <v>57.54071183527211</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.017316978876364</v>
+        <v>5.017316978874311</v>
       </c>
       <c r="C3" t="n">
-        <v>4.102221228919612</v>
+        <v>4.102221228919597</v>
       </c>
       <c r="D3" t="n">
-        <v>5.017316978876363</v>
+        <v>5.01731697887431</v>
       </c>
       <c r="E3" t="n">
-        <v>4.438166356151575</v>
+        <v>4.438166356151592</v>
       </c>
       <c r="F3" t="n">
-        <v>4.438166356151574</v>
+        <v>4.438166356151585</v>
       </c>
       <c r="G3" t="n">
-        <v>5.00933736639248</v>
+        <v>5.009337366391573</v>
       </c>
       <c r="H3" t="n">
-        <v>5.017316978876363</v>
+        <v>5.01731697887431</v>
       </c>
       <c r="I3" t="n">
-        <v>4.968827328789157</v>
+        <v>4.968827328789159</v>
       </c>
       <c r="J3" t="n">
-        <v>5.017316978876364</v>
+        <v>5.01731697887431</v>
       </c>
       <c r="K3" t="n">
-        <v>5.017316978876364</v>
+        <v>5.01731697887431</v>
       </c>
       <c r="L3" t="n">
-        <v>5.017316978876363</v>
+        <v>5.01731697887431</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.238601603858813</v>
+        <v>8.238601603857735</v>
       </c>
       <c r="C4" t="n">
-        <v>7.841580640535817</v>
+        <v>7.841580640535877</v>
       </c>
       <c r="D4" t="n">
-        <v>8.395943433111677</v>
+        <v>22.27523501458419</v>
       </c>
       <c r="E4" t="n">
-        <v>7.624233667500003</v>
+        <v>7.624233667500024</v>
       </c>
       <c r="F4" t="n">
-        <v>8.122134405095313</v>
+        <v>8.122134405095364</v>
       </c>
       <c r="G4" t="n">
-        <v>21.72603369470171</v>
+        <v>8.230621991373688</v>
       </c>
       <c r="H4" t="n">
-        <v>24.73461926358056</v>
+        <v>24.73461926357771</v>
       </c>
       <c r="I4" t="n">
-        <v>21.68552365709802</v>
+        <v>8.190111953772442</v>
       </c>
       <c r="J4" t="n">
-        <v>22.13015842208876</v>
+        <v>22.13015842208799</v>
       </c>
       <c r="K4" t="n">
-        <v>7.974164281738471</v>
+        <v>7.974164281737536</v>
       </c>
       <c r="L4" t="n">
-        <v>8.124378263311558</v>
+        <v>8.124378263310279</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.986221601917531</v>
+        <v>9.986221601916824</v>
       </c>
       <c r="C5" t="n">
-        <v>9.937731951831175</v>
+        <v>9.93773195183118</v>
       </c>
       <c r="D5" t="n">
-        <v>9.986158752548185</v>
+        <v>9.986158752547587</v>
       </c>
       <c r="E5" t="n">
-        <v>9.918715195030707</v>
+        <v>9.918715195030805</v>
       </c>
       <c r="F5" t="n">
-        <v>9.918715195030707</v>
+        <v>9.918715195030805</v>
       </c>
       <c r="G5" t="n">
-        <v>9.978241989434883</v>
+        <v>9.978241989432767</v>
       </c>
       <c r="H5" t="n">
-        <v>9.986221601917531</v>
+        <v>9.986221601916824</v>
       </c>
       <c r="I5" t="n">
-        <v>9.937731951831175</v>
+        <v>9.93773195183118</v>
       </c>
       <c r="J5" t="n">
-        <v>9.986221601917531</v>
+        <v>9.986221601916824</v>
       </c>
       <c r="K5" t="n">
-        <v>9.986221601917531</v>
+        <v>9.986221601916824</v>
       </c>
       <c r="L5" t="n">
-        <v>9.986221601917531</v>
+        <v>9.986221601916824</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.26020294554869</v>
+        <v>21.26020294554774</v>
       </c>
       <c r="C6" t="n">
-        <v>32.96474676814995</v>
+        <v>32.96474676772119</v>
       </c>
       <c r="D6" t="n">
-        <v>35.46932221284843</v>
+        <v>35.46932221284625</v>
       </c>
       <c r="E6" t="n">
-        <v>29.74771057604357</v>
+        <v>29.74771057604369</v>
       </c>
       <c r="F6" t="n">
-        <v>21.57345869909703</v>
+        <v>21.57345869909707</v>
       </c>
       <c r="G6" t="n">
-        <v>33.02100836001343</v>
+        <v>33.02100836001332</v>
       </c>
       <c r="H6" t="n">
-        <v>33.02898797240511</v>
+        <v>33.02898797240349</v>
       </c>
       <c r="I6" t="n">
-        <v>32.98049832241026</v>
+        <v>32.98049832241033</v>
       </c>
       <c r="J6" t="n">
-        <v>33.03130084873572</v>
+        <v>33.03130084873415</v>
       </c>
       <c r="K6" t="n">
-        <v>21.04159172420623</v>
+        <v>21.04159172420487</v>
       </c>
       <c r="L6" t="n">
-        <v>45.32246799690002</v>
+        <v>45.32246799689879</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>487.6069073942285</v>
+        <v>487.6069073942272</v>
       </c>
       <c r="C7" t="n">
-        <v>621.6513653629526</v>
+        <v>621.6513653629528</v>
       </c>
       <c r="D7" t="n">
         <v>621.6998615665982</v>
       </c>
       <c r="E7" t="n">
-        <v>776.3917890712539</v>
+        <v>776.3917890712544</v>
       </c>
       <c r="F7" t="n">
-        <v>621.6513649323338</v>
+        <v>621.651364932334</v>
       </c>
       <c r="G7" t="n">
-        <v>621.6918754005562</v>
+        <v>621.6918754005553</v>
       </c>
       <c r="H7" t="n">
-        <v>621.6998550130395</v>
+        <v>621.6998550130384</v>
       </c>
       <c r="I7" t="n">
-        <v>621.6513653629526</v>
+        <v>621.6513653629528</v>
       </c>
       <c r="J7" t="n">
-        <v>621.6998550130395</v>
+        <v>621.6998550130384</v>
       </c>
       <c r="K7" t="n">
-        <v>452.8528967559308</v>
+        <v>544.0058772954446</v>
       </c>
       <c r="L7" t="n">
-        <v>621.6998550130395</v>
+        <v>621.6998550130384</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.495128703057096</v>
+        <v>7.495128703056322</v>
       </c>
       <c r="C8" t="n">
-        <v>5.672568282100057</v>
+        <v>5.672568282100062</v>
       </c>
       <c r="D8" t="n">
-        <v>6.971800013538869</v>
+        <v>6.97180001353817</v>
       </c>
       <c r="E8" t="n">
-        <v>5.672568282100057</v>
+        <v>5.672568282100062</v>
       </c>
       <c r="F8" t="n">
-        <v>5.672568282100057</v>
+        <v>5.672568282100062</v>
       </c>
       <c r="G8" t="n">
-        <v>5.002558398819937</v>
+        <v>5.002558398819319</v>
       </c>
       <c r="H8" t="n">
-        <v>6.771736329229259</v>
+        <v>6.771736329228554</v>
       </c>
       <c r="I8" t="n">
-        <v>5.672568282100057</v>
+        <v>5.672568282100062</v>
       </c>
       <c r="J8" t="n">
-        <v>7.228792573164104</v>
+        <v>7.228792573163087</v>
       </c>
       <c r="K8" t="n">
-        <v>7.12674860161687</v>
+        <v>7.126748601616161</v>
       </c>
       <c r="L8" t="n">
-        <v>7.435156220419646</v>
+        <v>7.905840437000993</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.975203657540685</v>
+        <v>7.975203657539412</v>
       </c>
       <c r="C9" t="n">
-        <v>6.237681628297042</v>
+        <v>6.237681628297032</v>
       </c>
       <c r="D9" t="n">
-        <v>7.762095088378488</v>
+        <v>7.762095088377848</v>
       </c>
       <c r="E9" t="n">
-        <v>6.237681628297042</v>
+        <v>6.237681628297038</v>
       </c>
       <c r="F9" t="n">
-        <v>6.237681628297042</v>
+        <v>6.237681628297038</v>
       </c>
       <c r="G9" t="n">
-        <v>6.930121428039207</v>
+        <v>6.93012142803885</v>
       </c>
       <c r="H9" t="n">
-        <v>7.682155182152109</v>
+        <v>7.682155182151109</v>
       </c>
       <c r="I9" t="n">
-        <v>6.237681628297042</v>
+        <v>6.237681628297038</v>
       </c>
       <c r="J9" t="n">
-        <v>7.867201637021574</v>
+        <v>7.86720163702072</v>
       </c>
       <c r="K9" t="n">
-        <v>7.825236071022007</v>
+        <v>7.825236071021012</v>
       </c>
       <c r="L9" t="n">
-        <v>8.142907880726739</v>
+        <v>7.951563851405262</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>231.510165273946</v>
+        <v>231.5101652739464</v>
       </c>
       <c r="C2" t="n">
-        <v>87.4175744020788</v>
+        <v>87.41757440207873</v>
       </c>
       <c r="D2" t="n">
-        <v>55.16575557223441</v>
+        <v>55.16575557223457</v>
       </c>
       <c r="E2" t="n">
-        <v>87.4175744020788</v>
+        <v>87.41757440207873</v>
       </c>
       <c r="F2" t="n">
-        <v>87.4175744020788</v>
+        <v>87.41757440207873</v>
       </c>
       <c r="G2" t="n">
-        <v>247.3037775309826</v>
+        <v>247.3037775309811</v>
       </c>
       <c r="H2" t="n">
-        <v>56.02718066988614</v>
+        <v>56.0271806698865</v>
       </c>
       <c r="I2" t="n">
-        <v>87.4175744020788</v>
+        <v>87.41757440207873</v>
       </c>
       <c r="J2" t="n">
-        <v>118.1915852780213</v>
+        <v>118.1915852780216</v>
       </c>
       <c r="K2" t="n">
-        <v>159.0695287577474</v>
+        <v>159.0695287577484</v>
       </c>
       <c r="L2" t="n">
-        <v>30.70517475789127</v>
+        <v>30.70517475789049</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.527053539215186</v>
+        <v>6.527053539215672</v>
       </c>
       <c r="C3" t="n">
-        <v>5.131450523920043</v>
+        <v>5.131450523920031</v>
       </c>
       <c r="D3" t="n">
-        <v>6.527053539215186</v>
+        <v>6.527053539215672</v>
       </c>
       <c r="E3" t="n">
-        <v>5.570831960213119</v>
+        <v>5.570831960213112</v>
       </c>
       <c r="F3" t="n">
-        <v>5.570831960213119</v>
+        <v>5.570831960213118</v>
       </c>
       <c r="G3" t="n">
-        <v>6.515473697159032</v>
+        <v>6.51547369715819</v>
       </c>
       <c r="H3" t="n">
-        <v>6.527053539215186</v>
+        <v>6.527053539215672</v>
       </c>
       <c r="I3" t="n">
-        <v>6.456475243655865</v>
+        <v>6.456475243655871</v>
       </c>
       <c r="J3" t="n">
-        <v>6.527053539215187</v>
+        <v>6.527053539215672</v>
       </c>
       <c r="K3" t="n">
-        <v>6.527053539215186</v>
+        <v>6.527053539215672</v>
       </c>
       <c r="L3" t="n">
-        <v>6.527053539215186</v>
+        <v>6.527053539215672</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.12585666716995</v>
+        <v>25.20602649650897</v>
       </c>
       <c r="C4" t="n">
-        <v>10.45828496754241</v>
+        <v>10.45828496754243</v>
       </c>
       <c r="D4" t="n">
-        <v>10.90708583782773</v>
+        <v>10.90705304073069</v>
       </c>
       <c r="E4" t="n">
-        <v>10.07420664619256</v>
+        <v>10.07420664619254</v>
       </c>
       <c r="F4" t="n">
         <v>10.88842536207585</v>
       </c>
       <c r="G4" t="n">
-        <v>11.11427682511296</v>
+        <v>11.11427682511332</v>
       </c>
       <c r="H4" t="n">
-        <v>28.73328845144093</v>
+        <v>11.00507153029235</v>
       </c>
       <c r="I4" t="n">
-        <v>11.0552783716101</v>
+        <v>11.05527837161009</v>
       </c>
       <c r="J4" t="n">
-        <v>11.29551329388972</v>
+        <v>25.85963651055261</v>
       </c>
       <c r="K4" t="n">
-        <v>11.00879405759869</v>
+        <v>11.00879405759967</v>
       </c>
       <c r="L4" t="n">
-        <v>10.89544283505693</v>
+        <v>10.89544283505656</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.84156157433468</v>
+        <v>11.84156157433505</v>
       </c>
       <c r="C5" t="n">
-        <v>11.77098327877529</v>
+        <v>11.77098327877528</v>
       </c>
       <c r="D5" t="n">
-        <v>11.84158394529513</v>
+        <v>11.84158394529478</v>
       </c>
       <c r="E5" t="n">
-        <v>11.65577740227976</v>
+        <v>11.65577740227975</v>
       </c>
       <c r="F5" t="n">
-        <v>11.65577740227976</v>
+        <v>11.65577740227975</v>
       </c>
       <c r="G5" t="n">
-        <v>11.82998173227806</v>
+        <v>11.82998173227842</v>
       </c>
       <c r="H5" t="n">
-        <v>11.84156157433468</v>
+        <v>11.84156157433505</v>
       </c>
       <c r="I5" t="n">
-        <v>11.77098327877529</v>
+        <v>11.77098327877528</v>
       </c>
       <c r="J5" t="n">
-        <v>11.84156157433468</v>
+        <v>11.84156157433505</v>
       </c>
       <c r="K5" t="n">
-        <v>11.84156157433468</v>
+        <v>11.84156157433505</v>
       </c>
       <c r="L5" t="n">
-        <v>11.84156157433468</v>
+        <v>11.84156157433505</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.4700744879027</v>
+        <v>23.47007448790363</v>
       </c>
       <c r="C6" t="n">
-        <v>36.14462884509643</v>
+        <v>36.14462884509641</v>
       </c>
       <c r="D6" t="n">
-        <v>38.98794865250851</v>
+        <v>38.98794865250842</v>
       </c>
       <c r="E6" t="n">
-        <v>32.6409152219896</v>
+        <v>32.64091522198959</v>
       </c>
       <c r="F6" t="n">
-        <v>23.73816990109684</v>
+        <v>23.73816990109681</v>
       </c>
       <c r="G6" t="n">
-        <v>36.31126346973353</v>
+        <v>36.31126346973355</v>
       </c>
       <c r="H6" t="n">
-        <v>36.32284331179503</v>
+        <v>36.32284331179542</v>
       </c>
       <c r="I6" t="n">
-        <v>36.25226501623053</v>
+        <v>36.25226501623055</v>
       </c>
       <c r="J6" t="n">
-        <v>36.32536920618713</v>
+        <v>36.3253692061872</v>
       </c>
       <c r="K6" t="n">
-        <v>23.23132771252019</v>
+        <v>23.23132771252045</v>
       </c>
       <c r="L6" t="n">
-        <v>49.74863503836971</v>
+        <v>49.74863503836988</v>
       </c>
     </row>
     <row r="7">
@@ -6655,34 +6655,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>458.4184264608908</v>
+        <v>458.4184264608904</v>
       </c>
       <c r="C7" t="n">
-        <v>584.2292253556885</v>
+        <v>584.2292253556883</v>
       </c>
       <c r="D7" t="n">
-        <v>584.2998146574791</v>
+        <v>584.2998146574786</v>
       </c>
       <c r="E7" t="n">
-        <v>729.4936758010336</v>
+        <v>729.4936758010335</v>
       </c>
       <c r="F7" t="n">
-        <v>584.2292256234188</v>
+        <v>584.2292256234185</v>
       </c>
       <c r="G7" t="n">
-        <v>584.288223809191</v>
+        <v>584.2882238091906</v>
       </c>
       <c r="H7" t="n">
         <v>584.299803651248</v>
       </c>
       <c r="I7" t="n">
-        <v>584.2292253556885</v>
+        <v>584.2292253556883</v>
       </c>
       <c r="J7" t="n">
         <v>584.299803651248</v>
       </c>
       <c r="K7" t="n">
-        <v>508.4045313847149</v>
+        <v>508.4045313847145</v>
       </c>
       <c r="L7" t="n">
         <v>584.299803651248</v>
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.940443211512427</v>
+        <v>4.940443211512336</v>
       </c>
       <c r="C8" t="n">
-        <v>6.809828275659423</v>
+        <v>6.809828275659419</v>
       </c>
       <c r="D8" t="n">
-        <v>9.340172233102477</v>
+        <v>9.340172233102711</v>
       </c>
       <c r="E8" t="n">
-        <v>6.809828275659423</v>
+        <v>6.809828275659419</v>
       </c>
       <c r="F8" t="n">
-        <v>6.809828275659423</v>
+        <v>6.809828275659419</v>
       </c>
       <c r="G8" t="n">
-        <v>4.186190142905998</v>
+        <v>4.186190142906122</v>
       </c>
       <c r="H8" t="n">
-        <v>9.445308652639129</v>
+        <v>9.445308652639257</v>
       </c>
       <c r="I8" t="n">
-        <v>6.809828275659423</v>
+        <v>6.809828275659419</v>
       </c>
       <c r="J8" t="n">
-        <v>7.901961291570117</v>
+        <v>7.901961291570364</v>
       </c>
       <c r="K8" t="n">
-        <v>6.563621700755016</v>
+        <v>6.563621700755103</v>
       </c>
       <c r="L8" t="n">
-        <v>9.433455168185699</v>
+        <v>9.433455168185882</v>
       </c>
     </row>
     <row r="9">
@@ -6735,13 +6735,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.196336276371831</v>
+        <v>8.196336276371575</v>
       </c>
       <c r="C9" t="n">
         <v>7.978302871857112</v>
       </c>
       <c r="D9" t="n">
-        <v>9.988352705453144</v>
+        <v>9.988352705453185</v>
       </c>
       <c r="E9" t="n">
         <v>7.978302871857112</v>
@@ -6750,22 +6750,22 @@
         <v>7.978302871857112</v>
       </c>
       <c r="G9" t="n">
-        <v>7.849936372804051</v>
+        <v>7.849936372803747</v>
       </c>
       <c r="H9" t="n">
-        <v>10.0322599267371</v>
+        <v>10.03225992673711</v>
       </c>
       <c r="I9" t="n">
         <v>7.978302871857112</v>
       </c>
       <c r="J9" t="n">
-        <v>9.403591810536033</v>
+        <v>9.403591810536215</v>
       </c>
       <c r="K9" t="n">
-        <v>8.857662727463122</v>
+        <v>8.857662727462998</v>
       </c>
       <c r="L9" t="n">
-        <v>10.30257856482969</v>
+        <v>10.02723203013072</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>353.1250766432689</v>
+        <v>353.1250766432685</v>
       </c>
       <c r="C2" t="n">
-        <v>103.5585183171749</v>
+        <v>103.5585183171752</v>
       </c>
       <c r="D2" t="n">
-        <v>71.31397105701062</v>
+        <v>71.31397105701214</v>
       </c>
       <c r="E2" t="n">
-        <v>103.5585183171749</v>
+        <v>103.5585183171752</v>
       </c>
       <c r="F2" t="n">
-        <v>103.5585183171749</v>
+        <v>103.5585183171752</v>
       </c>
       <c r="G2" t="n">
-        <v>257.0163548765331</v>
+        <v>257.016354876535</v>
       </c>
       <c r="H2" t="n">
-        <v>47.80236643588302</v>
+        <v>47.80236643588527</v>
       </c>
       <c r="I2" t="n">
-        <v>103.5585183171749</v>
+        <v>103.5585183171752</v>
       </c>
       <c r="J2" t="n">
-        <v>142.4190941573846</v>
+        <v>142.419094157384</v>
       </c>
       <c r="K2" t="n">
-        <v>150.341555772543</v>
+        <v>150.3415557725446</v>
       </c>
       <c r="L2" t="n">
-        <v>143.2177925073601</v>
+        <v>85.17001660332149</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.200111922469699</v>
+        <v>7.200111922469721</v>
       </c>
       <c r="C3" t="n">
-        <v>5.596961317789382</v>
+        <v>5.596961317789379</v>
       </c>
       <c r="D3" t="n">
-        <v>7.200111922469699</v>
+        <v>7.200111922469726</v>
       </c>
       <c r="E3" t="n">
-        <v>6.087669303524355</v>
+        <v>6.087669303524383</v>
       </c>
       <c r="F3" t="n">
-        <v>6.087669303524355</v>
+        <v>6.087669303524382</v>
       </c>
       <c r="G3" t="n">
-        <v>7.188951099651916</v>
+        <v>7.188951099652971</v>
       </c>
       <c r="H3" t="n">
-        <v>7.200111922469699</v>
+        <v>7.200111922469721</v>
       </c>
       <c r="I3" t="n">
-        <v>7.132510257447812</v>
+        <v>7.132510257447915</v>
       </c>
       <c r="J3" t="n">
-        <v>7.200111922469699</v>
+        <v>7.20011192246972</v>
       </c>
       <c r="K3" t="n">
-        <v>7.200111922469699</v>
+        <v>7.20011192246972</v>
       </c>
       <c r="L3" t="n">
-        <v>7.200111922469699</v>
+        <v>7.200111922469721</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.17618176935798</v>
+        <v>12.17618176935785</v>
       </c>
       <c r="C4" t="n">
-        <v>11.50518762462364</v>
+        <v>11.50518762462368</v>
       </c>
       <c r="D4" t="n">
-        <v>27.51379599979619</v>
+        <v>11.93814682918101</v>
       </c>
       <c r="E4" t="n">
-        <v>11.06139010106305</v>
+        <v>11.06139010106316</v>
       </c>
       <c r="F4" t="n">
-        <v>11.94539942488759</v>
+        <v>11.94539942488761</v>
       </c>
       <c r="G4" t="n">
-        <v>12.16502094653953</v>
+        <v>26.68087134774396</v>
       </c>
       <c r="H4" t="n">
-        <v>30.59450546591831</v>
+        <v>30.5945054659198</v>
       </c>
       <c r="I4" t="n">
-        <v>12.10858010433549</v>
+        <v>12.10858010433555</v>
       </c>
       <c r="J4" t="n">
-        <v>12.38648813730569</v>
+        <v>27.44253062538152</v>
       </c>
       <c r="K4" t="n">
-        <v>12.03976863327994</v>
+        <v>12.03976863327969</v>
       </c>
       <c r="L4" t="n">
-        <v>11.94866119583246</v>
+        <v>11.94866119583271</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12.68378915754634</v>
+        <v>12.68378915754763</v>
       </c>
       <c r="C5" t="n">
-        <v>12.61618749252555</v>
+        <v>12.61618749252559</v>
       </c>
       <c r="D5" t="n">
-        <v>12.68383983868407</v>
+        <v>12.68383983868521</v>
       </c>
       <c r="E5" t="n">
-        <v>12.45248430649478</v>
+        <v>12.45248430649482</v>
       </c>
       <c r="F5" t="n">
-        <v>12.45248430649478</v>
+        <v>12.45248430649482</v>
       </c>
       <c r="G5" t="n">
-        <v>12.67262833473059</v>
+        <v>12.67262833473096</v>
       </c>
       <c r="H5" t="n">
-        <v>12.68378915754634</v>
+        <v>12.68378915754763</v>
       </c>
       <c r="I5" t="n">
-        <v>12.61618749252555</v>
+        <v>12.61618749252559</v>
       </c>
       <c r="J5" t="n">
-        <v>12.68378915754634</v>
+        <v>12.68378915754763</v>
       </c>
       <c r="K5" t="n">
-        <v>12.68378915754634</v>
+        <v>12.68378915754763</v>
       </c>
       <c r="L5" t="n">
-        <v>12.68378915754634</v>
+        <v>12.68378915754763</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24.63954930678728</v>
+        <v>24.63954930678725</v>
       </c>
       <c r="C6" t="n">
-        <v>37.88972480300597</v>
+        <v>37.88972480344643</v>
       </c>
       <c r="D6" t="n">
-        <v>40.9047045408885</v>
+        <v>40.90470454088967</v>
       </c>
       <c r="E6" t="n">
-        <v>34.2216624309722</v>
+        <v>34.22166243097233</v>
       </c>
       <c r="F6" t="n">
-        <v>24.9012929056293</v>
+        <v>24.90129290562943</v>
       </c>
       <c r="G6" t="n">
-        <v>38.10009716635183</v>
+        <v>38.10009716635211</v>
       </c>
       <c r="H6" t="n">
-        <v>38.11125798923493</v>
+        <v>38.11125798923653</v>
       </c>
       <c r="I6" t="n">
-        <v>38.04365632414644</v>
+        <v>38.04365632414662</v>
       </c>
       <c r="J6" t="n">
-        <v>38.11390551492312</v>
+        <v>38.11390551492268</v>
       </c>
       <c r="K6" t="n">
-        <v>24.38930540653481</v>
+        <v>24.38930540653382</v>
       </c>
       <c r="L6" t="n">
-        <v>52.18358414517896</v>
+        <v>52.18358414517883</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>458.3400539981808</v>
+        <v>458.3400539981818</v>
       </c>
       <c r="C7" t="n">
         <v>584.0781263394352</v>
       </c>
       <c r="D7" t="n">
-        <v>584.1457394683808</v>
+        <v>584.1457394683806</v>
       </c>
       <c r="E7" t="n">
-        <v>729.255217640791</v>
+        <v>729.2552176407908</v>
       </c>
       <c r="F7" t="n">
-        <v>584.0781268563875</v>
+        <v>584.0781268563876</v>
       </c>
       <c r="G7" t="n">
-        <v>584.1345671816401</v>
+        <v>584.1345671816399</v>
       </c>
       <c r="H7" t="n">
-        <v>584.1457280044584</v>
+        <v>584.1457280044591</v>
       </c>
       <c r="I7" t="n">
         <v>584.0781263394352</v>
       </c>
       <c r="J7" t="n">
-        <v>584.1457280044584</v>
+        <v>584.1457280044591</v>
       </c>
       <c r="K7" t="n">
-        <v>511.2534312298811</v>
+        <v>508.2960982078808</v>
       </c>
       <c r="L7" t="n">
-        <v>584.1457280044584</v>
+        <v>584.1457280044591</v>
       </c>
     </row>
     <row r="8">
@@ -7091,34 +7091,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.535884788532251</v>
+        <v>2.535884788531666</v>
       </c>
       <c r="C8" t="n">
-        <v>7.335743361370169</v>
+        <v>7.335743361370179</v>
       </c>
       <c r="D8" t="n">
-        <v>9.733643957490319</v>
+        <v>9.733643957490887</v>
       </c>
       <c r="E8" t="n">
-        <v>7.335743361370169</v>
+        <v>7.335743361370179</v>
       </c>
       <c r="F8" t="n">
-        <v>7.335743361370169</v>
+        <v>7.335743361370179</v>
       </c>
       <c r="G8" t="n">
-        <v>4.916961329049803</v>
+        <v>4.916961329049859</v>
       </c>
       <c r="H8" t="n">
-        <v>10.49730003634657</v>
+        <v>10.49730003634732</v>
       </c>
       <c r="I8" t="n">
-        <v>7.335743361370169</v>
+        <v>7.335743361370179</v>
       </c>
       <c r="J8" t="n">
-        <v>8.14125460735349</v>
+        <v>8.1412546073536</v>
       </c>
       <c r="K8" t="n">
-        <v>7.498683716809022</v>
+        <v>7.498683716809296</v>
       </c>
       <c r="L8" t="n">
         <v>8.247337329027207</v>
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.666292820009438</v>
+        <v>7.666292820010183</v>
       </c>
       <c r="C9" t="n">
-        <v>8.712496799013607</v>
+        <v>8.712496799013685</v>
       </c>
       <c r="D9" t="n">
-        <v>10.59793929080389</v>
+        <v>10.59793929080372</v>
       </c>
       <c r="E9" t="n">
-        <v>8.712496799013607</v>
+        <v>8.712496799013685</v>
       </c>
       <c r="F9" t="n">
-        <v>8.712496799013607</v>
+        <v>8.712496799013685</v>
       </c>
       <c r="G9" t="n">
-        <v>8.597709336930954</v>
+        <v>8.597709336931162</v>
       </c>
       <c r="H9" t="n">
-        <v>10.90978994795068</v>
+        <v>10.90978994795194</v>
       </c>
       <c r="I9" t="n">
-        <v>8.712496799013607</v>
+        <v>8.712496799013685</v>
       </c>
       <c r="J9" t="n">
-        <v>9.950576998347097</v>
+        <v>9.950576998347598</v>
       </c>
       <c r="K9" t="n">
-        <v>9.687817020777027</v>
+        <v>9.687817020777196</v>
       </c>
       <c r="L9" t="n">
-        <v>9.994902698143406</v>
+        <v>10.59374103736669</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>55.11850663443088</v>
+        <v>55.11850663443095</v>
       </c>
       <c r="C2" t="n">
-        <v>47.5211031524077</v>
+        <v>47.52110315240783</v>
       </c>
       <c r="D2" t="n">
-        <v>135.5845222181583</v>
+        <v>135.5845222181586</v>
       </c>
       <c r="E2" t="n">
-        <v>47.5211031524077</v>
+        <v>47.52110315240783</v>
       </c>
       <c r="F2" t="n">
-        <v>47.5211031524077</v>
+        <v>47.52110315240783</v>
       </c>
       <c r="G2" t="n">
-        <v>145.4315111976248</v>
+        <v>145.4315111976243</v>
       </c>
       <c r="H2" t="n">
-        <v>182.2454813402723</v>
+        <v>182.2454813402733</v>
       </c>
       <c r="I2" t="n">
-        <v>47.5211031524077</v>
+        <v>47.52110315240783</v>
       </c>
       <c r="J2" t="n">
-        <v>46.38882627140798</v>
+        <v>46.38882627140836</v>
       </c>
       <c r="K2" t="n">
-        <v>37.58549115429059</v>
+        <v>37.58549115429088</v>
       </c>
       <c r="L2" t="n">
-        <v>132.6711302371757</v>
+        <v>132.6711302371762</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.615892744052426</v>
+        <v>3.615892744052436</v>
       </c>
       <c r="C3" t="n">
-        <v>2.503199848189032</v>
+        <v>2.503199848189114</v>
       </c>
       <c r="D3" t="n">
-        <v>3.615892744052426</v>
+        <v>3.615892744052435</v>
       </c>
       <c r="E3" t="n">
-        <v>2.803706323996871</v>
+        <v>2.803706323996928</v>
       </c>
       <c r="F3" t="n">
-        <v>2.803706323996877</v>
+        <v>2.803706323996928</v>
       </c>
       <c r="G3" t="n">
-        <v>3.608196334672458</v>
+        <v>3.60819633467261</v>
       </c>
       <c r="H3" t="n">
-        <v>3.615892744052426</v>
+        <v>3.615892744052435</v>
       </c>
       <c r="I3" t="n">
-        <v>3.569022746393578</v>
+        <v>3.56902274639363</v>
       </c>
       <c r="J3" t="n">
-        <v>3.615892744052418</v>
+        <v>3.615892744052435</v>
       </c>
       <c r="K3" t="n">
-        <v>3.615892744052426</v>
+        <v>3.615892744052435</v>
       </c>
       <c r="L3" t="n">
-        <v>3.615892744052426</v>
+        <v>3.615892744052435</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.176732952471639</v>
+        <v>6.176732952471752</v>
       </c>
       <c r="C4" t="n">
-        <v>5.817776921979457</v>
+        <v>5.817776921979518</v>
       </c>
       <c r="D4" t="n">
-        <v>6.560095184767415</v>
+        <v>6.56009518476773</v>
       </c>
       <c r="E4" t="n">
-        <v>5.690366776592563</v>
+        <v>5.690366776592637</v>
       </c>
       <c r="F4" t="n">
-        <v>6.079070619375567</v>
+        <v>6.079070619375659</v>
       </c>
       <c r="G4" t="n">
-        <v>18.19081369016779</v>
+        <v>18.19081369016832</v>
       </c>
       <c r="H4" t="n">
-        <v>21.71633272925256</v>
+        <v>21.71633272925278</v>
       </c>
       <c r="I4" t="n">
-        <v>6.12986295481276</v>
+        <v>18.15164010188948</v>
       </c>
       <c r="J4" t="n">
-        <v>18.94295365405412</v>
+        <v>18.94295365405434</v>
       </c>
       <c r="K4" t="n">
-        <v>5.870823008079432</v>
+        <v>5.87082300807955</v>
       </c>
       <c r="L4" t="n">
-        <v>6.141601069333406</v>
+        <v>6.141601069333574</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.912158121428619</v>
+        <v>7.912158121428772</v>
       </c>
       <c r="C5" t="n">
-        <v>7.865288123769717</v>
+        <v>7.865288123769924</v>
       </c>
       <c r="D5" t="n">
-        <v>7.912177967537891</v>
+        <v>7.912177967537997</v>
       </c>
       <c r="E5" t="n">
-        <v>7.773182036699223</v>
+        <v>7.773182036699269</v>
       </c>
       <c r="F5" t="n">
-        <v>7.773182036699223</v>
+        <v>7.773182036699269</v>
       </c>
       <c r="G5" t="n">
-        <v>7.904461712048628</v>
+        <v>7.904461712048801</v>
       </c>
       <c r="H5" t="n">
-        <v>7.912158121428619</v>
+        <v>7.912158121428772</v>
       </c>
       <c r="I5" t="n">
-        <v>7.865288123769717</v>
+        <v>7.865288123769924</v>
       </c>
       <c r="J5" t="n">
-        <v>7.912158121428619</v>
+        <v>7.912158121428772</v>
       </c>
       <c r="K5" t="n">
-        <v>7.912158121428619</v>
+        <v>7.912158121428772</v>
       </c>
       <c r="L5" t="n">
-        <v>7.912158121428619</v>
+        <v>7.912158121428772</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.40708350465294</v>
+        <v>18.40708350465323</v>
       </c>
       <c r="C6" t="n">
-        <v>28.6695033471617</v>
+        <v>28.66950334743765</v>
       </c>
       <c r="D6" t="n">
-        <v>30.95794957546781</v>
+        <v>30.95794957546824</v>
       </c>
       <c r="E6" t="n">
-        <v>25.83559409806152</v>
+        <v>25.83559409806187</v>
       </c>
       <c r="F6" t="n">
-        <v>18.63477174881735</v>
+        <v>18.6347717488177</v>
       </c>
       <c r="G6" t="n">
-        <v>28.7947143427779</v>
+        <v>28.79471434277832</v>
       </c>
       <c r="H6" t="n">
-        <v>28.80241075211027</v>
+        <v>28.80241075211054</v>
       </c>
       <c r="I6" t="n">
-        <v>28.75554075449874</v>
+        <v>28.75554075449945</v>
       </c>
       <c r="J6" t="n">
-        <v>28.80445371429723</v>
+        <v>28.80445371429793</v>
       </c>
       <c r="K6" t="n">
-        <v>18.21398496565112</v>
+        <v>18.21398496565149</v>
       </c>
       <c r="L6" t="n">
-        <v>39.66119928867382</v>
+        <v>39.6611992886749</v>
       </c>
     </row>
     <row r="7">
@@ -7450,34 +7450,34 @@
         <v>485.2720984862551</v>
       </c>
       <c r="C7" t="n">
-        <v>618.8637173729537</v>
+        <v>618.8637173729546</v>
       </c>
       <c r="D7" t="n">
-        <v>618.9105916846328</v>
+        <v>618.9105916846331</v>
       </c>
       <c r="E7" t="n">
-        <v>773.0797014043956</v>
+        <v>773.0797014043965</v>
       </c>
       <c r="F7" t="n">
-        <v>618.8637154152261</v>
+        <v>618.8637154152273</v>
       </c>
       <c r="G7" t="n">
-        <v>618.9028909612334</v>
+        <v>618.9028909612341</v>
       </c>
       <c r="H7" t="n">
-        <v>618.9105873706128</v>
+        <v>618.9105873706137</v>
       </c>
       <c r="I7" t="n">
-        <v>618.8637173729537</v>
+        <v>618.8637173729546</v>
       </c>
       <c r="J7" t="n">
-        <v>618.9105873706128</v>
+        <v>618.9105873706137</v>
       </c>
       <c r="K7" t="n">
-        <v>538.33846388448</v>
+        <v>541.4799238866181</v>
       </c>
       <c r="L7" t="n">
-        <v>618.9105873706128</v>
+        <v>618.9105873706137</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.955283793931155</v>
+        <v>5.95528379393119</v>
       </c>
       <c r="C8" t="n">
-        <v>4.384693260930744</v>
+        <v>4.384693260930777</v>
       </c>
       <c r="D8" t="n">
-        <v>3.991832153118858</v>
+        <v>3.991832153118916</v>
       </c>
       <c r="E8" t="n">
-        <v>4.384693260930744</v>
+        <v>4.384693260930777</v>
       </c>
       <c r="F8" t="n">
-        <v>4.384693260930744</v>
+        <v>4.384693260930777</v>
       </c>
       <c r="G8" t="n">
-        <v>3.833419086627646</v>
+        <v>3.833419086627694</v>
       </c>
       <c r="H8" t="n">
-        <v>3.225761073577147</v>
+        <v>3.225761073577202</v>
       </c>
       <c r="I8" t="n">
-        <v>4.384693260930744</v>
+        <v>4.384693260930777</v>
       </c>
       <c r="J8" t="n">
-        <v>6.247549386581284</v>
+        <v>6.247549386581339</v>
       </c>
       <c r="K8" t="n">
-        <v>6.381999137220586</v>
+        <v>6.381999137220627</v>
       </c>
       <c r="L8" t="n">
-        <v>6.767445808431434</v>
+        <v>4.636337470653844</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.575146893598792</v>
+        <v>6.575146893598881</v>
       </c>
       <c r="C9" t="n">
-        <v>4.928238034336275</v>
+        <v>4.928238034336339</v>
       </c>
       <c r="D9" t="n">
-        <v>5.775529121687986</v>
+        <v>5.775529121688073</v>
       </c>
       <c r="E9" t="n">
-        <v>4.928238034336275</v>
+        <v>4.928238034336339</v>
       </c>
       <c r="F9" t="n">
-        <v>4.928238034336275</v>
+        <v>4.928238034336339</v>
       </c>
       <c r="G9" t="n">
-        <v>5.682009830552604</v>
+        <v>5.682009830552652</v>
       </c>
       <c r="H9" t="n">
-        <v>5.467075321385284</v>
+        <v>5.467075321385337</v>
       </c>
       <c r="I9" t="n">
-        <v>4.928238034336275</v>
+        <v>4.928238034336339</v>
       </c>
       <c r="J9" t="n">
-        <v>6.694525904318545</v>
+        <v>6.694525904318579</v>
       </c>
       <c r="K9" t="n">
-        <v>6.748985547732195</v>
+        <v>6.748985547732262</v>
       </c>
       <c r="L9" t="n">
-        <v>6.906214604756225</v>
+        <v>6.039846013766793</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>119.7816842511189</v>
+        <v>119.7816842511191</v>
       </c>
       <c r="C2" t="n">
-        <v>55.62596229123778</v>
+        <v>55.62596229123791</v>
       </c>
       <c r="D2" t="n">
-        <v>115.2247438149565</v>
+        <v>115.2247438149604</v>
       </c>
       <c r="E2" t="n">
-        <v>55.62596229123784</v>
+        <v>55.62596229123791</v>
       </c>
       <c r="F2" t="n">
-        <v>55.62596229123784</v>
+        <v>55.62596229123791</v>
       </c>
       <c r="G2" t="n">
-        <v>217.7178155833859</v>
+        <v>217.7178155833867</v>
       </c>
       <c r="H2" t="n">
-        <v>76.50149902462344</v>
+        <v>76.50149902462358</v>
       </c>
       <c r="I2" t="n">
-        <v>55.62596229123778</v>
+        <v>55.62596229123791</v>
       </c>
       <c r="J2" t="n">
-        <v>102.8365770007658</v>
+        <v>102.836577000766</v>
       </c>
       <c r="K2" t="n">
-        <v>64.91947539560546</v>
+        <v>64.91947539560567</v>
       </c>
       <c r="L2" t="n">
-        <v>120.679289428769</v>
+        <v>77.77198216267152</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.301685135992733</v>
+        <v>5.301685135992912</v>
       </c>
       <c r="C3" t="n">
-        <v>3.996428468580286</v>
+        <v>3.996428468580294</v>
       </c>
       <c r="D3" t="n">
-        <v>5.301685135992733</v>
+        <v>5.301685135992912</v>
       </c>
       <c r="E3" t="n">
-        <v>4.373808858386819</v>
+        <v>4.373808858386899</v>
       </c>
       <c r="F3" t="n">
-        <v>4.373808858386818</v>
+        <v>4.373808858386894</v>
       </c>
       <c r="G3" t="n">
-        <v>5.290237369653632</v>
+        <v>5.290237369653593</v>
       </c>
       <c r="H3" t="n">
-        <v>5.301685135992733</v>
+        <v>5.301685135992912</v>
       </c>
       <c r="I3" t="n">
-        <v>5.231285642743364</v>
+        <v>5.231285642743446</v>
       </c>
       <c r="J3" t="n">
-        <v>5.301685135992733</v>
+        <v>5.301685135992912</v>
       </c>
       <c r="K3" t="n">
-        <v>5.301685135992733</v>
+        <v>5.301685135992912</v>
       </c>
       <c r="L3" t="n">
-        <v>5.301685135992732</v>
+        <v>5.301685135992911</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.799047724144247</v>
+        <v>21.84153302426971</v>
       </c>
       <c r="C4" t="n">
-        <v>8.245863954145943</v>
+        <v>8.24586395414577</v>
       </c>
       <c r="D4" t="n">
-        <v>8.91421912686649</v>
+        <v>8.914219126866012</v>
       </c>
       <c r="E4" t="n">
-        <v>7.983782356324995</v>
+        <v>7.983782356324939</v>
       </c>
       <c r="F4" t="n">
-        <v>8.629669316780555</v>
+        <v>8.629669316780557</v>
       </c>
       <c r="G4" t="n">
-        <v>21.83008525793088</v>
+        <v>8.787599957805039</v>
       </c>
       <c r="H4" t="n">
-        <v>24.84254493037105</v>
+        <v>24.84254493037103</v>
       </c>
       <c r="I4" t="n">
-        <v>21.77113353102062</v>
+        <v>21.77113353102034</v>
       </c>
       <c r="J4" t="n">
-        <v>22.46087291751847</v>
+        <v>8.975385917660645</v>
       </c>
       <c r="K4" t="n">
-        <v>8.453478495561649</v>
+        <v>8.453478495561873</v>
       </c>
       <c r="L4" t="n">
-        <v>8.68483743723897</v>
+        <v>8.684837437238894</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.07380462083999</v>
+        <v>10.07380462083996</v>
       </c>
       <c r="C5" t="n">
-        <v>10.00340512759045</v>
+        <v>10.00340512759069</v>
       </c>
       <c r="D5" t="n">
-        <v>10.07382018994698</v>
+        <v>10.07382018994673</v>
       </c>
       <c r="E5" t="n">
-        <v>9.892331104000474</v>
+        <v>9.892331104000743</v>
       </c>
       <c r="F5" t="n">
-        <v>9.892331104000474</v>
+        <v>9.892331104000744</v>
       </c>
       <c r="G5" t="n">
-        <v>10.06235685450077</v>
+        <v>10.06235685450082</v>
       </c>
       <c r="H5" t="n">
-        <v>10.07380462083999</v>
+        <v>10.07380462083996</v>
       </c>
       <c r="I5" t="n">
-        <v>10.00340512759045</v>
+        <v>10.00340512759069</v>
       </c>
       <c r="J5" t="n">
-        <v>10.07380462083999</v>
+        <v>10.07380462083996</v>
       </c>
       <c r="K5" t="n">
-        <v>10.07380462083999</v>
+        <v>10.07380462083996</v>
       </c>
       <c r="L5" t="n">
-        <v>10.07380462083999</v>
+        <v>10.07380462083996</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.00746549867197</v>
+        <v>21.00746549867201</v>
       </c>
       <c r="C6" t="n">
-        <v>32.4695854888061</v>
+        <v>32.46958548915371</v>
       </c>
       <c r="D6" t="n">
-        <v>35.05680416334459</v>
+        <v>35.05680416334447</v>
       </c>
       <c r="E6" t="n">
-        <v>29.29813907418252</v>
+        <v>29.29813907418257</v>
       </c>
       <c r="F6" t="n">
         <v>21.23965305601324</v>
       </c>
       <c r="G6" t="n">
-        <v>32.632463553726</v>
+        <v>32.63246355372589</v>
       </c>
       <c r="H6" t="n">
-        <v>32.6439113199727</v>
+        <v>32.64391131997284</v>
       </c>
       <c r="I6" t="n">
-        <v>32.57351182681592</v>
+        <v>32.57351182681586</v>
       </c>
       <c r="J6" t="n">
         <v>32.64619818144276</v>
       </c>
       <c r="K6" t="n">
-        <v>20.79131254658932</v>
+        <v>20.79131254658944</v>
       </c>
       <c r="L6" t="n">
-        <v>44.79915197214687</v>
+        <v>44.79915197214698</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>455.7472849511627</v>
+        <v>455.7472849511624</v>
       </c>
       <c r="C7" t="n">
-        <v>580.9711849382921</v>
+        <v>580.971184938292</v>
       </c>
       <c r="D7" t="n">
-        <v>581.0415935078724</v>
+        <v>581.0415935078729</v>
       </c>
       <c r="E7" t="n">
-        <v>725.5581576381103</v>
+        <v>725.5581576381105</v>
       </c>
       <c r="F7" t="n">
-        <v>580.9711845886781</v>
+        <v>580.9711845886782</v>
       </c>
       <c r="G7" t="n">
-        <v>581.0301366652021</v>
+        <v>581.0301366652022</v>
       </c>
       <c r="H7" t="n">
-        <v>581.041584431542</v>
+        <v>581.0415844315421</v>
       </c>
       <c r="I7" t="n">
-        <v>580.9711849382921</v>
+        <v>580.971184938292</v>
       </c>
       <c r="J7" t="n">
-        <v>581.041584431542</v>
+        <v>581.0415844315421</v>
       </c>
       <c r="K7" t="n">
-        <v>508.4455790613813</v>
+        <v>423.273694080008</v>
       </c>
       <c r="L7" t="n">
-        <v>581.041584431542</v>
+        <v>581.0415844315421</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.426747696240467</v>
+        <v>6.426747696240468</v>
       </c>
       <c r="C8" t="n">
-        <v>6.282837230427121</v>
+        <v>6.28283723042713</v>
       </c>
       <c r="D8" t="n">
-        <v>6.37224369790736</v>
+        <v>6.37224369790731</v>
       </c>
       <c r="E8" t="n">
-        <v>6.282837230427121</v>
+        <v>6.28283723042713</v>
       </c>
       <c r="F8" t="n">
-        <v>6.282837230427121</v>
+        <v>6.28283723042713</v>
       </c>
       <c r="G8" t="n">
-        <v>3.790258467401268</v>
+        <v>3.790258467401258</v>
       </c>
       <c r="H8" t="n">
-        <v>7.636332872700134</v>
+        <v>7.63633287270012</v>
       </c>
       <c r="I8" t="n">
-        <v>6.282837230427121</v>
+        <v>6.28283723042713</v>
       </c>
       <c r="J8" t="n">
-        <v>7.05499531561743</v>
+        <v>7.054995315617448</v>
       </c>
       <c r="K8" t="n">
-        <v>7.752411931394373</v>
+        <v>7.752411931394383</v>
       </c>
       <c r="L8" t="n">
-        <v>7.677069937050816</v>
+        <v>6.836114928959422</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.025453125142738</v>
+        <v>8.025453125142715</v>
       </c>
       <c r="C9" t="n">
-        <v>6.964832388237128</v>
+        <v>6.96483238823713</v>
       </c>
       <c r="D9" t="n">
-        <v>8.003331996849791</v>
+        <v>8.003331996849763</v>
       </c>
       <c r="E9" t="n">
-        <v>6.964832388237128</v>
+        <v>6.96483238823713</v>
       </c>
       <c r="F9" t="n">
-        <v>6.964832388237128</v>
+        <v>6.96483238823713</v>
       </c>
       <c r="G9" t="n">
-        <v>6.91375738098631</v>
+        <v>6.913757380986312</v>
       </c>
       <c r="H9" t="n">
-        <v>8.519668473497877</v>
+        <v>8.519668473497896</v>
       </c>
       <c r="I9" t="n">
-        <v>6.964832388237128</v>
+        <v>6.96483238823713</v>
       </c>
       <c r="J9" t="n">
-        <v>8.282195051881848</v>
+        <v>8.282195051881841</v>
       </c>
       <c r="K9" t="n">
-        <v>8.565470217448802</v>
+        <v>8.565470217448809</v>
       </c>
       <c r="L9" t="n">
-        <v>8.535920921506438</v>
+        <v>8.194060231633237</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Hydrogen/hydrogen land use results.xlsx
+++ b/Results/Hydrogen/hydrogen land use results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28.51959972144363</v>
+        <v>28.51959972144453</v>
       </c>
       <c r="C2" t="n">
-        <v>55.07466720368068</v>
+        <v>55.07466720368004</v>
       </c>
       <c r="D2" t="n">
-        <v>118.283365709883</v>
+        <v>118.2833657098831</v>
       </c>
       <c r="E2" t="n">
-        <v>55.07466720368068</v>
+        <v>55.07466720368004</v>
       </c>
       <c r="F2" t="n">
-        <v>55.07466720368068</v>
+        <v>55.07466720368004</v>
       </c>
       <c r="G2" t="n">
-        <v>90.55606635355741</v>
+        <v>90.55606635355807</v>
       </c>
       <c r="H2" t="n">
-        <v>181.4559123346697</v>
+        <v>181.4559123346686</v>
       </c>
       <c r="I2" t="n">
-        <v>55.07466720368068</v>
+        <v>55.07466720368004</v>
       </c>
       <c r="J2" t="n">
-        <v>49.53480942920022</v>
+        <v>49.53480942920193</v>
       </c>
       <c r="K2" t="n">
-        <v>34.78862090000982</v>
+        <v>34.78862090000865</v>
       </c>
       <c r="L2" t="n">
-        <v>13.02146820476462</v>
+        <v>159.4345329922353</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.984255050875503</v>
+        <v>1.984255050875196</v>
       </c>
       <c r="C3" t="n">
-        <v>1.173858341730922</v>
+        <v>1.173858341730902</v>
       </c>
       <c r="D3" t="n">
-        <v>1.984255050875503</v>
+        <v>1.984255050875196</v>
       </c>
       <c r="E3" t="n">
-        <v>1.376556343150911</v>
+        <v>1.37655634315087</v>
       </c>
       <c r="F3" t="n">
-        <v>1.376556343150879</v>
+        <v>1.376556343150871</v>
       </c>
       <c r="G3" t="n">
-        <v>1.979733000758681</v>
+        <v>1.97973300075894</v>
       </c>
       <c r="H3" t="n">
-        <v>1.984255050875503</v>
+        <v>1.984255050875196</v>
       </c>
       <c r="I3" t="n">
-        <v>1.95701330145055</v>
+        <v>1.95701330145049</v>
       </c>
       <c r="J3" t="n">
-        <v>1.984255050875503</v>
+        <v>1.984255050875196</v>
       </c>
       <c r="K3" t="n">
-        <v>1.984255050875503</v>
+        <v>1.984255050875197</v>
       </c>
       <c r="L3" t="n">
-        <v>1.984255050875503</v>
+        <v>1.984255050875196</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.090424665668298</v>
+        <v>4.09042466566776</v>
       </c>
       <c r="C4" t="n">
-        <v>3.932677319261733</v>
+        <v>3.932677319261728</v>
       </c>
       <c r="D4" t="n">
-        <v>4.175298528824691</v>
+        <v>4.175318037160461</v>
       </c>
       <c r="E4" t="n">
-        <v>3.898883751007163</v>
+        <v>3.898883751007094</v>
       </c>
       <c r="F4" t="n">
-        <v>4.082313411900459</v>
+        <v>4.082313411900405</v>
       </c>
       <c r="G4" t="n">
-        <v>15.54442772675217</v>
+        <v>15.54442772675213</v>
       </c>
       <c r="H4" t="n">
-        <v>18.78162889570952</v>
+        <v>18.78162889570996</v>
       </c>
       <c r="I4" t="n">
-        <v>4.063182916243152</v>
+        <v>15.52170802744369</v>
       </c>
       <c r="J4" t="n">
-        <v>4.239737876662783</v>
+        <v>15.95931911940827</v>
       </c>
       <c r="K4" t="n">
-        <v>3.930516400183484</v>
+        <v>3.930516400183405</v>
       </c>
       <c r="L4" t="n">
-        <v>4.144701134886949</v>
+        <v>4.144701134886796</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.726786654178929</v>
+        <v>5.726786654179097</v>
       </c>
       <c r="C5" t="n">
-        <v>5.699544904754394</v>
+        <v>5.699544904754403</v>
       </c>
       <c r="D5" t="n">
-        <v>5.726783824482181</v>
+        <v>5.726783824482139</v>
       </c>
       <c r="E5" t="n">
-        <v>5.652502716499955</v>
+        <v>5.652502716499916</v>
       </c>
       <c r="F5" t="n">
-        <v>5.652502716499955</v>
+        <v>5.652502716499916</v>
       </c>
       <c r="G5" t="n">
-        <v>5.722264604062719</v>
+        <v>5.722264604062844</v>
       </c>
       <c r="H5" t="n">
-        <v>5.726786654178929</v>
+        <v>5.726786654179097</v>
       </c>
       <c r="I5" t="n">
-        <v>5.699544904754394</v>
+        <v>5.699544904754403</v>
       </c>
       <c r="J5" t="n">
-        <v>5.726786654178929</v>
+        <v>5.726786654179097</v>
       </c>
       <c r="K5" t="n">
-        <v>5.726786654178929</v>
+        <v>5.726786654179097</v>
       </c>
       <c r="L5" t="n">
-        <v>5.726786654178929</v>
+        <v>5.726786654179097</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.72778431922366</v>
+        <v>15.72778431922364</v>
       </c>
       <c r="C6" t="n">
-        <v>24.72119354787248</v>
+        <v>24.72119354804417</v>
       </c>
       <c r="D6" t="n">
-        <v>26.67107458682915</v>
+        <v>26.67107458682885</v>
       </c>
       <c r="E6" t="n">
-        <v>22.24689275694148</v>
+        <v>22.24689275694153</v>
       </c>
       <c r="F6" t="n">
-        <v>15.95979114860445</v>
+        <v>15.95979114860436</v>
       </c>
       <c r="G6" t="n">
-        <v>24.78710558083943</v>
+        <v>24.78710558083914</v>
       </c>
       <c r="H6" t="n">
-        <v>24.79162763094629</v>
+        <v>24.79162763094601</v>
       </c>
       <c r="I6" t="n">
-        <v>24.76438588153021</v>
+        <v>24.76438588153072</v>
       </c>
       <c r="J6" t="n">
-        <v>24.79340893218418</v>
+        <v>24.79340893218408</v>
       </c>
       <c r="K6" t="n">
-        <v>15.55941877647538</v>
+        <v>15.55941877647524</v>
       </c>
       <c r="L6" t="n">
-        <v>34.2595698731196</v>
+        <v>34.25956987311942</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>515.0219614556753</v>
+        <v>515.0219614556754</v>
       </c>
       <c r="C7" t="n">
         <v>657.0221274340049</v>
       </c>
       <c r="D7" t="n">
-        <v>657.0493709638371</v>
+        <v>657.0493709638372</v>
       </c>
       <c r="E7" t="n">
-        <v>820.918743828835</v>
+        <v>820.9187438288351</v>
       </c>
       <c r="F7" t="n">
-        <v>657.0221256220832</v>
+        <v>657.0221256220824</v>
       </c>
       <c r="G7" t="n">
-        <v>657.0448471333139</v>
+        <v>657.0448471333143</v>
       </c>
       <c r="H7" t="n">
-        <v>657.0493691834307</v>
+        <v>657.0493691834303</v>
       </c>
       <c r="I7" t="n">
         <v>657.0221274340049</v>
       </c>
       <c r="J7" t="n">
-        <v>657.0493691834307</v>
+        <v>657.0493691834303</v>
       </c>
       <c r="K7" t="n">
-        <v>574.7581321101153</v>
+        <v>478.2115105901403</v>
       </c>
       <c r="L7" t="n">
-        <v>657.0493691834307</v>
+        <v>657.0493691834303</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.918644083430334</v>
+        <v>4.918644083430266</v>
       </c>
       <c r="C8" t="n">
-        <v>2.507350833693946</v>
+        <v>2.5073508336938</v>
       </c>
       <c r="D8" t="n">
-        <v>3.003574057350299</v>
+        <v>3.003574057350146</v>
       </c>
       <c r="E8" t="n">
-        <v>2.507350833693946</v>
+        <v>2.5073508336938</v>
       </c>
       <c r="F8" t="n">
-        <v>2.507350833693946</v>
+        <v>2.5073508336938</v>
       </c>
       <c r="G8" t="n">
-        <v>3.606453486315528</v>
+        <v>3.606453486315507</v>
       </c>
       <c r="H8" t="n">
-        <v>2.085407559954473</v>
+        <v>2.085407559954481</v>
       </c>
       <c r="I8" t="n">
-        <v>2.507350833693946</v>
+        <v>2.5073508336938</v>
       </c>
       <c r="J8" t="n">
-        <v>4.529990183161274</v>
+        <v>4.5299901831613</v>
       </c>
       <c r="K8" t="n">
-        <v>4.794643469280122</v>
+        <v>4.794643469280354</v>
       </c>
       <c r="L8" t="n">
-        <v>5.280721700383756</v>
+        <v>5.280721700383689</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.167930158145228</v>
+        <v>5.167930158145353</v>
       </c>
       <c r="C9" t="n">
-        <v>3.126742231314435</v>
+        <v>3.126742231314274</v>
       </c>
       <c r="D9" t="n">
-        <v>4.387999082813585</v>
+        <v>4.387999082813701</v>
       </c>
       <c r="E9" t="n">
-        <v>3.126742231314435</v>
+        <v>3.126742231314274</v>
       </c>
       <c r="F9" t="n">
-        <v>3.126742231314435</v>
+        <v>3.126742231314274</v>
       </c>
       <c r="G9" t="n">
-        <v>4.612063302576538</v>
+        <v>4.612063302576455</v>
       </c>
       <c r="H9" t="n">
-        <v>4.017097723503296</v>
+        <v>4.017097723503507</v>
       </c>
       <c r="I9" t="n">
-        <v>3.126742231314435</v>
+        <v>3.126742231314274</v>
       </c>
       <c r="J9" t="n">
-        <v>5.00998256700735</v>
+        <v>5.009982567007441</v>
       </c>
       <c r="K9" t="n">
-        <v>5.117459862876309</v>
+        <v>5.117459862876137</v>
       </c>
       <c r="L9" t="n">
-        <v>5.315523881190961</v>
+        <v>4.22645351663272</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>112.73718964518</v>
+        <v>112.7371896451804</v>
       </c>
       <c r="C2" t="n">
-        <v>78.9381813416222</v>
+        <v>78.93818134162333</v>
       </c>
       <c r="D2" t="n">
-        <v>60.22520562207448</v>
+        <v>60.22520562207439</v>
       </c>
       <c r="E2" t="n">
-        <v>78.9381813416222</v>
+        <v>78.93818134162333</v>
       </c>
       <c r="F2" t="n">
-        <v>78.9381813416222</v>
+        <v>78.93818134162333</v>
       </c>
       <c r="G2" t="n">
-        <v>215.6787120017912</v>
+        <v>215.6787120017909</v>
       </c>
       <c r="H2" t="n">
-        <v>64.73136664546323</v>
+        <v>64.73136664546277</v>
       </c>
       <c r="I2" t="n">
-        <v>78.9381813416222</v>
+        <v>78.93818134162333</v>
       </c>
       <c r="J2" t="n">
-        <v>107.2175734006595</v>
+        <v>107.217573400665</v>
       </c>
       <c r="K2" t="n">
-        <v>77.57719299712028</v>
+        <v>77.57719299711923</v>
       </c>
       <c r="L2" t="n">
-        <v>97.55330965010386</v>
+        <v>97.55330965010404</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.220641620573334</v>
+        <v>6.220641620573294</v>
       </c>
       <c r="C3" t="n">
-        <v>5.023076849432901</v>
+        <v>5.023076849432933</v>
       </c>
       <c r="D3" t="n">
-        <v>6.220641620573334</v>
+        <v>6.220641620573294</v>
       </c>
       <c r="E3" t="n">
-        <v>5.432278018024864</v>
+        <v>5.432278018024724</v>
       </c>
       <c r="F3" t="n">
-        <v>5.432278018024845</v>
+        <v>5.432278018024709</v>
       </c>
       <c r="G3" t="n">
-        <v>6.210499934978031</v>
+        <v>6.210499934976976</v>
       </c>
       <c r="H3" t="n">
-        <v>6.220641620573334</v>
+        <v>6.220641620573294</v>
       </c>
       <c r="I3" t="n">
-        <v>6.15891794375969</v>
+        <v>6.158917943759653</v>
       </c>
       <c r="J3" t="n">
-        <v>6.220641620573335</v>
+        <v>6.220641620573295</v>
       </c>
       <c r="K3" t="n">
-        <v>6.220641620573333</v>
+        <v>6.220641620573294</v>
       </c>
       <c r="L3" t="n">
-        <v>6.220641620573334</v>
+        <v>6.220641620573294</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.96743795462764</v>
+        <v>10.34216513503251</v>
       </c>
       <c r="C4" t="n">
-        <v>9.887530255968597</v>
+        <v>9.887530255968549</v>
       </c>
       <c r="D4" t="n">
-        <v>24.69084358460322</v>
+        <v>24.69084358460201</v>
       </c>
       <c r="E4" t="n">
-        <v>9.531839281396891</v>
+        <v>9.531839281397</v>
       </c>
       <c r="F4" t="n">
-        <v>10.23430237526662</v>
+        <v>10.23430237526683</v>
       </c>
       <c r="G4" t="n">
-        <v>10.33202344943743</v>
+        <v>23.95729626903261</v>
       </c>
       <c r="H4" t="n">
-        <v>26.98566856769997</v>
+        <v>26.98566856769985</v>
       </c>
       <c r="I4" t="n">
-        <v>10.28044145821876</v>
+        <v>10.28044145821873</v>
       </c>
       <c r="J4" t="n">
-        <v>24.59899953113167</v>
+        <v>10.59120509036229</v>
       </c>
       <c r="K4" t="n">
-        <v>10.15152073547532</v>
+        <v>10.15152073547489</v>
       </c>
       <c r="L4" t="n">
-        <v>10.23436996695496</v>
+        <v>10.23436996695492</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.2546337066143</v>
+        <v>11.25463370661532</v>
       </c>
       <c r="C5" t="n">
-        <v>11.19291002980101</v>
+        <v>11.19291002980074</v>
       </c>
       <c r="D5" t="n">
-        <v>11.25462971123111</v>
+        <v>11.2546297112318</v>
       </c>
       <c r="E5" t="n">
-        <v>11.1159402548415</v>
+        <v>11.1159402548414</v>
       </c>
       <c r="F5" t="n">
-        <v>11.1159402548415</v>
+        <v>11.11594025484147</v>
       </c>
       <c r="G5" t="n">
-        <v>11.24449202101932</v>
+        <v>11.24449202101925</v>
       </c>
       <c r="H5" t="n">
-        <v>11.2546337066143</v>
+        <v>11.25463370661532</v>
       </c>
       <c r="I5" t="n">
-        <v>11.19291002980101</v>
+        <v>11.19291002980074</v>
       </c>
       <c r="J5" t="n">
-        <v>11.2546337066143</v>
+        <v>11.25463370661532</v>
       </c>
       <c r="K5" t="n">
-        <v>11.2546337066143</v>
+        <v>11.25463370661532</v>
       </c>
       <c r="L5" t="n">
-        <v>11.2546337066143</v>
+        <v>11.25463370661532</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22.50631544381421</v>
+        <v>22.50631544381413</v>
       </c>
       <c r="C6" t="n">
-        <v>34.69018411563643</v>
+        <v>34.6901841160466</v>
       </c>
       <c r="D6" t="n">
-        <v>37.37701432638398</v>
+        <v>37.37701432638431</v>
       </c>
       <c r="E6" t="n">
-        <v>31.32919411480767</v>
+        <v>31.32919411480832</v>
       </c>
       <c r="F6" t="n">
-        <v>22.78909967681419</v>
+        <v>22.7890996768158</v>
       </c>
       <c r="G6" t="n">
-        <v>34.81291592021946</v>
+        <v>34.81291592022043</v>
       </c>
       <c r="H6" t="n">
-        <v>34.82305760571433</v>
+        <v>34.8230576057144</v>
       </c>
       <c r="I6" t="n">
-        <v>34.76133392900087</v>
+        <v>34.7613339290026</v>
       </c>
       <c r="J6" t="n">
-        <v>34.82547815693803</v>
+        <v>34.82547815693638</v>
       </c>
       <c r="K6" t="n">
-        <v>22.27752563874892</v>
+        <v>22.27752563874922</v>
       </c>
       <c r="L6" t="n">
-        <v>47.68892466346006</v>
+        <v>47.68892466346323</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>456.0686257631173</v>
+        <v>456.0686257631168</v>
       </c>
       <c r="C7" t="n">
-        <v>581.2716566610344</v>
+        <v>581.2716566610346</v>
       </c>
       <c r="D7" t="n">
         <v>581.3333895925686</v>
       </c>
       <c r="E7" t="n">
-        <v>725.8245356992308</v>
+        <v>725.8245356992313</v>
       </c>
       <c r="F7" t="n">
-        <v>581.2716566088444</v>
+        <v>581.2716566088446</v>
       </c>
       <c r="G7" t="n">
-        <v>581.3232386522519</v>
+        <v>581.3232386522523</v>
       </c>
       <c r="H7" t="n">
-        <v>581.3333803378476</v>
+        <v>581.3333803378483</v>
       </c>
       <c r="I7" t="n">
-        <v>581.2716566610344</v>
+        <v>581.2716566610346</v>
       </c>
       <c r="J7" t="n">
-        <v>581.3333803378476</v>
+        <v>581.3333803378483</v>
       </c>
       <c r="K7" t="n">
-        <v>508.754493477081</v>
+        <v>508.7544934770817</v>
       </c>
       <c r="L7" t="n">
-        <v>581.3333803378476</v>
+        <v>581.3333803378483</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.500847379187135</v>
+        <v>7.500847379186215</v>
       </c>
       <c r="C8" t="n">
-        <v>6.750460844098193</v>
+        <v>6.750460844098816</v>
       </c>
       <c r="D8" t="n">
-        <v>8.83582986496662</v>
+        <v>8.835829864967385</v>
       </c>
       <c r="E8" t="n">
-        <v>6.750460844098193</v>
+        <v>6.750460844098816</v>
       </c>
       <c r="F8" t="n">
-        <v>6.750460844098193</v>
+        <v>6.750460844098816</v>
       </c>
       <c r="G8" t="n">
-        <v>4.849654729222802</v>
+        <v>4.849654729222605</v>
       </c>
       <c r="H8" t="n">
-        <v>8.917696681754988</v>
+        <v>8.917696681754853</v>
       </c>
       <c r="I8" t="n">
-        <v>6.750460844098193</v>
+        <v>6.750460844098816</v>
       </c>
       <c r="J8" t="n">
-        <v>7.878953115763976</v>
+        <v>7.878953115764002</v>
       </c>
       <c r="K8" t="n">
-        <v>8.309083299371585</v>
+        <v>8.309083299372238</v>
       </c>
       <c r="L8" t="n">
-        <v>8.281235224518346</v>
+        <v>8.281235224519259</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.002647382001632</v>
+        <v>9.002647382001784</v>
       </c>
       <c r="C9" t="n">
-        <v>7.772270221317972</v>
+        <v>7.772270221317999</v>
       </c>
       <c r="D9" t="n">
-        <v>9.546414588838266</v>
+        <v>9.546414588839781</v>
       </c>
       <c r="E9" t="n">
-        <v>7.772270221317972</v>
+        <v>7.772270221317999</v>
       </c>
       <c r="F9" t="n">
-        <v>7.772270221317972</v>
+        <v>7.772270221317999</v>
       </c>
       <c r="G9" t="n">
-        <v>7.88790841886544</v>
+        <v>7.887908418865964</v>
       </c>
       <c r="H9" t="n">
-        <v>9.580953469303575</v>
+        <v>9.580953469303418</v>
       </c>
       <c r="I9" t="n">
-        <v>7.772270221317972</v>
+        <v>7.772270221317999</v>
       </c>
       <c r="J9" t="n">
-        <v>9.157548772594284</v>
+        <v>9.157548772593861</v>
       </c>
       <c r="K9" t="n">
-        <v>9.331938990494001</v>
+        <v>9.33193899049451</v>
       </c>
       <c r="L9" t="n">
-        <v>9.132488150428662</v>
+        <v>9.321979025936731</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-15.83302403596091</v>
+        <v>-15.83302403596069</v>
       </c>
       <c r="C2" t="n">
-        <v>7.241481360480872</v>
+        <v>7.241481360480218</v>
       </c>
       <c r="D2" t="n">
-        <v>119.5922547783652</v>
+        <v>119.5922547783689</v>
       </c>
       <c r="E2" t="n">
-        <v>52.14063836887477</v>
+        <v>52.14063836887366</v>
       </c>
       <c r="F2" t="n">
-        <v>52.14063836887477</v>
+        <v>52.14063836887366</v>
       </c>
       <c r="G2" t="n">
-        <v>69.14478879905819</v>
+        <v>69.14478879905899</v>
       </c>
       <c r="H2" t="n">
-        <v>80.86661188509694</v>
+        <v>80.86661188509575</v>
       </c>
       <c r="I2" t="n">
-        <v>52.14063836887477</v>
+        <v>52.14063836887366</v>
       </c>
       <c r="J2" t="n">
-        <v>35.45031363811658</v>
+        <v>35.45031363811567</v>
       </c>
       <c r="K2" t="n">
-        <v>62.47352553697431</v>
+        <v>62.47352553697409</v>
       </c>
       <c r="L2" t="n">
-        <v>65.3462130448554</v>
+        <v>65.3462130448559</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.736620471301221</v>
+        <v>1.736620471301237</v>
       </c>
       <c r="C3" t="n">
         <v>1.083515158923763</v>
       </c>
       <c r="D3" t="n">
-        <v>1.736620471301236</v>
+        <v>1.736620471301229</v>
       </c>
       <c r="E3" t="n">
-        <v>1.380517034720345</v>
+        <v>1.380517034724069</v>
       </c>
       <c r="F3" t="n">
-        <v>1.380517034720774</v>
+        <v>1.380517034724046</v>
       </c>
       <c r="G3" t="n">
-        <v>1.730573246506099</v>
+        <v>1.73057324650613</v>
       </c>
       <c r="H3" t="n">
-        <v>1.736620471301236</v>
+        <v>1.736620471301242</v>
       </c>
       <c r="I3" t="n">
-        <v>1.698926289838011</v>
+        <v>1.698926289837984</v>
       </c>
       <c r="J3" t="n">
-        <v>1.736620471301237</v>
+        <v>1.736620471301243</v>
       </c>
       <c r="K3" t="n">
-        <v>1.736620471301237</v>
+        <v>1.736620471301229</v>
       </c>
       <c r="L3" t="n">
-        <v>1.736620471301237</v>
+        <v>1.73662047130123</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.455724172536242</v>
+        <v>13.7375747211099</v>
       </c>
       <c r="C4" t="n">
-        <v>3.267406149351941</v>
+        <v>3.267406149351937</v>
       </c>
       <c r="D4" t="n">
-        <v>3.559682451165855</v>
+        <v>3.559706198468819</v>
       </c>
       <c r="E4" t="n">
-        <v>3.326147270161365</v>
+        <v>3.326147270161381</v>
       </c>
       <c r="F4" t="n">
-        <v>3.443103411088597</v>
+        <v>3.443103411088614</v>
       </c>
       <c r="G4" t="n">
-        <v>13.73152749631468</v>
+        <v>3.449676947741094</v>
       </c>
       <c r="H4" t="n">
-        <v>16.70185024134044</v>
+        <v>16.7018502413405</v>
       </c>
       <c r="I4" t="n">
-        <v>13.69988053964659</v>
+        <v>3.418029991072975</v>
       </c>
       <c r="J4" t="n">
-        <v>14.0035836385381</v>
+        <v>14.00358363853813</v>
       </c>
       <c r="K4" t="n">
-        <v>3.384962364635957</v>
+        <v>3.384962364635973</v>
       </c>
       <c r="L4" t="n">
-        <v>3.478781709208412</v>
+        <v>3.478781709208432</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.043310481855281</v>
+        <v>5.043310481855271</v>
       </c>
       <c r="C5" t="n">
-        <v>5.03523021879581</v>
+        <v>5.035230218795909</v>
       </c>
       <c r="D5" t="n">
-        <v>5.043304414150588</v>
+        <v>5.043304414150535</v>
       </c>
       <c r="E5" t="n">
-        <v>5.025158425301387</v>
+        <v>5.025158425301417</v>
       </c>
       <c r="F5" t="n">
-        <v>5.025158425301387</v>
+        <v>5.025158425301417</v>
       </c>
       <c r="G5" t="n">
-        <v>5.037263257060113</v>
+        <v>5.037263257060129</v>
       </c>
       <c r="H5" t="n">
-        <v>5.043310481855281</v>
+        <v>5.043310481855271</v>
       </c>
       <c r="I5" t="n">
-        <v>5.005616300392031</v>
+        <v>5.005616300392059</v>
       </c>
       <c r="J5" t="n">
-        <v>5.043310481855281</v>
+        <v>5.043310481855271</v>
       </c>
       <c r="K5" t="n">
-        <v>5.043310481855281</v>
+        <v>5.043310481855271</v>
       </c>
       <c r="L5" t="n">
-        <v>5.043310481855281</v>
+        <v>5.043310481855271</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.29807182082252</v>
+        <v>14.29807182082242</v>
       </c>
       <c r="C6" t="n">
-        <v>22.52779551919751</v>
+        <v>22.52779551919787</v>
       </c>
       <c r="D6" t="n">
-        <v>24.21952087724377</v>
+        <v>24.21952087724447</v>
       </c>
       <c r="E6" t="n">
-        <v>20.24861842862763</v>
+        <v>20.24861842862831</v>
       </c>
       <c r="F6" t="n">
-        <v>14.53252106539301</v>
+        <v>14.53252106539312</v>
       </c>
       <c r="G6" t="n">
-        <v>22.50952202791323</v>
+        <v>22.50952202791321</v>
       </c>
       <c r="H6" t="n">
-        <v>22.51556925271376</v>
+        <v>22.51556925271415</v>
       </c>
       <c r="I6" t="n">
-        <v>22.4778750712451</v>
+        <v>22.47787507124503</v>
       </c>
       <c r="J6" t="n">
-        <v>22.51718422519613</v>
+        <v>22.51718422519656</v>
       </c>
       <c r="K6" t="n">
-        <v>14.14542758697481</v>
+        <v>14.14542758697523</v>
       </c>
       <c r="L6" t="n">
-        <v>31.09943245562244</v>
+        <v>31.09943245562311</v>
       </c>
     </row>
     <row r="7">
@@ -1510,25 +1510,25 @@
         <v>472.7088039140141</v>
       </c>
       <c r="C7" t="n">
-        <v>603.0532314493583</v>
+        <v>603.0532314493582</v>
       </c>
       <c r="D7" t="n">
-        <v>603.0613140870591</v>
+        <v>603.0613140870594</v>
       </c>
       <c r="E7" t="n">
         <v>753.4476492800371</v>
       </c>
       <c r="F7" t="n">
-        <v>603.0236171491749</v>
+        <v>603.023617149175</v>
       </c>
       <c r="G7" t="n">
-        <v>603.0552644876227</v>
+        <v>603.0552644876225</v>
       </c>
       <c r="H7" t="n">
         <v>603.0613117124192</v>
       </c>
       <c r="I7" t="n">
-        <v>603.0236175309543</v>
+        <v>603.0236175309545</v>
       </c>
       <c r="J7" t="n">
         <v>603.0613117124192</v>
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.349283506835739</v>
+        <v>6.349283506835744</v>
       </c>
       <c r="C8" t="n">
-        <v>2.092553655152999</v>
+        <v>2.092553655153051</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4326594946956694</v>
+        <v>0.432659494695582</v>
       </c>
       <c r="E8" t="n">
-        <v>2.213119991982347</v>
+        <v>2.213119991982312</v>
       </c>
       <c r="F8" t="n">
-        <v>2.213119991982347</v>
+        <v>2.213119991982312</v>
       </c>
       <c r="G8" t="n">
-        <v>3.41717964446588</v>
+        <v>3.417179644465831</v>
       </c>
       <c r="H8" t="n">
-        <v>1.541052704473401</v>
+        <v>1.541052704473445</v>
       </c>
       <c r="I8" t="n">
-        <v>2.213119991982347</v>
+        <v>2.213119991982312</v>
       </c>
       <c r="J8" t="n">
-        <v>4.630067517652128</v>
+        <v>4.63006751765216</v>
       </c>
       <c r="K8" t="n">
-        <v>3.722123302943449</v>
+        <v>3.722123302943486</v>
       </c>
       <c r="L8" t="n">
-        <v>1.361311434758441</v>
+        <v>1.361311434758434</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.002651261568204</v>
+        <v>6.002651261568211</v>
       </c>
       <c r="C9" t="n">
-        <v>2.125685016538492</v>
+        <v>2.125685016538516</v>
       </c>
       <c r="D9" t="n">
-        <v>1.989880872792201</v>
+        <v>1.9898808727922</v>
       </c>
       <c r="E9" t="n">
-        <v>2.835278726306624</v>
+        <v>2.835278726306652</v>
       </c>
       <c r="F9" t="n">
-        <v>2.835278726306624</v>
+        <v>2.835278726306652</v>
       </c>
       <c r="G9" t="n">
-        <v>4.228470255155881</v>
+        <v>4.228470255155901</v>
       </c>
       <c r="H9" t="n">
-        <v>2.442713516930704</v>
+        <v>2.442713516930739</v>
       </c>
       <c r="I9" t="n">
-        <v>2.835278726306624</v>
+        <v>2.835278726306656</v>
       </c>
       <c r="J9" t="n">
-        <v>4.977551841335552</v>
+        <v>4.977551841335569</v>
       </c>
       <c r="K9" t="n">
-        <v>4.462774424459043</v>
+        <v>4.462774424459033</v>
       </c>
       <c r="L9" t="n">
-        <v>2.068052917493928</v>
+        <v>2.068052917493882</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.306010916300769</v>
+        <v>8.30601091630073</v>
       </c>
       <c r="C2" t="n">
-        <v>9.865129949857273</v>
+        <v>9.865129949857334</v>
       </c>
       <c r="D2" t="n">
-        <v>141.3151066139582</v>
+        <v>141.3151066139581</v>
       </c>
       <c r="E2" t="n">
-        <v>75.91998006382458</v>
+        <v>75.91998006382471</v>
       </c>
       <c r="F2" t="n">
-        <v>75.91998006382458</v>
+        <v>75.91998006382471</v>
       </c>
       <c r="G2" t="n">
-        <v>86.00953882059683</v>
+        <v>86.00953882059747</v>
       </c>
       <c r="H2" t="n">
-        <v>50.55239755859181</v>
+        <v>50.5523975585917</v>
       </c>
       <c r="I2" t="n">
-        <v>75.91998006382458</v>
+        <v>75.91998006382471</v>
       </c>
       <c r="J2" t="n">
-        <v>25.9339148038574</v>
+        <v>25.93391480385732</v>
       </c>
       <c r="K2" t="n">
-        <v>93.93741360972393</v>
+        <v>93.93741360972378</v>
       </c>
       <c r="L2" t="n">
-        <v>96.65095074226629</v>
+        <v>96.6509507422663</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.194249767491242</v>
+        <v>2.194249767491201</v>
       </c>
       <c r="C3" t="n">
-        <v>1.60526519027067</v>
+        <v>1.605265190270611</v>
       </c>
       <c r="D3" t="n">
-        <v>2.194249767491242</v>
+        <v>2.194249767491201</v>
       </c>
       <c r="E3" t="n">
-        <v>2.245083690772412</v>
+        <v>2.245083690772393</v>
       </c>
       <c r="F3" t="n">
-        <v>2.245083690772419</v>
+        <v>2.245083690772392</v>
       </c>
       <c r="G3" t="n">
-        <v>2.188971796760164</v>
+        <v>2.188971796760137</v>
       </c>
       <c r="H3" t="n">
-        <v>2.194249767491242</v>
+        <v>2.194249767491201</v>
       </c>
       <c r="I3" t="n">
-        <v>2.161389537408299</v>
+        <v>2.161389537408256</v>
       </c>
       <c r="J3" t="n">
-        <v>2.194249767491212</v>
+        <v>2.1942497674912</v>
       </c>
       <c r="K3" t="n">
-        <v>2.194249767491242</v>
+        <v>2.194249767491201</v>
       </c>
       <c r="L3" t="n">
-        <v>2.194249767491242</v>
+        <v>2.194249767491202</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.08280079086069</v>
+        <v>14.0828007908607</v>
       </c>
       <c r="C4" t="n">
-        <v>3.786495827188501</v>
+        <v>3.786495827188502</v>
       </c>
       <c r="D4" t="n">
-        <v>14.40387575258529</v>
+        <v>14.40387575258522</v>
       </c>
       <c r="E4" t="n">
-        <v>3.916584499018277</v>
+        <v>3.916584499018193</v>
       </c>
       <c r="F4" t="n">
-        <v>4.01235832459809</v>
+        <v>4.012358324598027</v>
       </c>
       <c r="G4" t="n">
-        <v>3.990642832903172</v>
+        <v>14.07752282012961</v>
       </c>
       <c r="H4" t="n">
-        <v>16.86411539263434</v>
+        <v>16.86411539263429</v>
       </c>
       <c r="I4" t="n">
-        <v>3.963060573551349</v>
+        <v>3.963060573551281</v>
       </c>
       <c r="J4" t="n">
-        <v>4.106717722740677</v>
+        <v>4.106717722740604</v>
       </c>
       <c r="K4" t="n">
-        <v>3.938565325925179</v>
+        <v>3.938565325925117</v>
       </c>
       <c r="L4" t="n">
-        <v>4.013128607378903</v>
+        <v>4.013128607378842</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.599064246116738</v>
+        <v>5.59906424611665</v>
       </c>
       <c r="C5" t="n">
-        <v>5.59077203865816</v>
+        <v>5.590772038658034</v>
       </c>
       <c r="D5" t="n">
-        <v>5.59904307351588</v>
+        <v>5.5990430735158</v>
       </c>
       <c r="E5" t="n">
-        <v>5.693356608512485</v>
+        <v>5.693356608512406</v>
       </c>
       <c r="F5" t="n">
-        <v>5.693356608512485</v>
+        <v>5.693356608512406</v>
       </c>
       <c r="G5" t="n">
-        <v>5.593786275385582</v>
+        <v>5.593786275385572</v>
       </c>
       <c r="H5" t="n">
-        <v>5.599064246116738</v>
+        <v>5.59906424611665</v>
       </c>
       <c r="I5" t="n">
-        <v>5.566204016033775</v>
+        <v>5.566204016033701</v>
       </c>
       <c r="J5" t="n">
-        <v>5.599064246116738</v>
+        <v>5.59906424611665</v>
       </c>
       <c r="K5" t="n">
-        <v>5.599064246116738</v>
+        <v>5.59906424611665</v>
       </c>
       <c r="L5" t="n">
-        <v>5.599064246116738</v>
+        <v>5.59906424611665</v>
       </c>
     </row>
     <row r="6">
@@ -1863,25 +1863,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.58545272490861</v>
+        <v>14.58545272490866</v>
       </c>
       <c r="C6" t="n">
-        <v>22.94471380790113</v>
+        <v>22.9447138077066</v>
       </c>
       <c r="D6" t="n">
-        <v>24.53934012455322</v>
+        <v>24.53934012455313</v>
       </c>
       <c r="E6" t="n">
-        <v>20.65235297906808</v>
+        <v>20.65235297906811</v>
       </c>
       <c r="F6" t="n">
-        <v>14.88979145079222</v>
+        <v>14.88979145079223</v>
       </c>
       <c r="G6" t="n">
-        <v>22.82453943120114</v>
+        <v>22.82453943120109</v>
       </c>
       <c r="H6" t="n">
-        <v>22.82981740191907</v>
+        <v>22.82981740191913</v>
       </c>
       <c r="I6" t="n">
         <v>22.79695717184919</v>
@@ -1890,10 +1890,10 @@
         <v>22.83143765157181</v>
       </c>
       <c r="K6" t="n">
-        <v>14.4323094183688</v>
+        <v>14.43230941836877</v>
       </c>
       <c r="L6" t="n">
-        <v>31.44174568619597</v>
+        <v>31.441745686196</v>
       </c>
     </row>
     <row r="7">
@@ -1915,22 +1915,22 @@
         <v>714.6511248521982</v>
       </c>
       <c r="F7" t="n">
-        <v>572.0363821673535</v>
+        <v>572.0363821673534</v>
       </c>
       <c r="G7" t="n">
-        <v>572.0639642214494</v>
+        <v>572.0639642214493</v>
       </c>
       <c r="H7" t="n">
         <v>572.0692421921808</v>
       </c>
       <c r="I7" t="n">
-        <v>572.0363819620974</v>
+        <v>572.0363819620973</v>
       </c>
       <c r="J7" t="n">
         <v>572.0692421921808</v>
       </c>
       <c r="K7" t="n">
-        <v>500.4634735910096</v>
+        <v>500.4634735910097</v>
       </c>
       <c r="L7" t="n">
         <v>572.0692421921808</v>
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.083389863809522</v>
+        <v>6.083389863809531</v>
       </c>
       <c r="C8" t="n">
-        <v>2.336845655251086</v>
+        <v>2.336845655251083</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2900905304590953</v>
+        <v>0.2900905304591124</v>
       </c>
       <c r="E8" t="n">
-        <v>2.178233844747116</v>
+        <v>2.178233844747123</v>
       </c>
       <c r="F8" t="n">
-        <v>2.178233844747116</v>
+        <v>2.178233844747123</v>
       </c>
       <c r="G8" t="n">
-        <v>3.408217747622901</v>
+        <v>3.408217747622892</v>
       </c>
       <c r="H8" t="n">
-        <v>2.642010574484335</v>
+        <v>2.642010574484354</v>
       </c>
       <c r="I8" t="n">
-        <v>2.178233844747116</v>
+        <v>2.178233844747123</v>
       </c>
       <c r="J8" t="n">
-        <v>5.514950200011319</v>
+        <v>5.514950200011344</v>
       </c>
       <c r="K8" t="n">
-        <v>3.742477987702221</v>
+        <v>3.742477987702239</v>
       </c>
       <c r="L8" t="n">
-        <v>1.089118875246706</v>
+        <v>1.089118875246718</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.056575566749192</v>
+        <v>6.056575566749199</v>
       </c>
       <c r="C9" t="n">
-        <v>2.404872842512085</v>
+        <v>2.404872842512086</v>
       </c>
       <c r="D9" t="n">
-        <v>2.241811644328002</v>
+        <v>2.241811644327995</v>
       </c>
       <c r="E9" t="n">
-        <v>3.168387249769963</v>
+        <v>3.168387249769967</v>
       </c>
       <c r="F9" t="n">
-        <v>3.168387249769963</v>
+        <v>3.168387249769967</v>
       </c>
       <c r="G9" t="n">
-        <v>4.49778183682239</v>
+        <v>4.497781836822394</v>
       </c>
       <c r="H9" t="n">
-        <v>3.200579337477703</v>
+        <v>3.200579337477731</v>
       </c>
       <c r="I9" t="n">
-        <v>3.168387249769963</v>
+        <v>3.168387249769967</v>
       </c>
       <c r="J9" t="n">
-        <v>5.744042044250588</v>
+        <v>5.744042044250606</v>
       </c>
       <c r="K9" t="n">
-        <v>4.967739177177522</v>
+        <v>4.967739177177515</v>
       </c>
       <c r="L9" t="n">
-        <v>2.221844401631392</v>
+        <v>2.221844401631401</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.34958948700154</v>
+        <v>18.34958948700138</v>
       </c>
       <c r="C2" t="n">
-        <v>10.90093750837567</v>
+        <v>10.90093750837539</v>
       </c>
       <c r="D2" t="n">
-        <v>152.4673227234418</v>
+        <v>152.4673227234411</v>
       </c>
       <c r="E2" t="n">
-        <v>75.6144505360452</v>
+        <v>75.61445053604506</v>
       </c>
       <c r="F2" t="n">
-        <v>75.6144505360452</v>
+        <v>75.61445053604506</v>
       </c>
       <c r="G2" t="n">
-        <v>97.09330168744704</v>
+        <v>97.09330168744658</v>
       </c>
       <c r="H2" t="n">
-        <v>35.62290380693623</v>
+        <v>35.6229038069357</v>
       </c>
       <c r="I2" t="n">
-        <v>75.6144505360452</v>
+        <v>75.61445053604506</v>
       </c>
       <c r="J2" t="n">
-        <v>17.12660932580554</v>
+        <v>17.12660932580546</v>
       </c>
       <c r="K2" t="n">
-        <v>111.7255536908271</v>
+        <v>111.7255536908265</v>
       </c>
       <c r="L2" t="n">
-        <v>133.1780066797589</v>
+        <v>133.1780066797583</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.270375902147857</v>
+        <v>2.270375902148407</v>
       </c>
       <c r="C3" t="n">
-        <v>1.696317566637756</v>
+        <v>1.696317566637638</v>
       </c>
       <c r="D3" t="n">
-        <v>2.270375902147854</v>
+        <v>2.270375902148032</v>
       </c>
       <c r="E3" t="n">
-        <v>2.479694096777119</v>
+        <v>2.479694096777135</v>
       </c>
       <c r="F3" t="n">
-        <v>2.479694096777122</v>
+        <v>2.479694096777115</v>
       </c>
       <c r="G3" t="n">
-        <v>2.26488404138553</v>
+        <v>2.264884041385222</v>
       </c>
       <c r="H3" t="n">
-        <v>2.270375902147854</v>
+        <v>2.270375902148032</v>
       </c>
       <c r="I3" t="n">
-        <v>2.236247775759947</v>
+        <v>2.236247775759893</v>
       </c>
       <c r="J3" t="n">
-        <v>2.270375902147857</v>
+        <v>2.270375902148032</v>
       </c>
       <c r="K3" t="n">
-        <v>2.270375902147854</v>
+        <v>2.270375902148032</v>
       </c>
       <c r="L3" t="n">
-        <v>2.270375902147854</v>
+        <v>2.270375902148032</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.169280006749673</v>
+        <v>4.169280006748765</v>
       </c>
       <c r="C4" t="n">
-        <v>3.942933045283077</v>
+        <v>3.942933045282987</v>
       </c>
       <c r="D4" t="n">
-        <v>4.266188291223673</v>
+        <v>4.266165232283749</v>
       </c>
       <c r="E4" t="n">
-        <v>4.083272931303895</v>
+        <v>4.083272931303875</v>
       </c>
       <c r="F4" t="n">
-        <v>4.190656819115761</v>
+        <v>4.190656819115567</v>
       </c>
       <c r="G4" t="n">
-        <v>14.40954260531967</v>
+        <v>14.4095426053202</v>
       </c>
       <c r="H4" t="n">
-        <v>17.17710621832191</v>
+        <v>17.1771062183224</v>
       </c>
       <c r="I4" t="n">
-        <v>14.38090633969407</v>
+        <v>14.38090633969389</v>
       </c>
       <c r="J4" t="n">
-        <v>14.73204896680002</v>
+        <v>14.7320489668002</v>
       </c>
       <c r="K4" t="n">
-        <v>4.121850848152287</v>
+        <v>4.121850848152159</v>
       </c>
       <c r="L4" t="n">
-        <v>4.190395350762273</v>
+        <v>4.190395350762304</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.774295148122349</v>
+        <v>5.774295148121953</v>
       </c>
       <c r="C5" t="n">
-        <v>5.76542808814706</v>
+        <v>5.765428088146908</v>
       </c>
       <c r="D5" t="n">
-        <v>5.774285163453242</v>
+        <v>5.774285163452784</v>
       </c>
       <c r="E5" t="n">
-        <v>5.920286436400622</v>
+        <v>5.920286436400538</v>
       </c>
       <c r="F5" t="n">
-        <v>5.920286436400622</v>
+        <v>5.920286436400538</v>
       </c>
       <c r="G5" t="n">
-        <v>5.768803287360038</v>
+        <v>5.768803287359995</v>
       </c>
       <c r="H5" t="n">
-        <v>5.774295148122349</v>
+        <v>5.774295148121953</v>
       </c>
       <c r="I5" t="n">
-        <v>5.740167021734447</v>
+        <v>5.740167021734308</v>
       </c>
       <c r="J5" t="n">
-        <v>5.774295148122349</v>
+        <v>5.774295148121953</v>
       </c>
       <c r="K5" t="n">
-        <v>5.774295148122349</v>
+        <v>5.774295148121953</v>
       </c>
       <c r="L5" t="n">
-        <v>5.774295148122349</v>
+        <v>5.774295148121953</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.79547844164336</v>
+        <v>14.79547844164356</v>
       </c>
       <c r="C6" t="n">
-        <v>23.34196203707461</v>
+        <v>23.34196203725469</v>
       </c>
       <c r="D6" t="n">
-        <v>24.91493570523975</v>
+        <v>24.91493570523972</v>
       </c>
       <c r="E6" t="n">
-        <v>21.00602931576174</v>
+        <v>21.00602931576166</v>
       </c>
       <c r="F6" t="n">
-        <v>15.13448682069416</v>
+        <v>15.13448682069411</v>
       </c>
       <c r="G6" t="n">
-        <v>23.17148545322356</v>
+        <v>23.17148545322399</v>
       </c>
       <c r="H6" t="n">
         <v>23.17697731397998</v>
       </c>
       <c r="I6" t="n">
-        <v>23.14284918759795</v>
+        <v>23.14284918759789</v>
       </c>
       <c r="J6" t="n">
-        <v>23.17862451295482</v>
+        <v>23.17862451295449</v>
       </c>
       <c r="K6" t="n">
-        <v>14.6397877972696</v>
+        <v>14.63978779727034</v>
       </c>
       <c r="L6" t="n">
-        <v>31.93215373073942</v>
+        <v>31.93215373073901</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>448.2869425194642</v>
+        <v>448.2869425194641</v>
       </c>
       <c r="C7" t="n">
-        <v>571.8104139668011</v>
+        <v>571.810413966801</v>
       </c>
       <c r="D7" t="n">
-        <v>571.8192848245699</v>
+        <v>571.8192848245695</v>
       </c>
       <c r="E7" t="n">
-        <v>714.338856099673</v>
+        <v>714.3388560996727</v>
       </c>
       <c r="F7" t="n">
-        <v>571.7851532503456</v>
+        <v>571.7851532503455</v>
       </c>
       <c r="G7" t="n">
-        <v>571.8137891660135</v>
+        <v>571.813789166013</v>
       </c>
       <c r="H7" t="n">
-        <v>571.8192810267756</v>
+        <v>571.8192810267755</v>
       </c>
       <c r="I7" t="n">
-        <v>571.7851529003883</v>
+        <v>571.785152900388</v>
       </c>
       <c r="J7" t="n">
-        <v>571.8192810267756</v>
+        <v>571.8192810267755</v>
       </c>
       <c r="K7" t="n">
-        <v>416.2700154173389</v>
+        <v>497.3402673390596</v>
       </c>
       <c r="L7" t="n">
-        <v>571.8192810267756</v>
+        <v>571.8192810267755</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.951766528904216</v>
+        <v>5.951766528904106</v>
       </c>
       <c r="C8" t="n">
-        <v>2.427421555856768</v>
+        <v>2.427421555856755</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1760701375268753</v>
+        <v>0.1760701375267467</v>
       </c>
       <c r="E8" t="n">
-        <v>2.385393151391134</v>
+        <v>2.385393151391108</v>
       </c>
       <c r="F8" t="n">
-        <v>2.385393151391134</v>
+        <v>2.385393151391109</v>
       </c>
       <c r="G8" t="n">
-        <v>3.328522727639901</v>
+        <v>3.328522727639785</v>
       </c>
       <c r="H8" t="n">
-        <v>3.121324341961424</v>
+        <v>3.121324341961645</v>
       </c>
       <c r="I8" t="n">
-        <v>2.385393151391134</v>
+        <v>2.385393151391109</v>
       </c>
       <c r="J8" t="n">
-        <v>5.990502030930661</v>
+        <v>5.990502030930529</v>
       </c>
       <c r="K8" t="n">
-        <v>3.667801718253476</v>
+        <v>3.667801718253709</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5022197377530911</v>
+        <v>0.502219737753511</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.065231850879925</v>
+        <v>6.065231850880278</v>
       </c>
       <c r="C9" t="n">
-        <v>2.509112545249142</v>
+        <v>2.509112545249128</v>
       </c>
       <c r="D9" t="n">
-        <v>2.287497042670147</v>
+        <v>2.287497042670017</v>
       </c>
       <c r="E9" t="n">
-        <v>3.368886032807794</v>
+        <v>3.368886032807768</v>
       </c>
       <c r="F9" t="n">
-        <v>3.368886032807794</v>
+        <v>3.368886032807768</v>
       </c>
       <c r="G9" t="n">
-        <v>4.571744814306292</v>
+        <v>4.571744814306307</v>
       </c>
       <c r="H9" t="n">
-        <v>3.487619986282034</v>
+        <v>3.48761998628174</v>
       </c>
       <c r="I9" t="n">
-        <v>3.368886032807794</v>
+        <v>3.368886032807768</v>
       </c>
       <c r="J9" t="n">
-        <v>6.095243428893565</v>
+        <v>6.095243428893625</v>
       </c>
       <c r="K9" t="n">
-        <v>5.144548443536674</v>
+        <v>5.14454844353679</v>
       </c>
       <c r="L9" t="n">
-        <v>2.090226985969252</v>
+        <v>2.090226985969462</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.12146722291607</v>
+        <v>5.121467222916081</v>
       </c>
       <c r="C2" t="n">
-        <v>7.909716311962353</v>
+        <v>7.909716311962323</v>
       </c>
       <c r="D2" t="n">
-        <v>140.4953359641918</v>
+        <v>140.4953359641917</v>
       </c>
       <c r="E2" t="n">
-        <v>81.00952377099537</v>
+        <v>81.00952377099458</v>
       </c>
       <c r="F2" t="n">
-        <v>81.00952377099537</v>
+        <v>81.00952377099458</v>
       </c>
       <c r="G2" t="n">
-        <v>95.22428108320145</v>
+        <v>95.22428108320226</v>
       </c>
       <c r="H2" t="n">
-        <v>70.73650725978732</v>
+        <v>70.73650725978725</v>
       </c>
       <c r="I2" t="n">
-        <v>81.00952377099537</v>
+        <v>81.00952377099458</v>
       </c>
       <c r="J2" t="n">
-        <v>37.56733158554658</v>
+        <v>37.5673315855466</v>
       </c>
       <c r="K2" t="n">
-        <v>84.56380215555365</v>
+        <v>84.5638021555537</v>
       </c>
       <c r="L2" t="n">
-        <v>99.07573936996394</v>
+        <v>99.0757393699638</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.97128919628425</v>
+        <v>1.97128919628424</v>
       </c>
       <c r="C3" t="n">
-        <v>1.241104350436613</v>
+        <v>1.241104350436617</v>
       </c>
       <c r="D3" t="n">
-        <v>1.97128919628425</v>
+        <v>1.971289196284241</v>
       </c>
       <c r="E3" t="n">
-        <v>2.133240117984761</v>
+        <v>2.133240117984771</v>
       </c>
       <c r="F3" t="n">
-        <v>2.133240117984762</v>
+        <v>2.13324011798477</v>
       </c>
       <c r="G3" t="n">
-        <v>1.966032384468557</v>
+        <v>1.96603238446855</v>
       </c>
       <c r="H3" t="n">
-        <v>1.97128919628425</v>
+        <v>1.97128919628424</v>
       </c>
       <c r="I3" t="n">
-        <v>1.938385997014466</v>
+        <v>1.938385997014455</v>
       </c>
       <c r="J3" t="n">
-        <v>1.97128919628425</v>
+        <v>1.97128919628424</v>
       </c>
       <c r="K3" t="n">
-        <v>1.97128919628425</v>
+        <v>1.97128919628424</v>
       </c>
       <c r="L3" t="n">
-        <v>1.97128919628425</v>
+        <v>1.97128919628424</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.841158240942411</v>
+        <v>3.841158240942406</v>
       </c>
       <c r="C4" t="n">
-        <v>3.589929838161907</v>
+        <v>3.589929838161883</v>
       </c>
       <c r="D4" t="n">
-        <v>3.92491611980608</v>
+        <v>3.924893536524882</v>
       </c>
       <c r="E4" t="n">
-        <v>3.782768716192677</v>
+        <v>3.782768716192671</v>
       </c>
       <c r="F4" t="n">
-        <v>3.867244782312856</v>
+        <v>3.867244782312845</v>
       </c>
       <c r="G4" t="n">
-        <v>3.835901429126725</v>
+        <v>3.835901429126727</v>
       </c>
       <c r="H4" t="n">
         <v>17.3488200055115</v>
       </c>
       <c r="I4" t="n">
-        <v>3.808255041672636</v>
+        <v>14.33776160048423</v>
       </c>
       <c r="J4" t="n">
-        <v>14.67965992838724</v>
+        <v>3.96001657777856</v>
       </c>
       <c r="K4" t="n">
-        <v>3.764629650955081</v>
+        <v>3.764629650955087</v>
       </c>
       <c r="L4" t="n">
-        <v>3.864860523997442</v>
+        <v>3.864860523997434</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.581912971063368</v>
+        <v>5.581912971063367</v>
       </c>
       <c r="C5" t="n">
-        <v>5.573720621387731</v>
+        <v>5.573720621387744</v>
       </c>
       <c r="D5" t="n">
-        <v>5.581920721857663</v>
+        <v>5.581920721857655</v>
       </c>
       <c r="E5" t="n">
-        <v>5.710682381505182</v>
+        <v>5.710682381505174</v>
       </c>
       <c r="F5" t="n">
-        <v>5.710682381505182</v>
+        <v>5.710682381505174</v>
       </c>
       <c r="G5" t="n">
-        <v>5.576656159247686</v>
+        <v>5.576656159247697</v>
       </c>
       <c r="H5" t="n">
-        <v>5.581912971063368</v>
+        <v>5.581912971063367</v>
       </c>
       <c r="I5" t="n">
-        <v>5.549009771793595</v>
+        <v>5.549009771793608</v>
       </c>
       <c r="J5" t="n">
-        <v>5.581912971063368</v>
+        <v>5.581912971063367</v>
       </c>
       <c r="K5" t="n">
-        <v>5.581912971063368</v>
+        <v>5.581912971063367</v>
       </c>
       <c r="L5" t="n">
-        <v>5.581912971063368</v>
+        <v>5.581912971063367</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.97842929806531</v>
+        <v>14.97842929806537</v>
       </c>
       <c r="C6" t="n">
-        <v>23.70347863067724</v>
+        <v>23.70347863085242</v>
       </c>
       <c r="D6" t="n">
-        <v>25.33400992373736</v>
+        <v>25.33400992373758</v>
       </c>
       <c r="E6" t="n">
-        <v>21.31654022975863</v>
+        <v>21.31654022975885</v>
       </c>
       <c r="F6" t="n">
-        <v>15.31384689161554</v>
+        <v>15.3138468916155</v>
       </c>
       <c r="G6" t="n">
-        <v>23.55024189556531</v>
+        <v>23.55024189556523</v>
       </c>
       <c r="H6" t="n">
-        <v>23.55549870737582</v>
+        <v>23.55549870737594</v>
       </c>
       <c r="I6" t="n">
-        <v>23.52259550811107</v>
+        <v>23.52259550811114</v>
       </c>
       <c r="J6" t="n">
-        <v>23.55718434501656</v>
+        <v>23.55718434501635</v>
       </c>
       <c r="K6" t="n">
-        <v>14.81910583025524</v>
+        <v>14.81910583025517</v>
       </c>
       <c r="L6" t="n">
-        <v>32.51496490661743</v>
+        <v>32.51496490661707</v>
       </c>
     </row>
     <row r="7">
@@ -2698,10 +2698,10 @@
         <v>473.9404836961292</v>
       </c>
       <c r="C7" t="n">
-        <v>604.5937741457612</v>
+        <v>604.5937741457611</v>
       </c>
       <c r="D7" t="n">
-        <v>604.6019698336443</v>
+        <v>604.6019698336444</v>
       </c>
       <c r="E7" t="n">
         <v>755.3496470798474</v>
@@ -2716,16 +2716,16 @@
         <v>604.601966495437</v>
       </c>
       <c r="I7" t="n">
-        <v>604.5690632961671</v>
+        <v>604.569063296167</v>
       </c>
       <c r="J7" t="n">
-        <v>604.601966495437</v>
+        <v>604.6019664954367</v>
       </c>
       <c r="K7" t="n">
-        <v>440.0758357937354</v>
+        <v>528.896191618301</v>
       </c>
       <c r="L7" t="n">
-        <v>604.601966495437</v>
+        <v>604.6019664954367</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.136485929409009</v>
+        <v>6.136485929409023</v>
       </c>
       <c r="C8" t="n">
-        <v>2.292375825571434</v>
+        <v>2.292375825571431</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3410098216763529</v>
+        <v>0.3410098216763676</v>
       </c>
       <c r="E8" t="n">
-        <v>1.99823028590564</v>
+        <v>1.998230285905676</v>
       </c>
       <c r="F8" t="n">
-        <v>1.99823028590564</v>
+        <v>1.998230285905676</v>
       </c>
       <c r="G8" t="n">
-        <v>3.198031927780582</v>
+        <v>3.198031927780589</v>
       </c>
       <c r="H8" t="n">
-        <v>2.138551910655163</v>
+        <v>2.138551910655164</v>
       </c>
       <c r="I8" t="n">
-        <v>1.99823028590564</v>
+        <v>1.998230285905676</v>
       </c>
       <c r="J8" t="n">
-        <v>5.068824263992415</v>
+        <v>5.068824263992408</v>
       </c>
       <c r="K8" t="n">
         <v>3.879185246874755</v>
       </c>
       <c r="L8" t="n">
-        <v>1.048414529840881</v>
+        <v>1.048414529840882</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.064827158708313</v>
+        <v>6.064827158708317</v>
       </c>
       <c r="C9" t="n">
-        <v>2.331482301811696</v>
+        <v>2.331482301811693</v>
       </c>
       <c r="D9" t="n">
-        <v>2.178835910991557</v>
+        <v>2.178835910991554</v>
       </c>
       <c r="E9" t="n">
-        <v>3.005361854898464</v>
+        <v>3.005361854898447</v>
       </c>
       <c r="F9" t="n">
-        <v>3.005361854898464</v>
+        <v>3.005361854898447</v>
       </c>
       <c r="G9" t="n">
-        <v>4.350943662329988</v>
+        <v>4.350943662329986</v>
       </c>
       <c r="H9" t="n">
-        <v>2.912147527689296</v>
+        <v>2.91214752768929</v>
       </c>
       <c r="I9" t="n">
-        <v>3.005361854898464</v>
+        <v>3.005361854898447</v>
       </c>
       <c r="J9" t="n">
-        <v>5.43675383568777</v>
+        <v>5.436753835687766</v>
       </c>
       <c r="K9" t="n">
-        <v>4.911165100490981</v>
+        <v>4.911165100490974</v>
       </c>
       <c r="L9" t="n">
-        <v>2.150081598785331</v>
+        <v>2.150081598785332</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35.07041894534263</v>
+        <v>35.07041894534262</v>
       </c>
       <c r="C2" t="n">
-        <v>10.80358955754099</v>
+        <v>10.803589557541</v>
       </c>
       <c r="D2" t="n">
-        <v>161.6318455833374</v>
+        <v>161.6318455833373</v>
       </c>
       <c r="E2" t="n">
-        <v>84.33259935649467</v>
+        <v>84.3325993564944</v>
       </c>
       <c r="F2" t="n">
-        <v>84.33259935649467</v>
+        <v>84.3325993564944</v>
       </c>
       <c r="G2" t="n">
-        <v>109.1565610745267</v>
+        <v>109.1565610745266</v>
       </c>
       <c r="H2" t="n">
-        <v>26.21492589959615</v>
+        <v>26.21492589959611</v>
       </c>
       <c r="I2" t="n">
-        <v>84.33259935649467</v>
+        <v>84.3325993564944</v>
       </c>
       <c r="J2" t="n">
-        <v>27.29215901810985</v>
+        <v>27.29215901810979</v>
       </c>
       <c r="K2" t="n">
-        <v>117.4641926360176</v>
+        <v>117.4641926360177</v>
       </c>
       <c r="L2" t="n">
-        <v>144.1270902073911</v>
+        <v>144.127090207391</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.257156831997257</v>
+        <v>2.257156831997276</v>
       </c>
       <c r="C3" t="n">
-        <v>1.552288011248236</v>
+        <v>1.552288011248241</v>
       </c>
       <c r="D3" t="n">
-        <v>2.257156831997257</v>
+        <v>2.257156831997276</v>
       </c>
       <c r="E3" t="n">
-        <v>2.541000639396962</v>
+        <v>2.541000639396966</v>
       </c>
       <c r="F3" t="n">
-        <v>2.541000639396963</v>
+        <v>2.541000639396964</v>
       </c>
       <c r="G3" t="n">
-        <v>2.251471462257092</v>
+        <v>2.251471462257042</v>
       </c>
       <c r="H3" t="n">
-        <v>2.257156831997258</v>
+        <v>2.257156831997277</v>
       </c>
       <c r="I3" t="n">
-        <v>2.221591973212597</v>
+        <v>2.221591973212581</v>
       </c>
       <c r="J3" t="n">
-        <v>2.257156831997258</v>
+        <v>2.257156831997277</v>
       </c>
       <c r="K3" t="n">
-        <v>2.257156831997258</v>
+        <v>2.257156831997276</v>
       </c>
       <c r="L3" t="n">
-        <v>2.257156831997258</v>
+        <v>2.257156831997277</v>
       </c>
     </row>
     <row r="4">
@@ -2971,34 +2971,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.19748389180995</v>
+        <v>4.197483891809963</v>
       </c>
       <c r="C4" t="n">
-        <v>3.92370691383918</v>
+        <v>3.923706913839178</v>
       </c>
       <c r="D4" t="n">
-        <v>4.281623678640794</v>
+        <v>14.79257946826736</v>
       </c>
       <c r="E4" t="n">
-        <v>4.110096392995433</v>
+        <v>4.11009639299542</v>
       </c>
       <c r="F4" t="n">
-        <v>4.218055504094957</v>
+        <v>4.218055504094965</v>
       </c>
       <c r="G4" t="n">
-        <v>14.44158108578818</v>
+        <v>4.191798522069792</v>
       </c>
       <c r="H4" t="n">
-        <v>17.24210069663389</v>
+        <v>17.24210069663384</v>
       </c>
       <c r="I4" t="n">
-        <v>14.41170159674368</v>
+        <v>14.41170159674365</v>
       </c>
       <c r="J4" t="n">
-        <v>4.308475289591504</v>
+        <v>14.77260229922035</v>
       </c>
       <c r="K4" t="n">
-        <v>4.160856175078586</v>
+        <v>4.160856175078595</v>
       </c>
       <c r="L4" t="n">
         <v>4.218801493164579</v>
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.812681038562382</v>
+        <v>5.812681038562385</v>
       </c>
       <c r="C5" t="n">
-        <v>5.803600313988238</v>
+        <v>5.803600313988242</v>
       </c>
       <c r="D5" t="n">
         <v>5.812687793931087</v>
       </c>
       <c r="E5" t="n">
-        <v>5.974111575622417</v>
+        <v>5.974111575622427</v>
       </c>
       <c r="F5" t="n">
-        <v>5.974111575622417</v>
+        <v>5.974111575622427</v>
       </c>
       <c r="G5" t="n">
-        <v>5.806995668822219</v>
+        <v>5.806995668822222</v>
       </c>
       <c r="H5" t="n">
-        <v>5.812681038562382</v>
+        <v>5.812681038562385</v>
       </c>
       <c r="I5" t="n">
-        <v>5.777116179777721</v>
+        <v>5.777116179777749</v>
       </c>
       <c r="J5" t="n">
-        <v>5.812681038562382</v>
+        <v>5.812681038562385</v>
       </c>
       <c r="K5" t="n">
-        <v>5.812681038562382</v>
+        <v>5.812681038562385</v>
       </c>
       <c r="L5" t="n">
-        <v>5.812681038562382</v>
+        <v>5.812681038562385</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.89269471022348</v>
+        <v>14.89269471022325</v>
       </c>
       <c r="C6" t="n">
-        <v>23.51077701903496</v>
+        <v>23.51077701885048</v>
       </c>
       <c r="D6" t="n">
-        <v>25.07944392097434</v>
+        <v>25.07944392097425</v>
       </c>
       <c r="E6" t="n">
-        <v>21.15672145753511</v>
+        <v>21.15672145753479</v>
       </c>
       <c r="F6" t="n">
-        <v>15.24209042352386</v>
+        <v>15.2420904235237</v>
       </c>
       <c r="G6" t="n">
-        <v>23.32424315630956</v>
+        <v>23.32424315630941</v>
       </c>
       <c r="H6" t="n">
-        <v>23.32992852603115</v>
+        <v>23.32992852603084</v>
       </c>
       <c r="I6" t="n">
-        <v>23.29436366726506</v>
+        <v>23.29436366726523</v>
       </c>
       <c r="J6" t="n">
-        <v>23.33158667951243</v>
+        <v>23.33158667951241</v>
       </c>
       <c r="K6" t="n">
-        <v>14.73596876048082</v>
+        <v>14.73596876048071</v>
       </c>
       <c r="L6" t="n">
-        <v>32.14332475278839</v>
+        <v>32.14332475278795</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>449.1491818118219</v>
+        <v>449.1491818118218</v>
       </c>
       <c r="C7" t="n">
         <v>572.9082688832428</v>
       </c>
       <c r="D7" t="n">
-        <v>572.9173539505416</v>
+        <v>572.9173539505417</v>
       </c>
       <c r="E7" t="n">
-        <v>715.7076307853393</v>
+        <v>715.7076307853392</v>
       </c>
       <c r="F7" t="n">
         <v>572.8817853755199</v>
       </c>
       <c r="G7" t="n">
-        <v>572.9116642380765</v>
+        <v>572.9116642380764</v>
       </c>
       <c r="H7" t="n">
-        <v>572.9173496078168</v>
+        <v>572.9173496078167</v>
       </c>
       <c r="I7" t="n">
         <v>572.8817847490326</v>
       </c>
       <c r="J7" t="n">
-        <v>572.9173496078168</v>
+        <v>572.9173496078167</v>
       </c>
       <c r="K7" t="n">
-        <v>417.071132687313</v>
+        <v>501.2055889382352</v>
       </c>
       <c r="L7" t="n">
-        <v>572.9173496078168</v>
+        <v>572.9173496078167</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.722303442687111</v>
+        <v>5.722303442687106</v>
       </c>
       <c r="C8" t="n">
-        <v>2.425590248705635</v>
+        <v>2.425590248705634</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.01356619512661769</v>
+        <v>-0.01356619512660481</v>
       </c>
       <c r="E8" t="n">
-        <v>2.18494090228818</v>
+        <v>2.184940902288195</v>
       </c>
       <c r="F8" t="n">
-        <v>2.18494090228818</v>
+        <v>2.184940902288194</v>
       </c>
       <c r="G8" t="n">
-        <v>3.084093376282087</v>
+        <v>3.084093376282091</v>
       </c>
       <c r="H8" t="n">
-        <v>3.357689154261917</v>
+        <v>3.357689154261926</v>
       </c>
       <c r="I8" t="n">
-        <v>2.18494090228818</v>
+        <v>2.184940902288195</v>
       </c>
       <c r="J8" t="n">
-        <v>5.731400655627994</v>
+        <v>5.731400655628015</v>
       </c>
       <c r="K8" t="n">
-        <v>3.578344631730239</v>
+        <v>3.578344631730203</v>
       </c>
       <c r="L8" t="n">
-        <v>0.280411064922307</v>
+        <v>0.2804110649223097</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.067438542619323</v>
+        <v>6.067438542619318</v>
       </c>
       <c r="C9" t="n">
-        <v>2.506039969136884</v>
+        <v>2.506039969136888</v>
       </c>
       <c r="D9" t="n">
-        <v>2.229881987283496</v>
+        <v>2.229881987283494</v>
       </c>
       <c r="E9" t="n">
-        <v>3.29309871369678</v>
+        <v>3.293098713696785</v>
       </c>
       <c r="F9" t="n">
-        <v>3.29309871369678</v>
+        <v>3.293098713696785</v>
       </c>
       <c r="G9" t="n">
-        <v>4.49607640557168</v>
+        <v>4.496076405571673</v>
       </c>
       <c r="H9" t="n">
-        <v>3.603318264090916</v>
+        <v>3.603318264090923</v>
       </c>
       <c r="I9" t="n">
-        <v>3.29309871369678</v>
+        <v>3.293098713696785</v>
       </c>
       <c r="J9" t="n">
-        <v>5.97619659608516</v>
+        <v>5.976196596085167</v>
       </c>
       <c r="K9" t="n">
-        <v>5.136972406986908</v>
+        <v>5.136972406986883</v>
       </c>
       <c r="L9" t="n">
-        <v>2.005379298856813</v>
+        <v>2.005379298856816</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.87238187873779</v>
+        <v>49.87238187873734</v>
       </c>
       <c r="C2" t="n">
-        <v>13.22920054393645</v>
+        <v>13.22920054393647</v>
       </c>
       <c r="D2" t="n">
-        <v>167.1066029508696</v>
+        <v>167.1066029508691</v>
       </c>
       <c r="E2" t="n">
-        <v>81.783508559591</v>
+        <v>81.78350855959064</v>
       </c>
       <c r="F2" t="n">
-        <v>81.783508559591</v>
+        <v>81.78350855959064</v>
       </c>
       <c r="G2" t="n">
-        <v>122.3209818880166</v>
+        <v>122.3209818880167</v>
       </c>
       <c r="H2" t="n">
-        <v>29.59368103826175</v>
+        <v>29.59368103826116</v>
       </c>
       <c r="I2" t="n">
-        <v>81.783508559591</v>
+        <v>81.78350855959064</v>
       </c>
       <c r="J2" t="n">
-        <v>27.29539434132911</v>
+        <v>27.29539434132884</v>
       </c>
       <c r="K2" t="n">
-        <v>125.8894019813275</v>
+        <v>125.8894019813268</v>
       </c>
       <c r="L2" t="n">
-        <v>170.5872615666002</v>
+        <v>170.5872615666</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.590139560024215</v>
+        <v>2.59013956002359</v>
       </c>
       <c r="C3" t="n">
-        <v>1.724411062321569</v>
+        <v>1.724411062321616</v>
       </c>
       <c r="D3" t="n">
-        <v>2.590139560024215</v>
+        <v>2.59013956002359</v>
       </c>
       <c r="E3" t="n">
-        <v>2.732208717930398</v>
+        <v>2.73220871793041</v>
       </c>
       <c r="F3" t="n">
-        <v>2.732208717930397</v>
+        <v>2.73220871793041</v>
       </c>
       <c r="G3" t="n">
-        <v>2.583940855381061</v>
+        <v>2.583940855380549</v>
       </c>
       <c r="H3" t="n">
-        <v>2.590139560024214</v>
+        <v>2.590139560023589</v>
       </c>
       <c r="I3" t="n">
-        <v>2.551810164095956</v>
+        <v>2.551810164095664</v>
       </c>
       <c r="J3" t="n">
-        <v>2.590139560024214</v>
+        <v>2.590139560023588</v>
       </c>
       <c r="K3" t="n">
-        <v>2.590139560024214</v>
+        <v>2.59013956002359</v>
       </c>
       <c r="L3" t="n">
-        <v>2.590139560024215</v>
+        <v>2.590139560023589</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15.50533634701683</v>
+        <v>15.50533634701669</v>
       </c>
       <c r="C4" t="n">
-        <v>4.510788079539939</v>
+        <v>4.51078807953995</v>
       </c>
       <c r="D4" t="n">
-        <v>4.905586019414178</v>
+        <v>4.905586019413776</v>
       </c>
       <c r="E4" t="n">
-        <v>4.649542899987135</v>
+        <v>4.649542899987158</v>
       </c>
       <c r="F4" t="n">
-        <v>4.833887347010084</v>
+        <v>4.833887347010107</v>
       </c>
       <c r="G4" t="n">
-        <v>15.49913764237349</v>
+        <v>15.49913764237333</v>
       </c>
       <c r="H4" t="n">
-        <v>18.30597116497043</v>
+        <v>4.806707359600702</v>
       </c>
       <c r="I4" t="n">
-        <v>4.792683764470013</v>
+        <v>15.46700695108825</v>
       </c>
       <c r="J4" t="n">
-        <v>15.88995988132809</v>
+        <v>4.958248831787166</v>
       </c>
       <c r="K4" t="n">
-        <v>4.806626349483263</v>
+        <v>4.806626349483127</v>
       </c>
       <c r="L4" t="n">
-        <v>4.850698441237145</v>
+        <v>4.850698441236482</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.311743976343259</v>
+        <v>6.311743976342886</v>
       </c>
       <c r="C5" t="n">
-        <v>6.301085188158646</v>
+        <v>6.301085188158662</v>
       </c>
       <c r="D5" t="n">
-        <v>6.311787224761435</v>
+        <v>6.311787224761038</v>
       </c>
       <c r="E5" t="n">
-        <v>6.43987977212652</v>
+        <v>6.439879772126533</v>
       </c>
       <c r="F5" t="n">
-        <v>6.43987977212652</v>
+        <v>6.439879772126533</v>
       </c>
       <c r="G5" t="n">
-        <v>6.30554527169989</v>
+        <v>6.305545271699606</v>
       </c>
       <c r="H5" t="n">
-        <v>6.311743976343259</v>
+        <v>6.311743976342886</v>
       </c>
       <c r="I5" t="n">
-        <v>6.273414580414667</v>
+        <v>6.273414580414683</v>
       </c>
       <c r="J5" t="n">
-        <v>6.311743976343259</v>
+        <v>6.311743976342886</v>
       </c>
       <c r="K5" t="n">
-        <v>6.311743976343259</v>
+        <v>6.311743976342886</v>
       </c>
       <c r="L5" t="n">
-        <v>6.311743976343259</v>
+        <v>6.311743976342886</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.59320405419932</v>
+        <v>15.59320405419923</v>
       </c>
       <c r="C6" t="n">
-        <v>24.59820014749058</v>
+        <v>24.59820014767095</v>
       </c>
       <c r="D6" t="n">
-        <v>26.28416875228908</v>
+        <v>26.28416875228899</v>
       </c>
       <c r="E6" t="n">
-        <v>22.13181631730031</v>
+        <v>22.13181631730034</v>
       </c>
       <c r="F6" t="n">
-        <v>15.9348386043237</v>
+        <v>15.93483860432374</v>
       </c>
       <c r="G6" t="n">
-        <v>24.44185855256615</v>
+        <v>24.44185855256617</v>
       </c>
       <c r="H6" t="n">
-        <v>24.44805725718176</v>
+        <v>24.44805725718155</v>
       </c>
       <c r="I6" t="n">
-        <v>24.40972786128093</v>
+        <v>24.40972786128092</v>
       </c>
       <c r="J6" t="n">
-        <v>24.44979748018786</v>
+        <v>24.4497974801874</v>
       </c>
       <c r="K6" t="n">
-        <v>15.42872061038021</v>
+        <v>15.42872061037989</v>
       </c>
       <c r="L6" t="n">
-        <v>33.69769185024648</v>
+        <v>33.69769185024656</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>449.2422140899213</v>
+        <v>449.242214089921</v>
       </c>
       <c r="C7" t="n">
         <v>573.0134919163082</v>
       </c>
       <c r="D7" t="n">
-        <v>573.024155685458</v>
+        <v>573.0241556854583</v>
       </c>
       <c r="E7" t="n">
-        <v>715.8275568187091</v>
+        <v>715.8275568187094</v>
       </c>
       <c r="F7" t="n">
         <v>572.9858219128056</v>
       </c>
       <c r="G7" t="n">
-        <v>573.0179519998495</v>
+        <v>573.0179519998494</v>
       </c>
       <c r="H7" t="n">
-        <v>573.0241507044921</v>
+        <v>573.0241507044917</v>
       </c>
       <c r="I7" t="n">
-        <v>572.9858213085635</v>
+        <v>572.9858213085636</v>
       </c>
       <c r="J7" t="n">
-        <v>573.0241507044921</v>
+        <v>573.0241507044917</v>
       </c>
       <c r="K7" t="n">
-        <v>498.3946520230532</v>
+        <v>501.3044125957954</v>
       </c>
       <c r="L7" t="n">
-        <v>573.0241507044921</v>
+        <v>573.0241507044917</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.729994341146719</v>
+        <v>5.729994341146609</v>
       </c>
       <c r="C8" t="n">
-        <v>2.638148879980268</v>
+        <v>2.638148879980274</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2626302358635129</v>
+        <v>0.2626302358633855</v>
       </c>
       <c r="E8" t="n">
-        <v>2.668130172169658</v>
+        <v>2.668130172169664</v>
       </c>
       <c r="F8" t="n">
-        <v>2.668130172169658</v>
+        <v>2.668130172169664</v>
       </c>
       <c r="G8" t="n">
-        <v>3.152184421372702</v>
+        <v>3.152184421372529</v>
       </c>
       <c r="H8" t="n">
-        <v>3.694548571198606</v>
+        <v>3.69454857119845</v>
       </c>
       <c r="I8" t="n">
-        <v>2.668130172169658</v>
+        <v>2.668130172169664</v>
       </c>
       <c r="J8" t="n">
-        <v>6.365027782896463</v>
+        <v>6.365027782896469</v>
       </c>
       <c r="K8" t="n">
-        <v>3.836023347247358</v>
+        <v>3.836023347247229</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03475966124538757</v>
+        <v>0.03475966124545218</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.277044351908943</v>
+        <v>6.277044351908952</v>
       </c>
       <c r="C9" t="n">
-        <v>2.748437571338563</v>
+        <v>2.748437571338565</v>
       </c>
       <c r="D9" t="n">
-        <v>2.578676992638496</v>
+        <v>2.578676992638726</v>
       </c>
       <c r="E9" t="n">
-        <v>3.732841117336583</v>
+        <v>3.73284111733659</v>
       </c>
       <c r="F9" t="n">
-        <v>3.732841117336583</v>
+        <v>3.73284111733659</v>
       </c>
       <c r="G9" t="n">
-        <v>4.742880301658634</v>
+        <v>4.742880301658415</v>
       </c>
       <c r="H9" t="n">
-        <v>3.976883276782404</v>
+        <v>3.976883276782307</v>
       </c>
       <c r="I9" t="n">
-        <v>3.732841117336583</v>
+        <v>3.732841117336589</v>
       </c>
       <c r="J9" t="n">
-        <v>6.599836626752589</v>
+        <v>6.59983662675262</v>
       </c>
       <c r="K9" t="n">
-        <v>5.508594290934899</v>
+        <v>5.508594290934737</v>
       </c>
       <c r="L9" t="n">
-        <v>2.086040031511224</v>
+        <v>2.086040031511005</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27.92279450361439</v>
+        <v>27.92279450361436</v>
       </c>
       <c r="C2" t="n">
-        <v>9.112028749451873</v>
+        <v>9.112028749451854</v>
       </c>
       <c r="D2" t="n">
-        <v>156.5517261016848</v>
+        <v>156.551726101685</v>
       </c>
       <c r="E2" t="n">
-        <v>95.01127686590084</v>
+        <v>95.01127686590038</v>
       </c>
       <c r="F2" t="n">
-        <v>95.01127686590084</v>
+        <v>95.01127686590038</v>
       </c>
       <c r="G2" t="n">
-        <v>115.5877179342976</v>
+        <v>115.5877179342894</v>
       </c>
       <c r="H2" t="n">
-        <v>63.14788813654506</v>
+        <v>63.1478881365451</v>
       </c>
       <c r="I2" t="n">
-        <v>95.01127686590084</v>
+        <v>95.01127686590038</v>
       </c>
       <c r="J2" t="n">
-        <v>26.16015873180598</v>
+        <v>26.16015873180601</v>
       </c>
       <c r="K2" t="n">
-        <v>107.2834037388485</v>
+        <v>107.2834037388487</v>
       </c>
       <c r="L2" t="n">
-        <v>102.642282714339</v>
+        <v>102.6422827143389</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.129910497919193</v>
+        <v>2.129910497919174</v>
       </c>
       <c r="C3" t="n">
-        <v>1.342549017976163</v>
+        <v>1.342549017976147</v>
       </c>
       <c r="D3" t="n">
-        <v>2.129910497919192</v>
+        <v>2.129910497919173</v>
       </c>
       <c r="E3" t="n">
-        <v>2.385669866726611</v>
+        <v>2.385669866726594</v>
       </c>
       <c r="F3" t="n">
-        <v>2.385669866726611</v>
+        <v>2.385669866726593</v>
       </c>
       <c r="G3" t="n">
-        <v>2.124563077956134</v>
+        <v>2.12456307795607</v>
       </c>
       <c r="H3" t="n">
-        <v>2.129910497919192</v>
+        <v>2.129910497919173</v>
       </c>
       <c r="I3" t="n">
-        <v>2.096447617884717</v>
+        <v>2.096447617884698</v>
       </c>
       <c r="J3" t="n">
-        <v>2.129910497919192</v>
+        <v>2.129910497919173</v>
       </c>
       <c r="K3" t="n">
-        <v>2.129910497919193</v>
+        <v>2.129910497919174</v>
       </c>
       <c r="L3" t="n">
-        <v>2.129910497919192</v>
+        <v>2.129910497919173</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.117425334880606</v>
+        <v>4.117425334880717</v>
       </c>
       <c r="C4" t="n">
-        <v>3.817333099642658</v>
+        <v>3.817333099642657</v>
       </c>
       <c r="D4" t="n">
-        <v>4.192270454096806</v>
+        <v>4.192270454096779</v>
       </c>
       <c r="E4" t="n">
-        <v>4.047944115092953</v>
+        <v>4.047944115092919</v>
       </c>
       <c r="F4" t="n">
-        <v>4.145085559051446</v>
+        <v>4.145085559051414</v>
       </c>
       <c r="G4" t="n">
-        <v>14.8672398877107</v>
+        <v>4.112077914917529</v>
       </c>
       <c r="H4" t="n">
-        <v>17.84506560464338</v>
+        <v>17.84506560464337</v>
       </c>
       <c r="I4" t="n">
-        <v>14.83912442763936</v>
+        <v>4.083962454846159</v>
       </c>
       <c r="J4" t="n">
-        <v>15.19914683182536</v>
+        <v>4.233317033790878</v>
       </c>
       <c r="K4" t="n">
-        <v>4.049138809679144</v>
+        <v>4.049138809679205</v>
       </c>
       <c r="L4" t="n">
-        <v>4.132735730161126</v>
+        <v>4.132735730161131</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.916882249918391</v>
+        <v>5.916882249918407</v>
       </c>
       <c r="C5" t="n">
-        <v>5.90795369412073</v>
+        <v>5.907953694120638</v>
       </c>
       <c r="D5" t="n">
-        <v>5.916901162404836</v>
+        <v>5.916901162404889</v>
       </c>
       <c r="E5" t="n">
-        <v>6.072600380614414</v>
+        <v>6.072600380614373</v>
       </c>
       <c r="F5" t="n">
-        <v>6.072600380614414</v>
+        <v>6.072600380614373</v>
       </c>
       <c r="G5" t="n">
-        <v>5.911534829955237</v>
+        <v>5.911534829955238</v>
       </c>
       <c r="H5" t="n">
-        <v>5.916882249918391</v>
+        <v>5.916882249918407</v>
       </c>
       <c r="I5" t="n">
-        <v>5.883419369883861</v>
+        <v>5.883419369883836</v>
       </c>
       <c r="J5" t="n">
-        <v>5.916882249918391</v>
+        <v>5.916882249918407</v>
       </c>
       <c r="K5" t="n">
-        <v>5.916882249918391</v>
+        <v>5.916882249918407</v>
       </c>
       <c r="L5" t="n">
-        <v>5.916882249918391</v>
+        <v>5.916882249918407</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.41784388002856</v>
+        <v>15.41784388002857</v>
       </c>
       <c r="C6" t="n">
-        <v>24.4022617640934</v>
+        <v>24.40226176391519</v>
       </c>
       <c r="D6" t="n">
-        <v>26.05569313279773</v>
+        <v>26.05569313279766</v>
       </c>
       <c r="E6" t="n">
-        <v>21.94879120777642</v>
+        <v>21.9487912077763</v>
       </c>
       <c r="F6" t="n">
-        <v>15.77651603283805</v>
+        <v>15.77651603283795</v>
       </c>
       <c r="G6" t="n">
-        <v>24.2233564886248</v>
+        <v>24.22335648862481</v>
       </c>
       <c r="H6" t="n">
-        <v>24.22870390857418</v>
+        <v>24.22870390857408</v>
       </c>
       <c r="I6" t="n">
-        <v>24.19524102855337</v>
+        <v>24.19524102855328</v>
       </c>
       <c r="J6" t="n">
-        <v>24.23043549197607</v>
+        <v>24.23043549197602</v>
       </c>
       <c r="K6" t="n">
-        <v>15.25417763147393</v>
+        <v>15.254177631474</v>
       </c>
       <c r="L6" t="n">
-        <v>33.43238395815016</v>
+        <v>33.43238395814993</v>
       </c>
     </row>
     <row r="7">
@@ -3886,34 +3886,34 @@
         <v>474.7405673041961</v>
       </c>
       <c r="C7" t="n">
-        <v>605.5946237421433</v>
+        <v>605.594623742143</v>
       </c>
       <c r="D7" t="n">
         <v>605.6035564905264</v>
       </c>
       <c r="E7" t="n">
-        <v>756.583203650463</v>
+        <v>756.5832036504629</v>
       </c>
       <c r="F7" t="n">
-        <v>605.5700898205516</v>
+        <v>605.5700898205515</v>
       </c>
       <c r="G7" t="n">
-        <v>605.5982048779777</v>
+        <v>605.5982048779775</v>
       </c>
       <c r="H7" t="n">
-        <v>605.6035522979414</v>
+        <v>605.6035522979413</v>
       </c>
       <c r="I7" t="n">
-        <v>605.5700894179065</v>
+        <v>605.5700894179062</v>
       </c>
       <c r="J7" t="n">
-        <v>605.6035522979414</v>
+        <v>605.6035522979413</v>
       </c>
       <c r="K7" t="n">
-        <v>529.7810266173359</v>
+        <v>529.7810266173357</v>
       </c>
       <c r="L7" t="n">
-        <v>605.6035522979414</v>
+        <v>605.6035522979413</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.830382828617778</v>
+        <v>5.83038282861782</v>
       </c>
       <c r="C8" t="n">
-        <v>2.404762038691502</v>
+        <v>2.404762038691481</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1875378020389893</v>
+        <v>0.1875378020389782</v>
       </c>
       <c r="E8" t="n">
-        <v>1.882764442347551</v>
+        <v>1.882764442347532</v>
       </c>
       <c r="F8" t="n">
-        <v>1.882764442347551</v>
+        <v>1.882764442347532</v>
       </c>
       <c r="G8" t="n">
-        <v>2.942894290939779</v>
+        <v>2.9428942909398</v>
       </c>
       <c r="H8" t="n">
-        <v>2.510561439532073</v>
+        <v>2.5105614395321</v>
       </c>
       <c r="I8" t="n">
-        <v>1.882764442347551</v>
+        <v>1.882764442347532</v>
       </c>
       <c r="J8" t="n">
-        <v>5.552182594351152</v>
+        <v>5.552182594351112</v>
       </c>
       <c r="K8" t="n">
-        <v>3.686744059292589</v>
+        <v>3.686744059292614</v>
       </c>
       <c r="L8" t="n">
-        <v>1.138609147658103</v>
+        <v>1.138609147658111</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.058045209845711</v>
+        <v>6.058045209845758</v>
       </c>
       <c r="C9" t="n">
-        <v>2.457421509414459</v>
+        <v>2.457421509414446</v>
       </c>
       <c r="D9" t="n">
-        <v>2.241580912581529</v>
+        <v>2.241580912581536</v>
       </c>
       <c r="E9" t="n">
-        <v>3.076190035863631</v>
+        <v>3.076190035863617</v>
       </c>
       <c r="F9" t="n">
-        <v>3.076190035863631</v>
+        <v>3.076190035863617</v>
       </c>
       <c r="G9" t="n">
-        <v>4.363185707745478</v>
+        <v>4.363185707745463</v>
       </c>
       <c r="H9" t="n">
-        <v>3.188762850748781</v>
+        <v>3.18876285074882</v>
       </c>
       <c r="I9" t="n">
-        <v>3.076190035863631</v>
+        <v>3.076190035863617</v>
       </c>
       <c r="J9" t="n">
-        <v>5.767764340633242</v>
+        <v>5.767764340633243</v>
       </c>
       <c r="K9" t="n">
-        <v>5.023161433124679</v>
+        <v>5.023161433124689</v>
       </c>
       <c r="L9" t="n">
-        <v>2.279879167122171</v>
+        <v>2.279879167122175</v>
       </c>
     </row>
   </sheetData>
@@ -4079,13 +4079,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>94.47615425993233</v>
+        <v>94.47615425993268</v>
       </c>
       <c r="C2" t="n">
-        <v>14.6212954776009</v>
+        <v>14.62129547760082</v>
       </c>
       <c r="D2" t="n">
-        <v>165.3018472133257</v>
+        <v>165.3018472133245</v>
       </c>
       <c r="E2" t="n">
         <v>112.8914756155039</v>
@@ -4094,22 +4094,22 @@
         <v>112.8914756155039</v>
       </c>
       <c r="G2" t="n">
-        <v>144.9343864847964</v>
+        <v>144.9343864847956</v>
       </c>
       <c r="H2" t="n">
-        <v>30.87942547582463</v>
+        <v>30.87942547582432</v>
       </c>
       <c r="I2" t="n">
         <v>112.8914756155039</v>
       </c>
       <c r="J2" t="n">
-        <v>45.44580244765925</v>
+        <v>45.4458024476588</v>
       </c>
       <c r="K2" t="n">
-        <v>143.1627779140661</v>
+        <v>143.1627779140655</v>
       </c>
       <c r="L2" t="n">
-        <v>149.592145780105</v>
+        <v>149.5921457801049</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.986798861756264</v>
+        <v>2.986798861755808</v>
       </c>
       <c r="C3" t="n">
-        <v>2.078066629428659</v>
+        <v>2.078066629428631</v>
       </c>
       <c r="D3" t="n">
-        <v>2.986798861756265</v>
+        <v>2.986798861755808</v>
       </c>
       <c r="E3" t="n">
-        <v>3.416877506976793</v>
+        <v>3.41687750697674</v>
       </c>
       <c r="F3" t="n">
-        <v>3.416877506976793</v>
+        <v>3.41687750697674</v>
       </c>
       <c r="G3" t="n">
-        <v>2.982540506961461</v>
+        <v>2.982540506961168</v>
       </c>
       <c r="H3" t="n">
-        <v>2.986798861756265</v>
+        <v>2.986798861755808</v>
       </c>
       <c r="I3" t="n">
-        <v>2.961121520051774</v>
+        <v>2.961121520051788</v>
       </c>
       <c r="J3" t="n">
-        <v>2.986798861756265</v>
+        <v>2.986798861755809</v>
       </c>
       <c r="K3" t="n">
-        <v>2.986798861756265</v>
+        <v>2.986798861755809</v>
       </c>
       <c r="L3" t="n">
-        <v>2.986798861756265</v>
+        <v>2.986798861755808</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.3881723769301</v>
+        <v>16.40066640990493</v>
       </c>
       <c r="C4" t="n">
-        <v>5.005065956202816</v>
+        <v>5.005065956202748</v>
       </c>
       <c r="D4" t="n">
-        <v>5.395918220139671</v>
+        <v>5.395939673708021</v>
       </c>
       <c r="E4" t="n">
-        <v>5.246795950921505</v>
+        <v>5.246795950921561</v>
       </c>
       <c r="F4" t="n">
-        <v>5.416488208203369</v>
+        <v>5.416488208203337</v>
       </c>
       <c r="G4" t="n">
-        <v>5.38391402213512</v>
+        <v>5.383914022134438</v>
       </c>
       <c r="H4" t="n">
-        <v>19.21111848370757</v>
+        <v>19.21111848370874</v>
       </c>
       <c r="I4" t="n">
-        <v>16.37498906820113</v>
+        <v>16.37498906820077</v>
       </c>
       <c r="J4" t="n">
-        <v>16.82731370036025</v>
+        <v>5.523512557256933</v>
       </c>
       <c r="K4" t="n">
-        <v>5.354177170623376</v>
+        <v>5.354177170623339</v>
       </c>
       <c r="L4" t="n">
-        <v>5.381122009888959</v>
+        <v>5.381122009888426</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.076609150731234</v>
+        <v>7.07660915073093</v>
       </c>
       <c r="C5" t="n">
-        <v>7.065546963787649</v>
+        <v>7.065546963787636</v>
       </c>
       <c r="D5" t="n">
-        <v>7.076651960893127</v>
+        <v>7.076651960892481</v>
       </c>
       <c r="E5" t="n">
-        <v>7.290833050467499</v>
+        <v>7.290833050467466</v>
       </c>
       <c r="F5" t="n">
-        <v>7.290833050467499</v>
+        <v>7.290833050467466</v>
       </c>
       <c r="G5" t="n">
-        <v>7.072350795936422</v>
+        <v>7.072350795936351</v>
       </c>
       <c r="H5" t="n">
-        <v>7.076609150731234</v>
+        <v>7.07660915073093</v>
       </c>
       <c r="I5" t="n">
-        <v>7.050931809026953</v>
+        <v>7.050931809026981</v>
       </c>
       <c r="J5" t="n">
-        <v>7.076609150731234</v>
+        <v>7.07660915073093</v>
       </c>
       <c r="K5" t="n">
-        <v>7.076609150731234</v>
+        <v>7.07660915073093</v>
       </c>
       <c r="L5" t="n">
-        <v>7.076609150731234</v>
+        <v>7.07660915073093</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.57761350638173</v>
+        <v>16.57761350638134</v>
       </c>
       <c r="C6" t="n">
-        <v>26.11306490412315</v>
+        <v>26.11306490412299</v>
       </c>
       <c r="D6" t="n">
-        <v>27.82469193713931</v>
+        <v>27.82469193713795</v>
       </c>
       <c r="E6" t="n">
-        <v>23.52636379364601</v>
+        <v>23.52636379364616</v>
       </c>
       <c r="F6" t="n">
-        <v>16.99030898860052</v>
+        <v>16.99030898860049</v>
       </c>
       <c r="G6" t="n">
-        <v>25.88881276266545</v>
+        <v>25.88881276266438</v>
       </c>
       <c r="H6" t="n">
-        <v>25.89307111739033</v>
+        <v>25.89307111738921</v>
       </c>
       <c r="I6" t="n">
-        <v>25.86739377575585</v>
+        <v>25.86739377575592</v>
       </c>
       <c r="J6" t="n">
-        <v>25.89490186217034</v>
+        <v>25.89490186216954</v>
       </c>
       <c r="K6" t="n">
-        <v>16.4045740988218</v>
+        <v>16.40457409882112</v>
       </c>
       <c r="L6" t="n">
-        <v>35.62384552998171</v>
+        <v>35.62384552998078</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>451.1537084978199</v>
+        <v>451.1537084978189</v>
       </c>
       <c r="C7" t="n">
-        <v>575.3814517770429</v>
+        <v>575.3814517770428</v>
       </c>
       <c r="D7" t="n">
-        <v>575.3925198517811</v>
+        <v>575.3925198517805</v>
       </c>
       <c r="E7" t="n">
         <v>718.7357905442969</v>
       </c>
       <c r="F7" t="n">
-        <v>575.3668377261716</v>
+        <v>575.3668377261715</v>
       </c>
       <c r="G7" t="n">
-        <v>575.3882556091926</v>
+        <v>575.388255609192</v>
       </c>
       <c r="H7" t="n">
-        <v>575.3925139639881</v>
+        <v>575.3925139639867</v>
       </c>
       <c r="I7" t="n">
-        <v>575.366836622282</v>
+        <v>575.3668366222819</v>
       </c>
       <c r="J7" t="n">
-        <v>575.3925139639881</v>
+        <v>575.3925139639867</v>
       </c>
       <c r="K7" t="n">
-        <v>503.4080646298203</v>
+        <v>418.9536798077611</v>
       </c>
       <c r="L7" t="n">
-        <v>575.3925139639881</v>
+        <v>575.3925139639867</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.474204910402205</v>
+        <v>5.474204910401818</v>
       </c>
       <c r="C8" t="n">
-        <v>2.864352795601272</v>
+        <v>2.864352795601274</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6985755457562313</v>
+        <v>0.698575545755953</v>
       </c>
       <c r="E8" t="n">
-        <v>2.347063841854987</v>
+        <v>2.34706384185497</v>
       </c>
       <c r="F8" t="n">
-        <v>2.347063841854987</v>
+        <v>2.34706384185497</v>
       </c>
       <c r="G8" t="n">
-        <v>3.010467050980984</v>
+        <v>3.01046705098069</v>
       </c>
       <c r="H8" t="n">
-        <v>4.057943857052825</v>
+        <v>4.057943857052602</v>
       </c>
       <c r="I8" t="n">
-        <v>2.347063841854987</v>
+        <v>2.34706384185497</v>
       </c>
       <c r="J8" t="n">
-        <v>6.390337957026277</v>
+        <v>6.390337957025872</v>
       </c>
       <c r="K8" t="n">
-        <v>4.001781940910777</v>
+        <v>4.001781940910357</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7839670631406473</v>
+        <v>0.7839670631405261</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.631416719258269</v>
+        <v>6.631416719258008</v>
       </c>
       <c r="C9" t="n">
-        <v>2.987953854954183</v>
+        <v>2.987953854954178</v>
       </c>
       <c r="D9" t="n">
-        <v>2.980098231977754</v>
+        <v>2.980098231977601</v>
       </c>
       <c r="E9" t="n">
         <v>3.848068382140049</v>
       </c>
       <c r="F9" t="n">
-        <v>3.848068382140048</v>
+        <v>3.848068382140049</v>
       </c>
       <c r="G9" t="n">
-        <v>4.910364891463447</v>
+        <v>4.910364891463153</v>
       </c>
       <c r="H9" t="n">
-        <v>4.34877563398063</v>
+        <v>4.348775633980381</v>
       </c>
       <c r="I9" t="n">
-        <v>3.848068382140048</v>
+        <v>3.848068382140049</v>
       </c>
       <c r="J9" t="n">
-        <v>6.865448326094843</v>
+        <v>6.865448326094815</v>
       </c>
       <c r="K9" t="n">
-        <v>5.911690313195695</v>
+        <v>5.911690313195545</v>
       </c>
       <c r="L9" t="n">
-        <v>2.565898129353228</v>
+        <v>2.565898129353105</v>
       </c>
     </row>
   </sheetData>
@@ -4478,34 +4478,34 @@
         <v>77.95692245052979</v>
       </c>
       <c r="C2" t="n">
-        <v>15.6405412864924</v>
+        <v>15.64054128649225</v>
       </c>
       <c r="D2" t="n">
-        <v>164.1969725023378</v>
+        <v>164.1969725023377</v>
       </c>
       <c r="E2" t="n">
-        <v>98.32662903127613</v>
+        <v>98.3266290312759</v>
       </c>
       <c r="F2" t="n">
-        <v>98.32662903127613</v>
+        <v>98.3266290312759</v>
       </c>
       <c r="G2" t="n">
-        <v>141.2246770421169</v>
+        <v>141.2246770421164</v>
       </c>
       <c r="H2" t="n">
-        <v>33.06448564581407</v>
+        <v>33.06448564581402</v>
       </c>
       <c r="I2" t="n">
-        <v>98.32662903127613</v>
+        <v>98.3266290312759</v>
       </c>
       <c r="J2" t="n">
-        <v>51.94323437294607</v>
+        <v>51.94323437294582</v>
       </c>
       <c r="K2" t="n">
-        <v>139.9507037893321</v>
+        <v>139.9507037893323</v>
       </c>
       <c r="L2" t="n">
-        <v>169.2013673112985</v>
+        <v>169.2013673112987</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.631142058495112</v>
+        <v>3.631142058495199</v>
       </c>
       <c r="C3" t="n">
-        <v>2.527819714366497</v>
+        <v>2.527819714366461</v>
       </c>
       <c r="D3" t="n">
-        <v>3.631142058495112</v>
+        <v>3.631142058495199</v>
       </c>
       <c r="E3" t="n">
-        <v>3.684077837315624</v>
+        <v>3.684077837315521</v>
       </c>
       <c r="F3" t="n">
-        <v>3.684077837315628</v>
+        <v>3.684077837315522</v>
       </c>
       <c r="G3" t="n">
-        <v>3.626500728631459</v>
+        <v>3.626500728631453</v>
       </c>
       <c r="H3" t="n">
-        <v>3.631142058495111</v>
+        <v>3.631142058495199</v>
       </c>
       <c r="I3" t="n">
-        <v>3.60385794905424</v>
+        <v>3.603857949054109</v>
       </c>
       <c r="J3" t="n">
-        <v>3.631142058495114</v>
+        <v>3.631142058495199</v>
       </c>
       <c r="K3" t="n">
-        <v>3.631142058495112</v>
+        <v>3.631142058495199</v>
       </c>
       <c r="L3" t="n">
-        <v>3.631142058495112</v>
+        <v>3.631142058495199</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.433214588915487</v>
+        <v>18.11520537703518</v>
       </c>
       <c r="C4" t="n">
-        <v>6.035584997752442</v>
+        <v>6.03558499775244</v>
       </c>
       <c r="D4" t="n">
-        <v>6.472160908187115</v>
+        <v>6.472132791290917</v>
       </c>
       <c r="E4" t="n">
-        <v>6.146552778001792</v>
+        <v>6.146552778001742</v>
       </c>
       <c r="F4" t="n">
-        <v>6.437664579807028</v>
+        <v>6.437664579806995</v>
       </c>
       <c r="G4" t="n">
-        <v>18.11056404717099</v>
+        <v>6.4285732590518</v>
       </c>
       <c r="H4" t="n">
-        <v>20.96050456394189</v>
+        <v>20.96050456394219</v>
       </c>
       <c r="I4" t="n">
-        <v>18.08792126759393</v>
+        <v>6.405930479474645</v>
       </c>
       <c r="J4" t="n">
-        <v>6.626014234243804</v>
+        <v>18.64012658735357</v>
       </c>
       <c r="K4" t="n">
-        <v>6.418486522548708</v>
+        <v>6.418486522548697</v>
       </c>
       <c r="L4" t="n">
-        <v>6.432347975022391</v>
+        <v>6.43234797502235</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.892991792739809</v>
+        <v>7.892991792739802</v>
       </c>
       <c r="C5" t="n">
-        <v>7.88026165119469</v>
+        <v>7.880261651194649</v>
       </c>
       <c r="D5" t="n">
-        <v>7.893077498943934</v>
+        <v>7.89307749894455</v>
       </c>
       <c r="E5" t="n">
-        <v>8.009077541860337</v>
+        <v>8.009077541860281</v>
       </c>
       <c r="F5" t="n">
-        <v>8.009077541860337</v>
+        <v>8.009077541860281</v>
       </c>
       <c r="G5" t="n">
-        <v>7.888350462876069</v>
+        <v>7.888350462876381</v>
       </c>
       <c r="H5" t="n">
-        <v>7.892991792739809</v>
+        <v>7.892991792739802</v>
       </c>
       <c r="I5" t="n">
-        <v>7.865707683298995</v>
+        <v>7.865707683298948</v>
       </c>
       <c r="J5" t="n">
-        <v>7.892991792739809</v>
+        <v>7.892991792739802</v>
       </c>
       <c r="K5" t="n">
-        <v>7.892991792739809</v>
+        <v>7.892991792739802</v>
       </c>
       <c r="L5" t="n">
-        <v>7.892991792739809</v>
+        <v>7.892991792739802</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.75850396322829</v>
+        <v>17.75850396322828</v>
       </c>
       <c r="C6" t="n">
-        <v>27.88156464555097</v>
+        <v>27.88156464531718</v>
       </c>
       <c r="D6" t="n">
-        <v>29.82832772411477</v>
+        <v>29.82832772411408</v>
       </c>
       <c r="E6" t="n">
-        <v>25.11829294054893</v>
+        <v>25.1182929405482</v>
       </c>
       <c r="F6" t="n">
-        <v>18.13358214680014</v>
+        <v>18.13358214679991</v>
       </c>
       <c r="G6" t="n">
-        <v>27.75076381216632</v>
+        <v>27.75076381216597</v>
       </c>
       <c r="H6" t="n">
-        <v>27.75540514194834</v>
+        <v>27.75540514194799</v>
       </c>
       <c r="I6" t="n">
-        <v>27.72812103258901</v>
+        <v>27.72812103258859</v>
       </c>
       <c r="J6" t="n">
-        <v>27.75736980116694</v>
+        <v>27.7573698011666</v>
       </c>
       <c r="K6" t="n">
-        <v>17.57280639232764</v>
+        <v>17.57280639232736</v>
       </c>
       <c r="L6" t="n">
-        <v>38.19800433418741</v>
+        <v>38.19800433418702</v>
       </c>
     </row>
     <row r="7">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>451.1819385357653</v>
+        <v>451.1819385357656</v>
       </c>
       <c r="C7" t="n">
         <v>575.3858401419777</v>
@@ -4684,28 +4684,28 @@
         <v>575.3985765351977</v>
       </c>
       <c r="E7" t="n">
-        <v>718.7146523022865</v>
+        <v>718.7146523022864</v>
       </c>
       <c r="F7" t="n">
-        <v>575.3712871804785</v>
+        <v>575.3712871804784</v>
       </c>
       <c r="G7" t="n">
         <v>575.393928953659</v>
       </c>
       <c r="H7" t="n">
-        <v>575.3985702835223</v>
+        <v>575.3985702835226</v>
       </c>
       <c r="I7" t="n">
-        <v>575.3712861740815</v>
+        <v>575.3712861740814</v>
       </c>
       <c r="J7" t="n">
-        <v>575.3985702835223</v>
+        <v>575.3985702835226</v>
       </c>
       <c r="K7" t="n">
-        <v>500.5069895959564</v>
+        <v>500.5069895959569</v>
       </c>
       <c r="L7" t="n">
-        <v>575.3985702835223</v>
+        <v>575.3985702835226</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.503339731785579</v>
+        <v>7.503339731785696</v>
       </c>
       <c r="C8" t="n">
-        <v>3.299633128646271</v>
+        <v>3.299633128646256</v>
       </c>
       <c r="D8" t="n">
-        <v>1.375133153887902</v>
+        <v>1.375133153888022</v>
       </c>
       <c r="E8" t="n">
-        <v>3.385313702186482</v>
+        <v>3.385313702186429</v>
       </c>
       <c r="F8" t="n">
-        <v>3.385313702186482</v>
+        <v>3.385313702186429</v>
       </c>
       <c r="G8" t="n">
-        <v>3.798103086599729</v>
+        <v>3.798103086599628</v>
       </c>
       <c r="H8" t="n">
-        <v>4.660097625465943</v>
+        <v>4.660097625466089</v>
       </c>
       <c r="I8" t="n">
-        <v>3.385313702186482</v>
+        <v>3.385313702186429</v>
       </c>
       <c r="J8" t="n">
-        <v>7.366923565426212</v>
+        <v>7.366923565426379</v>
       </c>
       <c r="K8" t="n">
-        <v>4.71453432002065</v>
+        <v>4.714534320020773</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8421129430806072</v>
+        <v>0.8421129430805915</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.402375140085176</v>
+        <v>8.402375140085297</v>
       </c>
       <c r="C9" t="n">
-        <v>3.429284188200922</v>
+        <v>3.42928418820091</v>
       </c>
       <c r="D9" t="n">
-        <v>3.629217868485094</v>
+        <v>3.629217868485247</v>
       </c>
       <c r="E9" t="n">
-        <v>4.665547044131785</v>
+        <v>4.665547044131761</v>
       </c>
       <c r="F9" t="n">
-        <v>4.665547044131787</v>
+        <v>4.665547044131761</v>
       </c>
       <c r="G9" t="n">
-        <v>5.633654965561086</v>
+        <v>5.633654965561147</v>
       </c>
       <c r="H9" t="n">
-        <v>4.967631658976138</v>
+        <v>4.967631658976173</v>
       </c>
       <c r="I9" t="n">
-        <v>4.665547044131785</v>
+        <v>4.665547044131761</v>
       </c>
       <c r="J9" t="n">
-        <v>7.912470010644483</v>
+        <v>7.912470010644649</v>
       </c>
       <c r="K9" t="n">
-        <v>6.566964720832006</v>
+        <v>6.566964720832015</v>
       </c>
       <c r="L9" t="n">
-        <v>2.861114835265926</v>
+        <v>2.861114835266121</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28.18391771809001</v>
+        <v>28.18391771809129</v>
       </c>
       <c r="C2" t="n">
-        <v>53.05096071271072</v>
+        <v>53.05096071271052</v>
       </c>
       <c r="D2" t="n">
-        <v>139.1744223312421</v>
+        <v>139.1744223312426</v>
       </c>
       <c r="E2" t="n">
-        <v>53.05096071271072</v>
+        <v>53.05096071271052</v>
       </c>
       <c r="F2" t="n">
-        <v>53.05096071271072</v>
+        <v>53.05096071271052</v>
       </c>
       <c r="G2" t="n">
-        <v>94.2156563578783</v>
+        <v>94.21565635787897</v>
       </c>
       <c r="H2" t="n">
-        <v>157.9512030097309</v>
+        <v>157.9512030097318</v>
       </c>
       <c r="I2" t="n">
-        <v>53.05096071271072</v>
+        <v>53.05096071271052</v>
       </c>
       <c r="J2" t="n">
-        <v>57.70993944318112</v>
+        <v>57.70993944318092</v>
       </c>
       <c r="K2" t="n">
-        <v>45.94299681519903</v>
+        <v>45.9429968151999</v>
       </c>
       <c r="L2" t="n">
-        <v>31.84892409387222</v>
+        <v>31.84892409387243</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.935829419729892</v>
+        <v>2.935829419731568</v>
       </c>
       <c r="C3" t="n">
-        <v>1.701278022201879</v>
+        <v>1.70127802220187</v>
       </c>
       <c r="D3" t="n">
-        <v>2.935829419729892</v>
+        <v>2.935829419731568</v>
       </c>
       <c r="E3" t="n">
         <v>1.99126189022787</v>
       </c>
       <c r="F3" t="n">
-        <v>1.99126189022787</v>
+        <v>1.991261890227871</v>
       </c>
       <c r="G3" t="n">
-        <v>2.930746495671317</v>
+        <v>2.930746495671819</v>
       </c>
       <c r="H3" t="n">
-        <v>2.935829419729892</v>
+        <v>2.935829419731568</v>
       </c>
       <c r="I3" t="n">
-        <v>2.905765357291468</v>
+        <v>2.905765357291473</v>
       </c>
       <c r="J3" t="n">
-        <v>2.935829419729892</v>
+        <v>2.935829419731568</v>
       </c>
       <c r="K3" t="n">
-        <v>2.935829419729893</v>
+        <v>2.935829419731569</v>
       </c>
       <c r="L3" t="n">
-        <v>2.935829419729892</v>
+        <v>2.935829419731568</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.68419846993648</v>
+        <v>5.218303940627054</v>
       </c>
       <c r="C4" t="n">
-        <v>4.973200191918218</v>
+        <v>4.973200191918245</v>
       </c>
       <c r="D4" t="n">
-        <v>5.67408819731285</v>
+        <v>5.674130661858963</v>
       </c>
       <c r="E4" t="n">
-        <v>4.886051070785214</v>
+        <v>4.886051070785205</v>
       </c>
       <c r="F4" t="n">
-        <v>5.175579782062487</v>
+        <v>5.17557978206246</v>
       </c>
       <c r="G4" t="n">
-        <v>16.67911554587842</v>
+        <v>5.213221016568167</v>
       </c>
       <c r="H4" t="n">
-        <v>19.9841441260693</v>
+        <v>19.98414412606981</v>
       </c>
       <c r="I4" t="n">
-        <v>16.6541344074981</v>
+        <v>16.65413440749877</v>
       </c>
       <c r="J4" t="n">
-        <v>17.35065729431838</v>
+        <v>5.380241708458732</v>
       </c>
       <c r="K4" t="n">
-        <v>5.02311268182041</v>
+        <v>5.023112681821782</v>
       </c>
       <c r="L4" t="n">
-        <v>5.235892558810042</v>
+        <v>5.235892558811098</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.93765283379615</v>
+        <v>6.937652833795734</v>
       </c>
       <c r="C5" t="n">
-        <v>6.907588771357466</v>
+        <v>6.907588771357501</v>
       </c>
       <c r="D5" t="n">
-        <v>6.937732609462861</v>
+        <v>6.937732609463444</v>
       </c>
       <c r="E5" t="n">
-        <v>6.762269384038404</v>
+        <v>6.762269384038465</v>
       </c>
       <c r="F5" t="n">
-        <v>6.762269384038404</v>
+        <v>6.762269384038465</v>
       </c>
       <c r="G5" t="n">
-        <v>6.932569909737666</v>
+        <v>6.932569909737945</v>
       </c>
       <c r="H5" t="n">
-        <v>6.93765283379615</v>
+        <v>6.937652833795734</v>
       </c>
       <c r="I5" t="n">
-        <v>6.907588771357466</v>
+        <v>6.907588771357501</v>
       </c>
       <c r="J5" t="n">
-        <v>6.93765283379615</v>
+        <v>6.937652833795734</v>
       </c>
       <c r="K5" t="n">
-        <v>6.93765283379615</v>
+        <v>6.937652833795734</v>
       </c>
       <c r="L5" t="n">
-        <v>6.93765283379615</v>
+        <v>6.937652833795734</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.98188997292518</v>
+        <v>16.98188997292543</v>
       </c>
       <c r="C6" t="n">
-        <v>26.52575585499336</v>
+        <v>26.52575585518811</v>
       </c>
       <c r="D6" t="n">
-        <v>28.70661632687908</v>
+        <v>28.7066163268791</v>
       </c>
       <c r="E6" t="n">
         <v>23.88443208359384</v>
       </c>
       <c r="F6" t="n">
-        <v>17.17291425587591</v>
+        <v>17.17291425587587</v>
       </c>
       <c r="G6" t="n">
-        <v>26.68787930849749</v>
+        <v>26.68787930849794</v>
       </c>
       <c r="H6" t="n">
-        <v>26.69296223249039</v>
+        <v>26.69296223249122</v>
       </c>
       <c r="I6" t="n">
-        <v>26.66289817011721</v>
+        <v>26.66289817011725</v>
       </c>
       <c r="J6" t="n">
-        <v>26.69487072304132</v>
+        <v>26.6948707230409</v>
       </c>
       <c r="K6" t="n">
-        <v>16.80150182119148</v>
+        <v>16.80150182119052</v>
       </c>
       <c r="L6" t="n">
-        <v>36.83698922169535</v>
+        <v>36.83698922169406</v>
       </c>
     </row>
     <row r="7">
@@ -5071,13 +5071,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>483.1353086263699</v>
+        <v>483.1353086263689</v>
       </c>
       <c r="C7" t="n">
         <v>616.2491148388974</v>
       </c>
       <c r="D7" t="n">
-        <v>616.2791818305134</v>
+        <v>616.2791818305132</v>
       </c>
       <c r="E7" t="n">
         <v>769.894319059516</v>
@@ -5086,22 +5086,22 @@
         <v>616.2491135441094</v>
       </c>
       <c r="G7" t="n">
-        <v>616.2740959772764</v>
+        <v>616.2740959772777</v>
       </c>
       <c r="H7" t="n">
-        <v>616.2791789013361</v>
+        <v>616.2791789013345</v>
       </c>
       <c r="I7" t="n">
         <v>616.2491148388974</v>
       </c>
       <c r="J7" t="n">
-        <v>616.2791789013361</v>
+        <v>616.2791789013345</v>
       </c>
       <c r="K7" t="n">
-        <v>539.1350987996814</v>
+        <v>539.1350987996792</v>
       </c>
       <c r="L7" t="n">
-        <v>616.2791789013361</v>
+        <v>616.2791789013345</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.964585769012221</v>
+        <v>5.964585769012868</v>
       </c>
       <c r="C8" t="n">
-        <v>3.649071700594437</v>
+        <v>3.649071700594451</v>
       </c>
       <c r="D8" t="n">
-        <v>3.403801137214187</v>
+        <v>3.403801137214752</v>
       </c>
       <c r="E8" t="n">
-        <v>3.649071700594437</v>
+        <v>3.649071700594451</v>
       </c>
       <c r="F8" t="n">
-        <v>3.649071700594437</v>
+        <v>3.649071700594451</v>
       </c>
       <c r="G8" t="n">
-        <v>4.455377263476314</v>
+        <v>4.455377263476181</v>
       </c>
       <c r="H8" t="n">
-        <v>3.391183644866335</v>
+        <v>3.39118364486689</v>
       </c>
       <c r="I8" t="n">
-        <v>3.649071700594437</v>
+        <v>3.649071700594451</v>
       </c>
       <c r="J8" t="n">
-        <v>5.36552098133449</v>
+        <v>5.365520981334581</v>
       </c>
       <c r="K8" t="n">
-        <v>5.564199859377915</v>
+        <v>5.564199859378564</v>
       </c>
       <c r="L8" t="n">
-        <v>5.957426718172884</v>
+        <v>5.957426718173706</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.21451966351709</v>
+        <v>6.214519663517254</v>
       </c>
       <c r="C9" t="n">
-        <v>4.286456950868443</v>
+        <v>4.286456950868431</v>
       </c>
       <c r="D9" t="n">
-        <v>5.171610930524124</v>
+        <v>5.171610930524629</v>
       </c>
       <c r="E9" t="n">
-        <v>4.286456950868443</v>
+        <v>4.286456950868431</v>
       </c>
       <c r="F9" t="n">
-        <v>4.286456950868443</v>
+        <v>4.286456950868431</v>
       </c>
       <c r="G9" t="n">
-        <v>5.575799431497356</v>
+        <v>5.575799431497215</v>
       </c>
       <c r="H9" t="n">
-        <v>5.169297456533389</v>
+        <v>5.169297456533234</v>
       </c>
       <c r="I9" t="n">
-        <v>4.286456950868443</v>
+        <v>4.286456950868431</v>
       </c>
       <c r="J9" t="n">
-        <v>5.970962855148624</v>
+        <v>5.970962855149585</v>
       </c>
       <c r="K9" t="n">
-        <v>6.051495338031976</v>
+        <v>6.051495338032358</v>
       </c>
       <c r="L9" t="n">
-        <v>6.21201987361649</v>
+        <v>5.28668723122766</v>
       </c>
     </row>
   </sheetData>
@@ -5267,13 +5267,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36.73350770359061</v>
+        <v>36.73350770359091</v>
       </c>
       <c r="C2" t="n">
         <v>51.04092156293711</v>
       </c>
       <c r="D2" t="n">
-        <v>133.5139383209082</v>
+        <v>133.5139383209075</v>
       </c>
       <c r="E2" t="n">
         <v>51.04092156293711</v>
@@ -5282,22 +5282,22 @@
         <v>51.04092156293711</v>
       </c>
       <c r="G2" t="n">
-        <v>99.2398779725691</v>
+        <v>99.23987797257054</v>
       </c>
       <c r="H2" t="n">
-        <v>144.1929798868384</v>
+        <v>144.1929798868389</v>
       </c>
       <c r="I2" t="n">
         <v>51.04092156293711</v>
       </c>
       <c r="J2" t="n">
-        <v>57.84227430616308</v>
+        <v>57.84227430616569</v>
       </c>
       <c r="K2" t="n">
-        <v>60.04860809384162</v>
+        <v>60.04860809384266</v>
       </c>
       <c r="L2" t="n">
-        <v>50.55602366029684</v>
+        <v>50.55602366029752</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.433896396182559</v>
+        <v>4.433896396183019</v>
       </c>
       <c r="C3" t="n">
-        <v>3.356916440060672</v>
+        <v>3.356916440060698</v>
       </c>
       <c r="D3" t="n">
-        <v>4.433896396182684</v>
+        <v>4.43389639618278</v>
       </c>
       <c r="E3" t="n">
-        <v>3.682118640309676</v>
+        <v>3.682118640309741</v>
       </c>
       <c r="F3" t="n">
-        <v>3.68211864030968</v>
+        <v>3.682118640309743</v>
       </c>
       <c r="G3" t="n">
-        <v>4.428022331392216</v>
+        <v>4.428022331393177</v>
       </c>
       <c r="H3" t="n">
-        <v>4.433896396182684</v>
+        <v>4.43389639618278</v>
       </c>
       <c r="I3" t="n">
-        <v>4.398887716220676</v>
+        <v>4.398887716220726</v>
       </c>
       <c r="J3" t="n">
-        <v>4.433896396182684</v>
+        <v>4.43389639618278</v>
       </c>
       <c r="K3" t="n">
-        <v>4.433896396182684</v>
+        <v>4.433896396182779</v>
       </c>
       <c r="L3" t="n">
-        <v>4.433896396182684</v>
+        <v>4.43389639618278</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.01263219649594</v>
+        <v>7.144798193580086</v>
       </c>
       <c r="C4" t="n">
-        <v>6.89634434041689</v>
+        <v>6.896344340416889</v>
       </c>
       <c r="D4" t="n">
-        <v>7.533603022919173</v>
+        <v>7.533603022919167</v>
       </c>
       <c r="E4" t="n">
-        <v>6.705503668110488</v>
+        <v>6.705503668110467</v>
       </c>
       <c r="F4" t="n">
-        <v>7.0956121112391</v>
+        <v>7.095612111239121</v>
       </c>
       <c r="G4" t="n">
-        <v>19.00675813170555</v>
+        <v>7.138924128789244</v>
       </c>
       <c r="H4" t="n">
-        <v>21.88693714115891</v>
+        <v>21.88693714115927</v>
       </c>
       <c r="I4" t="n">
-        <v>18.97762351653407</v>
+        <v>18.97762351653454</v>
       </c>
       <c r="J4" t="n">
-        <v>19.64377239719977</v>
+        <v>7.323073197073256</v>
       </c>
       <c r="K4" t="n">
-        <v>6.923772039558581</v>
+        <v>6.923772039558908</v>
       </c>
       <c r="L4" t="n">
-        <v>7.113084974969732</v>
+        <v>7.113084974969975</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.640112128382192</v>
+        <v>8.640112128384391</v>
       </c>
       <c r="C5" t="n">
-        <v>8.605103448420557</v>
+        <v>8.605103448420676</v>
       </c>
       <c r="D5" t="n">
-        <v>8.640120707207357</v>
+        <v>8.640120707207547</v>
       </c>
       <c r="E5" t="n">
-        <v>8.509643527418445</v>
+        <v>8.509643527418511</v>
       </c>
       <c r="F5" t="n">
-        <v>8.509643527418445</v>
+        <v>8.509643527418515</v>
       </c>
       <c r="G5" t="n">
-        <v>8.634238063591935</v>
+        <v>8.634238063591953</v>
       </c>
       <c r="H5" t="n">
-        <v>8.64011212838229</v>
+        <v>8.64011212838451</v>
       </c>
       <c r="I5" t="n">
-        <v>8.605103448420557</v>
+        <v>8.605103448420676</v>
       </c>
       <c r="J5" t="n">
-        <v>8.64011212838229</v>
+        <v>8.64011212838451</v>
       </c>
       <c r="K5" t="n">
-        <v>8.64011212838229</v>
+        <v>8.64011212838451</v>
       </c>
       <c r="L5" t="n">
-        <v>8.64011212838229</v>
+        <v>8.64011212838451</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.66831443052965</v>
+        <v>18.66831443053067</v>
       </c>
       <c r="C6" t="n">
-        <v>28.90013387401107</v>
+        <v>28.90013387401133</v>
       </c>
       <c r="D6" t="n">
-        <v>31.17178364960814</v>
+        <v>31.17178364960913</v>
       </c>
       <c r="E6" t="n">
-        <v>26.07730192970538</v>
+        <v>26.07730192970565</v>
       </c>
       <c r="F6" t="n">
-        <v>18.90462561784814</v>
+        <v>18.90462561784819</v>
       </c>
       <c r="G6" t="n">
-        <v>29.0185108981006</v>
+        <v>29.01851089810112</v>
       </c>
       <c r="H6" t="n">
-        <v>29.02438496276262</v>
+        <v>29.02438496276286</v>
       </c>
       <c r="I6" t="n">
-        <v>28.98937628292933</v>
+        <v>28.98937628292954</v>
       </c>
       <c r="J6" t="n">
-        <v>29.02642020020237</v>
+        <v>29.02642020020341</v>
       </c>
       <c r="K6" t="n">
-        <v>18.47594510615149</v>
+        <v>18.47594510615222</v>
       </c>
       <c r="L6" t="n">
-        <v>39.84216656842695</v>
+        <v>39.842166568427</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>452.0099395287885</v>
+        <v>452.0099395287908</v>
       </c>
       <c r="C7" t="n">
-        <v>576.3252700494407</v>
+        <v>576.3252700494409</v>
       </c>
       <c r="D7" t="n">
-        <v>576.3602824400514</v>
+        <v>576.3602824400518</v>
       </c>
       <c r="E7" t="n">
-        <v>719.8229266645496</v>
+        <v>719.8229266645501</v>
       </c>
       <c r="F7" t="n">
-        <v>576.3252688305544</v>
+        <v>576.3252688305552</v>
       </c>
       <c r="G7" t="n">
-        <v>576.3544046646128</v>
+        <v>576.3544046646127</v>
       </c>
       <c r="H7" t="n">
-        <v>576.3602787294021</v>
+        <v>576.3602787294036</v>
       </c>
       <c r="I7" t="n">
-        <v>576.3252700494407</v>
+        <v>576.3252700494409</v>
       </c>
       <c r="J7" t="n">
-        <v>576.3602787294021</v>
+        <v>576.3602787294036</v>
       </c>
       <c r="K7" t="n">
-        <v>419.7810042570769</v>
+        <v>504.3112053957737</v>
       </c>
       <c r="L7" t="n">
-        <v>576.3602787294021</v>
+        <v>576.3602787294036</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.428830560356765</v>
+        <v>7.428830560357031</v>
       </c>
       <c r="C8" t="n">
-        <v>5.401517538703951</v>
+        <v>5.401517538703994</v>
       </c>
       <c r="D8" t="n">
-        <v>4.979176489370385</v>
+        <v>4.979176489370998</v>
       </c>
       <c r="E8" t="n">
-        <v>5.401517538703951</v>
+        <v>5.401517538703994</v>
       </c>
       <c r="F8" t="n">
-        <v>5.401517538703951</v>
+        <v>5.401517538703994</v>
       </c>
       <c r="G8" t="n">
-        <v>5.86777960686229</v>
+        <v>5.867779606862381</v>
       </c>
       <c r="H8" t="n">
-        <v>5.180753866313862</v>
+        <v>5.180753866314416</v>
       </c>
       <c r="I8" t="n">
-        <v>5.401517538703951</v>
+        <v>5.401517538703994</v>
       </c>
       <c r="J8" t="n">
-        <v>6.990858174674932</v>
+        <v>6.99085817467515</v>
       </c>
       <c r="K8" t="n">
-        <v>6.779620209110488</v>
+        <v>6.779620209111049</v>
       </c>
       <c r="L8" t="n">
-        <v>7.207854929004336</v>
+        <v>7.207854929004366</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.795469521077201</v>
+        <v>7.795469521077502</v>
       </c>
       <c r="C9" t="n">
-        <v>6.032705431509404</v>
+        <v>6.032705431509418</v>
       </c>
       <c r="D9" t="n">
-        <v>6.797826803210539</v>
+        <v>6.797826803210468</v>
       </c>
       <c r="E9" t="n">
-        <v>6.032705431509404</v>
+        <v>6.032705431509418</v>
       </c>
       <c r="F9" t="n">
-        <v>6.032705431509404</v>
+        <v>6.032705431509418</v>
       </c>
       <c r="G9" t="n">
-        <v>7.134091654910676</v>
+        <v>7.13409165491078</v>
       </c>
       <c r="H9" t="n">
-        <v>6.882664641139776</v>
+        <v>6.882664641139762</v>
       </c>
       <c r="I9" t="n">
-        <v>6.032705431509404</v>
+        <v>6.032705431509418</v>
       </c>
       <c r="J9" t="n">
-        <v>7.6175521823799</v>
+        <v>7.617552182379955</v>
       </c>
       <c r="K9" t="n">
-        <v>7.531126092285924</v>
+        <v>7.531126092286831</v>
       </c>
       <c r="L9" t="n">
-        <v>7.706217352820231</v>
+        <v>7.008598613414478</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>40.05050430626786</v>
+        <v>40.05050430626833</v>
       </c>
       <c r="C2" t="n">
-        <v>59.40835180411806</v>
+        <v>59.40835180412287</v>
       </c>
       <c r="D2" t="n">
-        <v>124.2999305634642</v>
+        <v>124.2999305634647</v>
       </c>
       <c r="E2" t="n">
-        <v>59.40835180411806</v>
+        <v>59.40835180412287</v>
       </c>
       <c r="F2" t="n">
-        <v>59.40835180411806</v>
+        <v>59.40835180412287</v>
       </c>
       <c r="G2" t="n">
-        <v>109.1792892885956</v>
+        <v>109.1792892885967</v>
       </c>
       <c r="H2" t="n">
-        <v>129.2103559793736</v>
+        <v>129.2103559793626</v>
       </c>
       <c r="I2" t="n">
-        <v>59.40835180411806</v>
+        <v>59.40835180412287</v>
       </c>
       <c r="J2" t="n">
-        <v>63.30301529517697</v>
+        <v>63.3030152951773</v>
       </c>
       <c r="K2" t="n">
-        <v>61.79147861028014</v>
+        <v>61.79147861028068</v>
       </c>
       <c r="L2" t="n">
-        <v>132.8885965185419</v>
+        <v>44.72325112177937</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.575671266194746</v>
+        <v>5.575671266194819</v>
       </c>
       <c r="C3" t="n">
-        <v>4.914516737117258</v>
+        <v>4.914516737117505</v>
       </c>
       <c r="D3" t="n">
-        <v>5.575671266194858</v>
+        <v>5.575671266194819</v>
       </c>
       <c r="E3" t="n">
-        <v>5.247000156558126</v>
+        <v>5.247000156558068</v>
       </c>
       <c r="F3" t="n">
-        <v>5.247000156557959</v>
+        <v>5.247000156558064</v>
       </c>
       <c r="G3" t="n">
-        <v>5.568812070072946</v>
+        <v>5.568812070073051</v>
       </c>
       <c r="H3" t="n">
-        <v>5.575671266194858</v>
+        <v>5.575671266194819</v>
       </c>
       <c r="I3" t="n">
-        <v>5.534070103811648</v>
+        <v>5.534070103812016</v>
       </c>
       <c r="J3" t="n">
-        <v>5.575671266194858</v>
+        <v>5.575671266194819</v>
       </c>
       <c r="K3" t="n">
-        <v>5.575671266194858</v>
+        <v>5.575671266194819</v>
       </c>
       <c r="L3" t="n">
-        <v>5.575671266194858</v>
+        <v>5.575671266194819</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.711465038226139</v>
+        <v>8.711465038226713</v>
       </c>
       <c r="C4" t="n">
-        <v>8.522848722158576</v>
+        <v>8.522848722158914</v>
       </c>
       <c r="D4" t="n">
-        <v>22.05009564551898</v>
+        <v>9.053057078975796</v>
       </c>
       <c r="E4" t="n">
-        <v>8.252646296380053</v>
+        <v>8.252646296380638</v>
       </c>
       <c r="F4" t="n">
-        <v>8.689274638290412</v>
+        <v>8.689274638290751</v>
       </c>
       <c r="G4" t="n">
-        <v>8.704605842105037</v>
+        <v>21.32178237509639</v>
       </c>
       <c r="H4" t="n">
-        <v>24.13917187536583</v>
+        <v>24.13917187536629</v>
       </c>
       <c r="I4" t="n">
-        <v>21.28704040883502</v>
+        <v>8.669863875843925</v>
       </c>
       <c r="J4" t="n">
-        <v>8.921703111437514</v>
+        <v>21.91017391022226</v>
       </c>
       <c r="K4" t="n">
-        <v>8.481203068994157</v>
+        <v>8.481203068994528</v>
       </c>
       <c r="L4" t="n">
-        <v>8.662627289735722</v>
+        <v>8.662627289735978</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.17108677968318</v>
+        <v>10.17108677968312</v>
       </c>
       <c r="C5" t="n">
-        <v>10.12948561729971</v>
+        <v>10.12948561730032</v>
       </c>
       <c r="D5" t="n">
-        <v>10.17100515703433</v>
+        <v>10.17100515703445</v>
       </c>
       <c r="E5" t="n">
-        <v>10.16122170189978</v>
+        <v>10.16122170189948</v>
       </c>
       <c r="F5" t="n">
-        <v>10.16122170189978</v>
+        <v>10.16122170189948</v>
       </c>
       <c r="G5" t="n">
-        <v>10.1642275835609</v>
+        <v>10.16422758356138</v>
       </c>
       <c r="H5" t="n">
-        <v>10.17108677968295</v>
+        <v>10.17108677968312</v>
       </c>
       <c r="I5" t="n">
-        <v>10.12948561729971</v>
+        <v>10.12948561730032</v>
       </c>
       <c r="J5" t="n">
-        <v>10.17108677968295</v>
+        <v>10.17108677968312</v>
       </c>
       <c r="K5" t="n">
-        <v>10.17108677968295</v>
+        <v>10.17108677968312</v>
       </c>
       <c r="L5" t="n">
-        <v>10.17108677968295</v>
+        <v>10.17108677968312</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.62198910861404</v>
+        <v>20.62198910861435</v>
       </c>
       <c r="C6" t="n">
-        <v>31.82061511223487</v>
+        <v>31.82061511223557</v>
       </c>
       <c r="D6" t="n">
-        <v>34.15348966204913</v>
+        <v>34.15348966205052</v>
       </c>
       <c r="E6" t="n">
-        <v>28.75193772627196</v>
+        <v>28.75193772627249</v>
       </c>
       <c r="F6" t="n">
-        <v>20.95463059507767</v>
+        <v>20.95463059507831</v>
       </c>
       <c r="G6" t="n">
-        <v>31.82267333024942</v>
+        <v>31.8226733302501</v>
       </c>
       <c r="H6" t="n">
-        <v>31.82953252623662</v>
+        <v>31.82953252623669</v>
       </c>
       <c r="I6" t="n">
-        <v>31.78793136398826</v>
+        <v>31.78793136398903</v>
       </c>
       <c r="J6" t="n">
-        <v>31.83173509427837</v>
+        <v>31.83173509427854</v>
       </c>
       <c r="K6" t="n">
-        <v>20.41380323907989</v>
+        <v>20.41380323908074</v>
       </c>
       <c r="L6" t="n">
-        <v>43.536748751776</v>
+        <v>43.53674875177708</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>453.1814478803062</v>
+        <v>453.1814478803067</v>
       </c>
       <c r="C7" t="n">
-        <v>577.6444798367033</v>
+        <v>577.6444798367047</v>
       </c>
       <c r="D7" t="n">
-        <v>577.6860853245182</v>
+        <v>577.6860853245183</v>
       </c>
       <c r="E7" t="n">
-        <v>721.3201889255255</v>
+        <v>721.3201889255257</v>
       </c>
       <c r="F7" t="n">
-        <v>577.6444786241846</v>
+        <v>577.6444786241854</v>
       </c>
       <c r="G7" t="n">
-        <v>577.679221802965</v>
+        <v>577.6792218029644</v>
       </c>
       <c r="H7" t="n">
-        <v>577.6860809990862</v>
+        <v>577.6860809990865</v>
       </c>
       <c r="I7" t="n">
-        <v>577.6444798367033</v>
+        <v>577.6444798367047</v>
       </c>
       <c r="J7" t="n">
-        <v>577.6860809990862</v>
+        <v>577.6860809990865</v>
       </c>
       <c r="K7" t="n">
-        <v>505.5476094218862</v>
+        <v>505.5476094218864</v>
       </c>
       <c r="L7" t="n">
-        <v>577.6860809990862</v>
+        <v>577.6860809990865</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.481078379687981</v>
+        <v>8.481078379688055</v>
       </c>
       <c r="C8" t="n">
-        <v>6.380239306116086</v>
+        <v>6.380239306115978</v>
       </c>
       <c r="D8" t="n">
-        <v>6.268811081770829</v>
+        <v>6.268811081770876</v>
       </c>
       <c r="E8" t="n">
-        <v>6.380239306116086</v>
+        <v>6.380239306115978</v>
       </c>
       <c r="F8" t="n">
-        <v>6.380239306116086</v>
+        <v>6.380239306115978</v>
       </c>
       <c r="G8" t="n">
-        <v>6.719494125090602</v>
+        <v>6.719494125090651</v>
       </c>
       <c r="H8" t="n">
-        <v>6.550845054500713</v>
+        <v>6.550845054500662</v>
       </c>
       <c r="I8" t="n">
-        <v>6.380239306116086</v>
+        <v>6.380239306115978</v>
       </c>
       <c r="J8" t="n">
-        <v>8.019873524827227</v>
+        <v>8.019873524827355</v>
       </c>
       <c r="K8" t="n">
-        <v>7.815464057068409</v>
+        <v>7.815464057068479</v>
       </c>
       <c r="L8" t="n">
-        <v>6.656782085213037</v>
+        <v>6.656782085213158</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.884614146685228</v>
+        <v>8.884614146685326</v>
       </c>
       <c r="C9" t="n">
-        <v>7.123490518108213</v>
+        <v>7.123490518108323</v>
       </c>
       <c r="D9" t="n">
-        <v>7.983653521931991</v>
+        <v>7.983653521931976</v>
       </c>
       <c r="E9" t="n">
-        <v>7.123490518108213</v>
+        <v>7.123490518108323</v>
       </c>
       <c r="F9" t="n">
-        <v>7.123490518108213</v>
+        <v>7.123490518108323</v>
       </c>
       <c r="G9" t="n">
-        <v>8.142168557723346</v>
+        <v>8.142168557723364</v>
       </c>
       <c r="H9" t="n">
-        <v>8.101048487421036</v>
+        <v>8.101048487421107</v>
       </c>
       <c r="I9" t="n">
-        <v>7.123490518108213</v>
+        <v>7.123490518108323</v>
       </c>
       <c r="J9" t="n">
-        <v>8.697275834888778</v>
+        <v>8.697275834888751</v>
       </c>
       <c r="K9" t="n">
-        <v>8.61359487390043</v>
+        <v>8.613594873900482</v>
       </c>
       <c r="L9" t="n">
-        <v>8.143629853691442</v>
+        <v>8.14362985369141</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>47.20660058191531</v>
+        <v>47.20660058191619</v>
       </c>
       <c r="C2" t="n">
-        <v>51.07890247681061</v>
+        <v>51.07890247681056</v>
       </c>
       <c r="D2" t="n">
-        <v>66.25774591306524</v>
+        <v>66.25774591306596</v>
       </c>
       <c r="E2" t="n">
-        <v>51.07890247681061</v>
+        <v>51.07890247681056</v>
       </c>
       <c r="F2" t="n">
-        <v>51.07890247681061</v>
+        <v>51.07890247681056</v>
       </c>
       <c r="G2" t="n">
-        <v>148.8017607086459</v>
+        <v>148.8017607086458</v>
       </c>
       <c r="H2" t="n">
-        <v>82.79716903358613</v>
+        <v>82.79716903358609</v>
       </c>
       <c r="I2" t="n">
-        <v>51.07890247681061</v>
+        <v>51.07890247681056</v>
       </c>
       <c r="J2" t="n">
-        <v>63.40644901487498</v>
+        <v>63.40644901487556</v>
       </c>
       <c r="K2" t="n">
-        <v>61.28301926271483</v>
+        <v>61.28301926271685</v>
       </c>
       <c r="L2" t="n">
-        <v>57.54071183527211</v>
+        <v>57.54071183527271</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.017316978874311</v>
+        <v>5.017316978875313</v>
       </c>
       <c r="C3" t="n">
-        <v>4.102221228919597</v>
+        <v>4.102221228919558</v>
       </c>
       <c r="D3" t="n">
-        <v>5.01731697887431</v>
+        <v>5.017316978875313</v>
       </c>
       <c r="E3" t="n">
-        <v>4.438166356151592</v>
+        <v>4.43816635615156</v>
       </c>
       <c r="F3" t="n">
-        <v>4.438166356151585</v>
+        <v>4.438166356151567</v>
       </c>
       <c r="G3" t="n">
-        <v>5.009337366391573</v>
+        <v>5.009337366392194</v>
       </c>
       <c r="H3" t="n">
-        <v>5.01731697887431</v>
+        <v>5.017316978875312</v>
       </c>
       <c r="I3" t="n">
-        <v>4.968827328789159</v>
+        <v>4.968827328789207</v>
       </c>
       <c r="J3" t="n">
-        <v>5.01731697887431</v>
+        <v>5.017316978875312</v>
       </c>
       <c r="K3" t="n">
-        <v>5.01731697887431</v>
+        <v>5.017316978875312</v>
       </c>
       <c r="L3" t="n">
-        <v>5.01731697887431</v>
+        <v>5.017316978875312</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.238601603857735</v>
+        <v>21.73401330718413</v>
       </c>
       <c r="C4" t="n">
-        <v>7.841580640535877</v>
+        <v>7.841580640535831</v>
       </c>
       <c r="D4" t="n">
-        <v>22.27523501458419</v>
+        <v>22.27523501458477</v>
       </c>
       <c r="E4" t="n">
-        <v>7.624233667500024</v>
+        <v>7.624233667499989</v>
       </c>
       <c r="F4" t="n">
-        <v>8.122134405095364</v>
+        <v>8.122134405095293</v>
       </c>
       <c r="G4" t="n">
-        <v>8.230621991373688</v>
+        <v>21.72603369470104</v>
       </c>
       <c r="H4" t="n">
-        <v>24.73461926357771</v>
+        <v>8.180868997625288</v>
       </c>
       <c r="I4" t="n">
-        <v>8.190111953772442</v>
+        <v>21.68552365709799</v>
       </c>
       <c r="J4" t="n">
-        <v>22.13015842208799</v>
+        <v>22.13015842208731</v>
       </c>
       <c r="K4" t="n">
-        <v>7.974164281737536</v>
+        <v>7.974164281738368</v>
       </c>
       <c r="L4" t="n">
-        <v>8.124378263310279</v>
+        <v>8.124378263310454</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.986221601916824</v>
+        <v>9.986221601917283</v>
       </c>
       <c r="C5" t="n">
-        <v>9.93773195183118</v>
+        <v>9.937731951831175</v>
       </c>
       <c r="D5" t="n">
-        <v>9.986158752547587</v>
+        <v>9.986158752548562</v>
       </c>
       <c r="E5" t="n">
-        <v>9.918715195030805</v>
+        <v>9.918715195030693</v>
       </c>
       <c r="F5" t="n">
-        <v>9.918715195030805</v>
+        <v>9.918715195030693</v>
       </c>
       <c r="G5" t="n">
-        <v>9.978241989432767</v>
+        <v>9.97824198943421</v>
       </c>
       <c r="H5" t="n">
-        <v>9.986221601916824</v>
+        <v>9.986221601917283</v>
       </c>
       <c r="I5" t="n">
-        <v>9.93773195183118</v>
+        <v>9.937731951831175</v>
       </c>
       <c r="J5" t="n">
-        <v>9.986221601916824</v>
+        <v>9.986221601917283</v>
       </c>
       <c r="K5" t="n">
-        <v>9.986221601916824</v>
+        <v>9.986221601917283</v>
       </c>
       <c r="L5" t="n">
-        <v>9.986221601916824</v>
+        <v>9.986221601917283</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.26020294554774</v>
+        <v>21.26020294554856</v>
       </c>
       <c r="C6" t="n">
-        <v>32.96474676772119</v>
+        <v>32.96474676772129</v>
       </c>
       <c r="D6" t="n">
-        <v>35.46932221284625</v>
+        <v>35.46932221284811</v>
       </c>
       <c r="E6" t="n">
-        <v>29.74771057604369</v>
+        <v>29.74771057604374</v>
       </c>
       <c r="F6" t="n">
-        <v>21.57345869909707</v>
+        <v>21.57345869909703</v>
       </c>
       <c r="G6" t="n">
-        <v>33.02100836001332</v>
+        <v>33.02100836001335</v>
       </c>
       <c r="H6" t="n">
-        <v>33.02898797240349</v>
+        <v>33.02898797240424</v>
       </c>
       <c r="I6" t="n">
-        <v>32.98049832241033</v>
+        <v>32.9804983224104</v>
       </c>
       <c r="J6" t="n">
-        <v>33.03130084873415</v>
+        <v>33.03130084873455</v>
       </c>
       <c r="K6" t="n">
-        <v>21.04159172420487</v>
+        <v>21.04159172420569</v>
       </c>
       <c r="L6" t="n">
-        <v>45.32246799689879</v>
+        <v>45.3224679969</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>487.6069073942272</v>
+        <v>487.6069073942284</v>
       </c>
       <c r="C7" t="n">
-        <v>621.6513653629528</v>
+        <v>621.6513653629527</v>
       </c>
       <c r="D7" t="n">
         <v>621.6998615665982</v>
       </c>
       <c r="E7" t="n">
-        <v>776.3917890712544</v>
+        <v>776.391789071254</v>
       </c>
       <c r="F7" t="n">
-        <v>621.651364932334</v>
+        <v>621.6513649323338</v>
       </c>
       <c r="G7" t="n">
-        <v>621.6918754005553</v>
+        <v>621.6918754005562</v>
       </c>
       <c r="H7" t="n">
-        <v>621.6998550130384</v>
+        <v>621.699855013039</v>
       </c>
       <c r="I7" t="n">
-        <v>621.6513653629528</v>
+        <v>621.6513653629527</v>
       </c>
       <c r="J7" t="n">
-        <v>621.6998550130384</v>
+        <v>621.699855013039</v>
       </c>
       <c r="K7" t="n">
-        <v>544.0058772954446</v>
+        <v>544.0058772954451</v>
       </c>
       <c r="L7" t="n">
-        <v>621.6998550130384</v>
+        <v>621.699855013039</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.495128703056322</v>
+        <v>7.495128703056792</v>
       </c>
       <c r="C8" t="n">
-        <v>5.672568282100062</v>
+        <v>5.672568282100056</v>
       </c>
       <c r="D8" t="n">
-        <v>6.97180001353817</v>
+        <v>6.971800013538574</v>
       </c>
       <c r="E8" t="n">
-        <v>5.672568282100062</v>
+        <v>5.672568282100056</v>
       </c>
       <c r="F8" t="n">
-        <v>5.672568282100062</v>
+        <v>5.672568282100056</v>
       </c>
       <c r="G8" t="n">
-        <v>5.002558398819319</v>
+        <v>5.002558398819723</v>
       </c>
       <c r="H8" t="n">
-        <v>6.771736329228554</v>
+        <v>6.771736329228866</v>
       </c>
       <c r="I8" t="n">
-        <v>5.672568282100062</v>
+        <v>5.672568282100056</v>
       </c>
       <c r="J8" t="n">
-        <v>7.228792573163087</v>
+        <v>7.228792573163844</v>
       </c>
       <c r="K8" t="n">
-        <v>7.126748601616161</v>
+        <v>7.126748601616653</v>
       </c>
       <c r="L8" t="n">
-        <v>7.905840437000993</v>
+        <v>7.435156220419453</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.975203657539412</v>
+        <v>7.975203657540028</v>
       </c>
       <c r="C9" t="n">
-        <v>6.237681628297032</v>
+        <v>6.237681628297037</v>
       </c>
       <c r="D9" t="n">
-        <v>7.762095088377848</v>
+        <v>7.76209508837833</v>
       </c>
       <c r="E9" t="n">
-        <v>6.237681628297038</v>
+        <v>6.237681628297037</v>
       </c>
       <c r="F9" t="n">
-        <v>6.237681628297038</v>
+        <v>6.237681628297037</v>
       </c>
       <c r="G9" t="n">
-        <v>6.93012142803885</v>
+        <v>6.930121428039112</v>
       </c>
       <c r="H9" t="n">
-        <v>7.682155182151109</v>
+        <v>7.682155182151559</v>
       </c>
       <c r="I9" t="n">
-        <v>6.237681628297038</v>
+        <v>6.237681628297037</v>
       </c>
       <c r="J9" t="n">
-        <v>7.86720163702072</v>
+        <v>7.867201637020955</v>
       </c>
       <c r="K9" t="n">
-        <v>7.825236071021012</v>
+        <v>7.825236071021255</v>
       </c>
       <c r="L9" t="n">
-        <v>7.951563851405262</v>
+        <v>7.951563851405736</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>231.5101652739464</v>
+        <v>231.5101652739467</v>
       </c>
       <c r="C2" t="n">
-        <v>87.41757440207873</v>
+        <v>87.41757440207896</v>
       </c>
       <c r="D2" t="n">
-        <v>55.16575557223457</v>
+        <v>55.16575557223466</v>
       </c>
       <c r="E2" t="n">
-        <v>87.41757440207873</v>
+        <v>87.41757440207896</v>
       </c>
       <c r="F2" t="n">
-        <v>87.41757440207873</v>
+        <v>87.41757440207896</v>
       </c>
       <c r="G2" t="n">
-        <v>247.3037775309811</v>
+        <v>247.3037775309861</v>
       </c>
       <c r="H2" t="n">
-        <v>56.0271806698865</v>
+        <v>56.02718066988705</v>
       </c>
       <c r="I2" t="n">
-        <v>87.41757440207873</v>
+        <v>87.41757440207896</v>
       </c>
       <c r="J2" t="n">
-        <v>118.1915852780216</v>
+        <v>118.1915852780225</v>
       </c>
       <c r="K2" t="n">
-        <v>159.0695287577484</v>
+        <v>159.0695287577481</v>
       </c>
       <c r="L2" t="n">
-        <v>30.70517475789049</v>
+        <v>30.70517475789159</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.527053539215672</v>
+        <v>6.527053539215205</v>
       </c>
       <c r="C3" t="n">
-        <v>5.131450523920031</v>
+        <v>5.131450523920229</v>
       </c>
       <c r="D3" t="n">
-        <v>6.527053539215672</v>
+        <v>6.527053539215205</v>
       </c>
       <c r="E3" t="n">
-        <v>5.570831960213112</v>
+        <v>5.570831960213344</v>
       </c>
       <c r="F3" t="n">
-        <v>5.570831960213118</v>
+        <v>5.57083196021344</v>
       </c>
       <c r="G3" t="n">
-        <v>6.51547369715819</v>
+        <v>6.515473697158982</v>
       </c>
       <c r="H3" t="n">
-        <v>6.527053539215672</v>
+        <v>6.527053539215205</v>
       </c>
       <c r="I3" t="n">
-        <v>6.456475243655871</v>
+        <v>6.456475243655915</v>
       </c>
       <c r="J3" t="n">
-        <v>6.527053539215672</v>
+        <v>6.527053539215205</v>
       </c>
       <c r="K3" t="n">
-        <v>6.527053539215672</v>
+        <v>6.527053539215205</v>
       </c>
       <c r="L3" t="n">
-        <v>6.527053539215672</v>
+        <v>6.527053539215205</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.20602649650897</v>
+        <v>25.20602649650926</v>
       </c>
       <c r="C4" t="n">
-        <v>10.45828496754243</v>
+        <v>10.45828496754248</v>
       </c>
       <c r="D4" t="n">
-        <v>10.90705304073069</v>
+        <v>10.90708583782876</v>
       </c>
       <c r="E4" t="n">
-        <v>10.07420664619254</v>
+        <v>10.07420664619256</v>
       </c>
       <c r="F4" t="n">
-        <v>10.88842536207585</v>
+        <v>10.88842536207588</v>
       </c>
       <c r="G4" t="n">
-        <v>11.11427682511332</v>
+        <v>25.19444665445272</v>
       </c>
       <c r="H4" t="n">
-        <v>11.00507153029235</v>
+        <v>28.73328845144193</v>
       </c>
       <c r="I4" t="n">
-        <v>11.05527837161009</v>
+        <v>25.13544820094964</v>
       </c>
       <c r="J4" t="n">
-        <v>25.85963651055261</v>
+        <v>11.29551329389054</v>
       </c>
       <c r="K4" t="n">
-        <v>11.00879405759967</v>
+        <v>11.00879405759966</v>
       </c>
       <c r="L4" t="n">
-        <v>10.89544283505656</v>
+        <v>10.89544283505676</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.84156157433505</v>
+        <v>11.84156157433498</v>
       </c>
       <c r="C5" t="n">
-        <v>11.77098327877528</v>
+        <v>11.77098327877532</v>
       </c>
       <c r="D5" t="n">
-        <v>11.84158394529478</v>
+        <v>11.84158394529425</v>
       </c>
       <c r="E5" t="n">
-        <v>11.65577740227975</v>
+        <v>11.65577740227976</v>
       </c>
       <c r="F5" t="n">
-        <v>11.65577740227975</v>
+        <v>11.65577740227976</v>
       </c>
       <c r="G5" t="n">
-        <v>11.82998173227842</v>
+        <v>11.82998173227823</v>
       </c>
       <c r="H5" t="n">
-        <v>11.84156157433505</v>
+        <v>11.84156157433498</v>
       </c>
       <c r="I5" t="n">
-        <v>11.77098327877528</v>
+        <v>11.77098327877532</v>
       </c>
       <c r="J5" t="n">
-        <v>11.84156157433505</v>
+        <v>11.84156157433498</v>
       </c>
       <c r="K5" t="n">
-        <v>11.84156157433505</v>
+        <v>11.84156157433498</v>
       </c>
       <c r="L5" t="n">
-        <v>11.84156157433505</v>
+        <v>11.84156157433498</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.47007448790363</v>
+        <v>23.47007448790329</v>
       </c>
       <c r="C6" t="n">
-        <v>36.14462884509641</v>
+        <v>36.14462884509648</v>
       </c>
       <c r="D6" t="n">
-        <v>38.98794865250842</v>
+        <v>38.98794865250873</v>
       </c>
       <c r="E6" t="n">
-        <v>32.64091522198959</v>
+        <v>32.64091522198954</v>
       </c>
       <c r="F6" t="n">
-        <v>23.73816990109681</v>
+        <v>23.73816990109684</v>
       </c>
       <c r="G6" t="n">
-        <v>36.31126346973355</v>
+        <v>36.31126346973291</v>
       </c>
       <c r="H6" t="n">
-        <v>36.32284331179542</v>
+        <v>36.32284331179588</v>
       </c>
       <c r="I6" t="n">
-        <v>36.25226501623055</v>
+        <v>36.2522650162305</v>
       </c>
       <c r="J6" t="n">
-        <v>36.3253692061872</v>
+        <v>36.32536920618788</v>
       </c>
       <c r="K6" t="n">
-        <v>23.23132771252045</v>
+        <v>23.23132771252085</v>
       </c>
       <c r="L6" t="n">
-        <v>49.74863503836988</v>
+        <v>49.74863503837036</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>458.4184264608904</v>
+        <v>458.4184264608907</v>
       </c>
       <c r="C7" t="n">
-        <v>584.2292253556883</v>
+        <v>584.2292253556884</v>
       </c>
       <c r="D7" t="n">
-        <v>584.2998146574786</v>
+        <v>584.2998146574791</v>
       </c>
       <c r="E7" t="n">
-        <v>729.4936758010335</v>
+        <v>729.4936758010333</v>
       </c>
       <c r="F7" t="n">
         <v>584.2292256234185</v>
       </c>
       <c r="G7" t="n">
-        <v>584.2882238091906</v>
+        <v>584.288223809191</v>
       </c>
       <c r="H7" t="n">
-        <v>584.299803651248</v>
+        <v>584.2998036512487</v>
       </c>
       <c r="I7" t="n">
-        <v>584.2292253556883</v>
+        <v>584.2292253556884</v>
       </c>
       <c r="J7" t="n">
-        <v>584.299803651248</v>
+        <v>584.2998036512487</v>
       </c>
       <c r="K7" t="n">
-        <v>508.4045313847145</v>
+        <v>511.3636439620032</v>
       </c>
       <c r="L7" t="n">
-        <v>584.299803651248</v>
+        <v>584.2998036512487</v>
       </c>
     </row>
     <row r="8">
@@ -6695,13 +6695,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.940443211512336</v>
+        <v>4.940443211512487</v>
       </c>
       <c r="C8" t="n">
         <v>6.809828275659419</v>
       </c>
       <c r="D8" t="n">
-        <v>9.340172233102711</v>
+        <v>9.340172233102642</v>
       </c>
       <c r="E8" t="n">
         <v>6.809828275659419</v>
@@ -6710,22 +6710,22 @@
         <v>6.809828275659419</v>
       </c>
       <c r="G8" t="n">
-        <v>4.186190142906122</v>
+        <v>4.186190142906011</v>
       </c>
       <c r="H8" t="n">
-        <v>9.445308652639257</v>
+        <v>9.44530865263922</v>
       </c>
       <c r="I8" t="n">
         <v>6.809828275659419</v>
       </c>
       <c r="J8" t="n">
-        <v>7.901961291570364</v>
+        <v>7.901961291570225</v>
       </c>
       <c r="K8" t="n">
-        <v>6.563621700755103</v>
+        <v>6.563621700754802</v>
       </c>
       <c r="L8" t="n">
-        <v>9.433455168185882</v>
+        <v>10.11076838866822</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.196336276371575</v>
+        <v>8.196336276371854</v>
       </c>
       <c r="C9" t="n">
-        <v>7.978302871857112</v>
+        <v>7.97830287185711</v>
       </c>
       <c r="D9" t="n">
-        <v>9.988352705453185</v>
+        <v>9.988352705453245</v>
       </c>
       <c r="E9" t="n">
-        <v>7.978302871857112</v>
+        <v>7.97830287185711</v>
       </c>
       <c r="F9" t="n">
-        <v>7.978302871857112</v>
+        <v>7.97830287185711</v>
       </c>
       <c r="G9" t="n">
-        <v>7.849936372803747</v>
+        <v>7.849936372803758</v>
       </c>
       <c r="H9" t="n">
-        <v>10.03225992673711</v>
+        <v>10.0322599267371</v>
       </c>
       <c r="I9" t="n">
-        <v>7.978302871857112</v>
+        <v>7.97830287185711</v>
       </c>
       <c r="J9" t="n">
-        <v>9.403591810536215</v>
+        <v>9.403591810536074</v>
       </c>
       <c r="K9" t="n">
-        <v>8.857662727462998</v>
+        <v>8.857662727463131</v>
       </c>
       <c r="L9" t="n">
-        <v>10.02723203013072</v>
+        <v>10.30257856482974</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>353.1250766432685</v>
+        <v>353.1250766432682</v>
       </c>
       <c r="C2" t="n">
-        <v>103.5585183171752</v>
+        <v>103.5585183171751</v>
       </c>
       <c r="D2" t="n">
-        <v>71.31397105701214</v>
+        <v>71.31397105701049</v>
       </c>
       <c r="E2" t="n">
-        <v>103.5585183171752</v>
+        <v>103.5585183171751</v>
       </c>
       <c r="F2" t="n">
-        <v>103.5585183171752</v>
+        <v>103.5585183171751</v>
       </c>
       <c r="G2" t="n">
-        <v>257.016354876535</v>
+        <v>257.0163548765341</v>
       </c>
       <c r="H2" t="n">
-        <v>47.80236643588527</v>
+        <v>47.80236643588285</v>
       </c>
       <c r="I2" t="n">
-        <v>103.5585183171752</v>
+        <v>103.5585183171751</v>
       </c>
       <c r="J2" t="n">
-        <v>142.419094157384</v>
+        <v>142.4190941573838</v>
       </c>
       <c r="K2" t="n">
-        <v>150.3415557725446</v>
+        <v>150.3415557725432</v>
       </c>
       <c r="L2" t="n">
-        <v>85.17001660332149</v>
+        <v>143.2177925073595</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.200111922469721</v>
+        <v>7.200111922469555</v>
       </c>
       <c r="C3" t="n">
-        <v>5.596961317789379</v>
+        <v>5.596961317789369</v>
       </c>
       <c r="D3" t="n">
-        <v>7.200111922469726</v>
+        <v>7.200111922469557</v>
       </c>
       <c r="E3" t="n">
-        <v>6.087669303524383</v>
+        <v>6.087669303524401</v>
       </c>
       <c r="F3" t="n">
-        <v>6.087669303524382</v>
+        <v>6.087669303524404</v>
       </c>
       <c r="G3" t="n">
-        <v>7.188951099652971</v>
+        <v>7.188951099652563</v>
       </c>
       <c r="H3" t="n">
-        <v>7.200111922469721</v>
+        <v>7.200111922469558</v>
       </c>
       <c r="I3" t="n">
-        <v>7.132510257447915</v>
+        <v>7.132510257447874</v>
       </c>
       <c r="J3" t="n">
-        <v>7.20011192246972</v>
+        <v>7.200111922469555</v>
       </c>
       <c r="K3" t="n">
-        <v>7.20011192246972</v>
+        <v>7.200111922469556</v>
       </c>
       <c r="L3" t="n">
-        <v>7.200111922469721</v>
+        <v>7.200111922469557</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.17618176935785</v>
+        <v>12.17618176935692</v>
       </c>
       <c r="C4" t="n">
-        <v>11.50518762462368</v>
+        <v>11.50518762462366</v>
       </c>
       <c r="D4" t="n">
-        <v>11.93814682918101</v>
+        <v>11.9381468291773</v>
       </c>
       <c r="E4" t="n">
-        <v>11.06139010106316</v>
+        <v>11.06139010106313</v>
       </c>
       <c r="F4" t="n">
-        <v>11.94539942488761</v>
+        <v>11.94539942488763</v>
       </c>
       <c r="G4" t="n">
-        <v>26.68087134774396</v>
+        <v>12.1650209465401</v>
       </c>
       <c r="H4" t="n">
-        <v>30.5945054659198</v>
+        <v>30.59450546591906</v>
       </c>
       <c r="I4" t="n">
-        <v>12.10858010433555</v>
+        <v>12.10858010433553</v>
       </c>
       <c r="J4" t="n">
-        <v>27.44253062538152</v>
+        <v>12.38648813730597</v>
       </c>
       <c r="K4" t="n">
-        <v>12.03976863327969</v>
+        <v>12.0397686332803</v>
       </c>
       <c r="L4" t="n">
-        <v>11.94866119583271</v>
+        <v>11.94866119583203</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12.68378915754763</v>
+        <v>12.68378915754854</v>
       </c>
       <c r="C5" t="n">
-        <v>12.61618749252559</v>
+        <v>12.61618749252558</v>
       </c>
       <c r="D5" t="n">
-        <v>12.68383983868521</v>
+        <v>12.68383983868563</v>
       </c>
       <c r="E5" t="n">
-        <v>12.45248430649482</v>
+        <v>12.4524843064948</v>
       </c>
       <c r="F5" t="n">
-        <v>12.45248430649482</v>
+        <v>12.4524843064948</v>
       </c>
       <c r="G5" t="n">
-        <v>12.67262833473096</v>
+        <v>12.67262833473038</v>
       </c>
       <c r="H5" t="n">
-        <v>12.68378915754763</v>
+        <v>12.68378915754854</v>
       </c>
       <c r="I5" t="n">
-        <v>12.61618749252559</v>
+        <v>12.61618749252558</v>
       </c>
       <c r="J5" t="n">
-        <v>12.68378915754763</v>
+        <v>12.68378915754854</v>
       </c>
       <c r="K5" t="n">
-        <v>12.68378915754763</v>
+        <v>12.68378915754854</v>
       </c>
       <c r="L5" t="n">
-        <v>12.68378915754763</v>
+        <v>12.68378915754854</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24.63954930678725</v>
+        <v>24.63954930678798</v>
       </c>
       <c r="C6" t="n">
-        <v>37.88972480344643</v>
+        <v>37.88972480344633</v>
       </c>
       <c r="D6" t="n">
-        <v>40.90470454088967</v>
+        <v>40.90470454088879</v>
       </c>
       <c r="E6" t="n">
-        <v>34.22166243097233</v>
+        <v>34.22166243097219</v>
       </c>
       <c r="F6" t="n">
-        <v>24.90129290562943</v>
+        <v>24.90129290562935</v>
       </c>
       <c r="G6" t="n">
-        <v>38.10009716635211</v>
+        <v>38.10009716635165</v>
       </c>
       <c r="H6" t="n">
-        <v>38.11125798923653</v>
+        <v>38.11125798923529</v>
       </c>
       <c r="I6" t="n">
-        <v>38.04365632414662</v>
+        <v>38.04365632414646</v>
       </c>
       <c r="J6" t="n">
-        <v>38.11390551492268</v>
+        <v>38.11390551492188</v>
       </c>
       <c r="K6" t="n">
-        <v>24.38930540653382</v>
+        <v>24.38930540653385</v>
       </c>
       <c r="L6" t="n">
-        <v>52.18358414517883</v>
+        <v>52.18358414517807</v>
       </c>
     </row>
     <row r="7">
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>458.3400539981818</v>
+        <v>458.3400539981805</v>
       </c>
       <c r="C7" t="n">
         <v>584.0781263394352</v>
@@ -7063,25 +7063,25 @@
         <v>729.2552176407908</v>
       </c>
       <c r="F7" t="n">
-        <v>584.0781268563876</v>
+        <v>584.0781268563875</v>
       </c>
       <c r="G7" t="n">
-        <v>584.1345671816399</v>
+        <v>584.1345671816401</v>
       </c>
       <c r="H7" t="n">
-        <v>584.1457280044591</v>
+        <v>584.1457280044576</v>
       </c>
       <c r="I7" t="n">
         <v>584.0781263394352</v>
       </c>
       <c r="J7" t="n">
-        <v>584.1457280044591</v>
+        <v>584.1457280044576</v>
       </c>
       <c r="K7" t="n">
-        <v>508.2960982078808</v>
+        <v>508.2960982078814</v>
       </c>
       <c r="L7" t="n">
-        <v>584.1457280044591</v>
+        <v>584.1457280044576</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.535884788531666</v>
+        <v>2.53588478853209</v>
       </c>
       <c r="C8" t="n">
-        <v>7.335743361370179</v>
+        <v>7.335743361370169</v>
       </c>
       <c r="D8" t="n">
-        <v>9.733643957490887</v>
+        <v>9.733643957490244</v>
       </c>
       <c r="E8" t="n">
-        <v>7.335743361370179</v>
+        <v>7.335743361370169</v>
       </c>
       <c r="F8" t="n">
-        <v>7.335743361370179</v>
+        <v>7.335743361370169</v>
       </c>
       <c r="G8" t="n">
-        <v>4.916961329049859</v>
+        <v>4.91696132904947</v>
       </c>
       <c r="H8" t="n">
-        <v>10.49730003634732</v>
+        <v>10.49730003634667</v>
       </c>
       <c r="I8" t="n">
-        <v>7.335743361370179</v>
+        <v>7.335743361370169</v>
       </c>
       <c r="J8" t="n">
-        <v>8.1412546073536</v>
+        <v>8.141254607353682</v>
       </c>
       <c r="K8" t="n">
-        <v>7.498683716809296</v>
+        <v>7.49868371680876</v>
       </c>
       <c r="L8" t="n">
-        <v>8.247337329027207</v>
+        <v>9.720277293231204</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.666292820010183</v>
+        <v>7.666292820009661</v>
       </c>
       <c r="C9" t="n">
-        <v>8.712496799013685</v>
+        <v>8.712496799013675</v>
       </c>
       <c r="D9" t="n">
-        <v>10.59793929080372</v>
+        <v>10.59793929080361</v>
       </c>
       <c r="E9" t="n">
-        <v>8.712496799013685</v>
+        <v>8.712496799013675</v>
       </c>
       <c r="F9" t="n">
-        <v>8.712496799013685</v>
+        <v>8.712496799013675</v>
       </c>
       <c r="G9" t="n">
-        <v>8.597709336931162</v>
+        <v>8.597709336930722</v>
       </c>
       <c r="H9" t="n">
-        <v>10.90978994795194</v>
+        <v>10.90978994795108</v>
       </c>
       <c r="I9" t="n">
-        <v>8.712496799013685</v>
+        <v>8.712496799013675</v>
       </c>
       <c r="J9" t="n">
-        <v>9.950576998347598</v>
+        <v>9.950576998347366</v>
       </c>
       <c r="K9" t="n">
-        <v>9.687817020777196</v>
+        <v>9.687817020776608</v>
       </c>
       <c r="L9" t="n">
-        <v>10.59374103736669</v>
+        <v>10.59374103736672</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>55.11850663443095</v>
+        <v>55.11850663443011</v>
       </c>
       <c r="C2" t="n">
-        <v>47.52110315240783</v>
+        <v>47.52110315240774</v>
       </c>
       <c r="D2" t="n">
-        <v>135.5845222181586</v>
+        <v>135.5845222181578</v>
       </c>
       <c r="E2" t="n">
-        <v>47.52110315240783</v>
+        <v>47.52110315240774</v>
       </c>
       <c r="F2" t="n">
-        <v>47.52110315240783</v>
+        <v>47.52110315240774</v>
       </c>
       <c r="G2" t="n">
-        <v>145.4315111976243</v>
+        <v>145.4315111976224</v>
       </c>
       <c r="H2" t="n">
-        <v>182.2454813402733</v>
+        <v>182.2454813402711</v>
       </c>
       <c r="I2" t="n">
-        <v>47.52110315240783</v>
+        <v>47.52110315240774</v>
       </c>
       <c r="J2" t="n">
-        <v>46.38882627140836</v>
+        <v>46.38882627140762</v>
       </c>
       <c r="K2" t="n">
-        <v>37.58549115429088</v>
+        <v>37.58549115429038</v>
       </c>
       <c r="L2" t="n">
-        <v>132.6711302371762</v>
+        <v>23.40039355782678</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.615892744052436</v>
+        <v>3.615892744052325</v>
       </c>
       <c r="C3" t="n">
-        <v>2.503199848189114</v>
+        <v>2.503199848189059</v>
       </c>
       <c r="D3" t="n">
-        <v>3.615892744052435</v>
+        <v>3.615892744052325</v>
       </c>
       <c r="E3" t="n">
-        <v>2.803706323996928</v>
+        <v>2.803706323996901</v>
       </c>
       <c r="F3" t="n">
-        <v>2.803706323996928</v>
+        <v>2.803706323996872</v>
       </c>
       <c r="G3" t="n">
-        <v>3.60819633467261</v>
+        <v>3.608196334672674</v>
       </c>
       <c r="H3" t="n">
-        <v>3.615892744052435</v>
+        <v>3.615892744052324</v>
       </c>
       <c r="I3" t="n">
-        <v>3.56902274639363</v>
+        <v>3.569022746393491</v>
       </c>
       <c r="J3" t="n">
-        <v>3.615892744052435</v>
+        <v>3.615892744052325</v>
       </c>
       <c r="K3" t="n">
-        <v>3.615892744052435</v>
+        <v>3.615892744052325</v>
       </c>
       <c r="L3" t="n">
-        <v>3.615892744052435</v>
+        <v>3.615892744052325</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.176732952471752</v>
+        <v>6.176732952471352</v>
       </c>
       <c r="C4" t="n">
-        <v>5.817776921979518</v>
+        <v>5.817776921979528</v>
       </c>
       <c r="D4" t="n">
-        <v>6.56009518476773</v>
+        <v>6.560095184767545</v>
       </c>
       <c r="E4" t="n">
-        <v>5.690366776592637</v>
+        <v>5.690366776592459</v>
       </c>
       <c r="F4" t="n">
-        <v>6.079070619375659</v>
+        <v>6.079070619375591</v>
       </c>
       <c r="G4" t="n">
-        <v>18.19081369016832</v>
+        <v>18.19081369016819</v>
       </c>
       <c r="H4" t="n">
-        <v>21.71633272925278</v>
+        <v>21.71633272925151</v>
       </c>
       <c r="I4" t="n">
-        <v>18.15164010188948</v>
+        <v>18.15164010188945</v>
       </c>
       <c r="J4" t="n">
-        <v>18.94295365405434</v>
+        <v>18.94295365405382</v>
       </c>
       <c r="K4" t="n">
-        <v>5.87082300807955</v>
+        <v>5.870823008079324</v>
       </c>
       <c r="L4" t="n">
-        <v>6.141601069333574</v>
+        <v>6.141601069332888</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.912158121428772</v>
+        <v>7.912158121428923</v>
       </c>
       <c r="C5" t="n">
-        <v>7.865288123769924</v>
+        <v>7.865288123769897</v>
       </c>
       <c r="D5" t="n">
-        <v>7.912177967537997</v>
+        <v>7.912177967537978</v>
       </c>
       <c r="E5" t="n">
-        <v>7.773182036699269</v>
+        <v>7.773182036699214</v>
       </c>
       <c r="F5" t="n">
-        <v>7.773182036699269</v>
+        <v>7.773182036699214</v>
       </c>
       <c r="G5" t="n">
-        <v>7.904461712048801</v>
+        <v>7.904461712048527</v>
       </c>
       <c r="H5" t="n">
-        <v>7.912158121428772</v>
+        <v>7.912158121428923</v>
       </c>
       <c r="I5" t="n">
-        <v>7.865288123769924</v>
+        <v>7.865288123769897</v>
       </c>
       <c r="J5" t="n">
-        <v>7.912158121428772</v>
+        <v>7.912158121428923</v>
       </c>
       <c r="K5" t="n">
-        <v>7.912158121428772</v>
+        <v>7.912158121428923</v>
       </c>
       <c r="L5" t="n">
-        <v>7.912158121428772</v>
+        <v>7.912158121428923</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.40708350465323</v>
+        <v>18.40708350465331</v>
       </c>
       <c r="C6" t="n">
-        <v>28.66950334743765</v>
+        <v>28.6695033471621</v>
       </c>
       <c r="D6" t="n">
-        <v>30.95794957546824</v>
+        <v>30.95794957546727</v>
       </c>
       <c r="E6" t="n">
-        <v>25.83559409806187</v>
+        <v>25.83559409806183</v>
       </c>
       <c r="F6" t="n">
-        <v>18.6347717488177</v>
+        <v>18.63477174881744</v>
       </c>
       <c r="G6" t="n">
-        <v>28.79471434277832</v>
+        <v>28.79471434277778</v>
       </c>
       <c r="H6" t="n">
-        <v>28.80241075211054</v>
+        <v>28.80241075211073</v>
       </c>
       <c r="I6" t="n">
-        <v>28.75554075449945</v>
+        <v>28.75554075449903</v>
       </c>
       <c r="J6" t="n">
-        <v>28.80445371429793</v>
+        <v>28.80445371429796</v>
       </c>
       <c r="K6" t="n">
-        <v>18.21398496565149</v>
+        <v>18.21398496565142</v>
       </c>
       <c r="L6" t="n">
-        <v>39.6611992886749</v>
+        <v>39.66119928867391</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>485.2720984862551</v>
+        <v>485.2720984862548</v>
       </c>
       <c r="C7" t="n">
-        <v>618.8637173729546</v>
+        <v>618.8637173729544</v>
       </c>
       <c r="D7" t="n">
         <v>618.9105916846331</v>
       </c>
       <c r="E7" t="n">
-        <v>773.0797014043965</v>
+        <v>773.0797014043962</v>
       </c>
       <c r="F7" t="n">
-        <v>618.8637154152273</v>
+        <v>618.863715415227</v>
       </c>
       <c r="G7" t="n">
-        <v>618.9028909612341</v>
+        <v>618.9028909612334</v>
       </c>
       <c r="H7" t="n">
-        <v>618.9105873706137</v>
+        <v>618.9105873706133</v>
       </c>
       <c r="I7" t="n">
-        <v>618.8637173729546</v>
+        <v>618.8637173729544</v>
       </c>
       <c r="J7" t="n">
-        <v>618.9105873706137</v>
+        <v>618.9105873706133</v>
       </c>
       <c r="K7" t="n">
-        <v>541.4799238866181</v>
+        <v>541.4799238866178</v>
       </c>
       <c r="L7" t="n">
-        <v>618.9105873706137</v>
+        <v>618.9105873706133</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.95528379393119</v>
+        <v>5.955283793931211</v>
       </c>
       <c r="C8" t="n">
-        <v>4.384693260930777</v>
+        <v>4.384693260930749</v>
       </c>
       <c r="D8" t="n">
-        <v>3.991832153118916</v>
+        <v>3.99183215311871</v>
       </c>
       <c r="E8" t="n">
-        <v>4.384693260930777</v>
+        <v>4.384693260930749</v>
       </c>
       <c r="F8" t="n">
-        <v>4.384693260930777</v>
+        <v>4.384693260930749</v>
       </c>
       <c r="G8" t="n">
-        <v>3.833419086627694</v>
+        <v>3.833419086627337</v>
       </c>
       <c r="H8" t="n">
-        <v>3.225761073577202</v>
+        <v>3.225761073577347</v>
       </c>
       <c r="I8" t="n">
-        <v>4.384693260930777</v>
+        <v>4.384693260930749</v>
       </c>
       <c r="J8" t="n">
-        <v>6.247549386581339</v>
+        <v>6.247549386580904</v>
       </c>
       <c r="K8" t="n">
-        <v>6.381999137220627</v>
+        <v>6.381999137220681</v>
       </c>
       <c r="L8" t="n">
-        <v>4.636337470653844</v>
+        <v>4.636337470654091</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.575146893598881</v>
+        <v>6.575146893598569</v>
       </c>
       <c r="C9" t="n">
-        <v>4.928238034336339</v>
+        <v>4.928238034336309</v>
       </c>
       <c r="D9" t="n">
-        <v>5.775529121688073</v>
+        <v>5.775529121687908</v>
       </c>
       <c r="E9" t="n">
-        <v>4.928238034336339</v>
+        <v>4.928238034336309</v>
       </c>
       <c r="F9" t="n">
-        <v>4.928238034336339</v>
+        <v>4.928238034336309</v>
       </c>
       <c r="G9" t="n">
-        <v>5.682009830552652</v>
+        <v>5.682009830552643</v>
       </c>
       <c r="H9" t="n">
-        <v>5.467075321385337</v>
+        <v>5.467075321384794</v>
       </c>
       <c r="I9" t="n">
-        <v>4.928238034336339</v>
+        <v>4.928238034336309</v>
       </c>
       <c r="J9" t="n">
-        <v>6.694525904318579</v>
+        <v>6.694525904318513</v>
       </c>
       <c r="K9" t="n">
-        <v>6.748985547732262</v>
+        <v>6.748985547732263</v>
       </c>
       <c r="L9" t="n">
-        <v>6.039846013766793</v>
+        <v>6.906214604755688</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>119.7816842511191</v>
+        <v>119.7816842511189</v>
       </c>
       <c r="C2" t="n">
-        <v>55.62596229123791</v>
+        <v>55.62596229123754</v>
       </c>
       <c r="D2" t="n">
-        <v>115.2247438149604</v>
+        <v>115.22474381496</v>
       </c>
       <c r="E2" t="n">
-        <v>55.62596229123791</v>
+        <v>55.62596229123754</v>
       </c>
       <c r="F2" t="n">
-        <v>55.62596229123791</v>
+        <v>55.62596229123754</v>
       </c>
       <c r="G2" t="n">
-        <v>217.7178155833867</v>
+        <v>217.7178155833818</v>
       </c>
       <c r="H2" t="n">
-        <v>76.50149902462358</v>
+        <v>76.50149902462398</v>
       </c>
       <c r="I2" t="n">
-        <v>55.62596229123791</v>
+        <v>55.62596229123754</v>
       </c>
       <c r="J2" t="n">
         <v>102.836577000766</v>
       </c>
       <c r="K2" t="n">
-        <v>64.91947539560567</v>
+        <v>64.91947539560586</v>
       </c>
       <c r="L2" t="n">
-        <v>77.77198216267152</v>
+        <v>120.6792894287696</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.301685135992912</v>
+        <v>5.301685135993555</v>
       </c>
       <c r="C3" t="n">
-        <v>3.996428468580294</v>
+        <v>3.996428468580268</v>
       </c>
       <c r="D3" t="n">
-        <v>5.301685135992912</v>
+        <v>5.301685135993555</v>
       </c>
       <c r="E3" t="n">
-        <v>4.373808858386899</v>
+        <v>4.373808858386839</v>
       </c>
       <c r="F3" t="n">
-        <v>4.373808858386894</v>
+        <v>4.373808858386827</v>
       </c>
       <c r="G3" t="n">
-        <v>5.290237369653593</v>
+        <v>5.290237369653899</v>
       </c>
       <c r="H3" t="n">
-        <v>5.301685135992912</v>
+        <v>5.301685135993555</v>
       </c>
       <c r="I3" t="n">
-        <v>5.231285642743446</v>
+        <v>5.231285642743442</v>
       </c>
       <c r="J3" t="n">
-        <v>5.301685135992912</v>
+        <v>5.301685135993555</v>
       </c>
       <c r="K3" t="n">
-        <v>5.301685135992912</v>
+        <v>5.301685135993555</v>
       </c>
       <c r="L3" t="n">
-        <v>5.301685135992911</v>
+        <v>5.301685135993554</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21.84153302426971</v>
+        <v>21.84153302427039</v>
       </c>
       <c r="C4" t="n">
-        <v>8.24586395414577</v>
+        <v>8.245863954145898</v>
       </c>
       <c r="D4" t="n">
-        <v>8.914219126866012</v>
+        <v>8.914253534698643</v>
       </c>
       <c r="E4" t="n">
-        <v>7.983782356324939</v>
+        <v>7.98378235632505</v>
       </c>
       <c r="F4" t="n">
-        <v>8.629669316780557</v>
+        <v>8.629669316780531</v>
       </c>
       <c r="G4" t="n">
-        <v>8.787599957805039</v>
+        <v>21.83008525793071</v>
       </c>
       <c r="H4" t="n">
-        <v>24.84254493037103</v>
+        <v>24.84254493037061</v>
       </c>
       <c r="I4" t="n">
-        <v>21.77113353102034</v>
+        <v>21.7711335310209</v>
       </c>
       <c r="J4" t="n">
-        <v>8.975385917660645</v>
+        <v>8.975385917660915</v>
       </c>
       <c r="K4" t="n">
-        <v>8.453478495561873</v>
+        <v>8.453478495561393</v>
       </c>
       <c r="L4" t="n">
-        <v>8.684837437238894</v>
+        <v>8.684837437239791</v>
       </c>
     </row>
     <row r="5">
@@ -7766,25 +7766,25 @@
         <v>10.07380462083996</v>
       </c>
       <c r="C5" t="n">
-        <v>10.00340512759069</v>
+        <v>10.00340512759048</v>
       </c>
       <c r="D5" t="n">
-        <v>10.07382018994673</v>
+        <v>10.07382018994734</v>
       </c>
       <c r="E5" t="n">
-        <v>9.892331104000743</v>
+        <v>9.892331104000457</v>
       </c>
       <c r="F5" t="n">
-        <v>9.892331104000744</v>
+        <v>9.892331104000457</v>
       </c>
       <c r="G5" t="n">
-        <v>10.06235685450082</v>
+        <v>10.06235685450023</v>
       </c>
       <c r="H5" t="n">
         <v>10.07380462083996</v>
       </c>
       <c r="I5" t="n">
-        <v>10.00340512759069</v>
+        <v>10.00340512759048</v>
       </c>
       <c r="J5" t="n">
         <v>10.07380462083996</v>
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.00746549867201</v>
+        <v>21.00746549867253</v>
       </c>
       <c r="C6" t="n">
-        <v>32.46958548915371</v>
+        <v>32.46958548915307</v>
       </c>
       <c r="D6" t="n">
-        <v>35.05680416334447</v>
+        <v>35.05680416334552</v>
       </c>
       <c r="E6" t="n">
-        <v>29.29813907418257</v>
+        <v>29.29813907418209</v>
       </c>
       <c r="F6" t="n">
-        <v>21.23965305601324</v>
+        <v>21.23965305601333</v>
       </c>
       <c r="G6" t="n">
-        <v>32.63246355372589</v>
+        <v>32.63246355372544</v>
       </c>
       <c r="H6" t="n">
-        <v>32.64391131997284</v>
+        <v>32.64391131997297</v>
       </c>
       <c r="I6" t="n">
-        <v>32.57351182681586</v>
+        <v>32.57351182681627</v>
       </c>
       <c r="J6" t="n">
-        <v>32.64619818144276</v>
+        <v>32.64619818144286</v>
       </c>
       <c r="K6" t="n">
-        <v>20.79131254658944</v>
+        <v>20.79131254658909</v>
       </c>
       <c r="L6" t="n">
-        <v>44.79915197214698</v>
+        <v>44.79915197214594</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>455.7472849511624</v>
+        <v>455.7472849511631</v>
       </c>
       <c r="C7" t="n">
-        <v>580.971184938292</v>
+        <v>580.9711849382925</v>
       </c>
       <c r="D7" t="n">
         <v>581.0415935078729</v>
       </c>
       <c r="E7" t="n">
-        <v>725.5581576381105</v>
+        <v>725.5581576381104</v>
       </c>
       <c r="F7" t="n">
-        <v>580.9711845886782</v>
+        <v>580.9711845886785</v>
       </c>
       <c r="G7" t="n">
-        <v>581.0301366652022</v>
+        <v>581.0301366652019</v>
       </c>
       <c r="H7" t="n">
-        <v>581.0415844315421</v>
+        <v>581.041584431543</v>
       </c>
       <c r="I7" t="n">
-        <v>580.971184938292</v>
+        <v>580.9711849382925</v>
       </c>
       <c r="J7" t="n">
-        <v>581.0415844315421</v>
+        <v>581.041584431543</v>
       </c>
       <c r="K7" t="n">
-        <v>423.273694080008</v>
+        <v>508.445579061381</v>
       </c>
       <c r="L7" t="n">
-        <v>581.0415844315421</v>
+        <v>581.041584431543</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.426747696240468</v>
+        <v>6.426747696240668</v>
       </c>
       <c r="C8" t="n">
-        <v>6.28283723042713</v>
+        <v>6.282837230427114</v>
       </c>
       <c r="D8" t="n">
-        <v>6.37224369790731</v>
+        <v>6.372243697907411</v>
       </c>
       <c r="E8" t="n">
-        <v>6.28283723042713</v>
+        <v>6.282837230427114</v>
       </c>
       <c r="F8" t="n">
-        <v>6.28283723042713</v>
+        <v>6.282837230427114</v>
       </c>
       <c r="G8" t="n">
-        <v>3.790258467401258</v>
+        <v>3.790258467400699</v>
       </c>
       <c r="H8" t="n">
-        <v>7.63633287270012</v>
+        <v>7.636332872700282</v>
       </c>
       <c r="I8" t="n">
-        <v>6.28283723042713</v>
+        <v>6.282837230427114</v>
       </c>
       <c r="J8" t="n">
-        <v>7.054995315617448</v>
+        <v>7.054995315617822</v>
       </c>
       <c r="K8" t="n">
-        <v>7.752411931394383</v>
+        <v>7.752411931394355</v>
       </c>
       <c r="L8" t="n">
-        <v>6.836114928959422</v>
+        <v>6.836114928959801</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.025453125142715</v>
+        <v>8.025453125142624</v>
       </c>
       <c r="C9" t="n">
-        <v>6.96483238823713</v>
+        <v>6.964832388237109</v>
       </c>
       <c r="D9" t="n">
-        <v>8.003331996849763</v>
+        <v>8.003331996849813</v>
       </c>
       <c r="E9" t="n">
-        <v>6.96483238823713</v>
+        <v>6.964832388237109</v>
       </c>
       <c r="F9" t="n">
-        <v>6.96483238823713</v>
+        <v>6.964832388237109</v>
       </c>
       <c r="G9" t="n">
-        <v>6.913757380986312</v>
+        <v>6.913757380986556</v>
       </c>
       <c r="H9" t="n">
-        <v>8.519668473497896</v>
+        <v>8.519668473498127</v>
       </c>
       <c r="I9" t="n">
-        <v>6.96483238823713</v>
+        <v>6.964832388237109</v>
       </c>
       <c r="J9" t="n">
-        <v>8.282195051881841</v>
+        <v>8.282195051882017</v>
       </c>
       <c r="K9" t="n">
-        <v>8.565470217448809</v>
+        <v>8.565470217449125</v>
       </c>
       <c r="L9" t="n">
-        <v>8.194060231633237</v>
+        <v>8.194060231633399</v>
       </c>
     </row>
   </sheetData>
